--- a/document/UI-001_VR内UI_画面仕様書.xlsx
+++ b/document/UI-001_VR内UI_画面仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tryro-dev-camera_sim\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7636C92F-8786-439D-929D-CB3125B013D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CCF119-7FB1-4574-85AD-9DC3F41ED29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="72">
   <si>
     <t>ソリューションタイトル</t>
   </si>
@@ -481,6 +481,53 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マップ移動ボタン</t>
+    <rPh sb="3" eb="5">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指定したマップに移動</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マップ選択ボタン</t>
+    <rPh sb="3" eb="5">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マップ名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マップを選択、選択されると枠を表示</t>
+    <rPh sb="4" eb="6">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2713,6 +2760,369 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>145675</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>220358</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AED655B-D82E-AE9A-6F21-000813CF9EDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="6776" t="3844" r="28778" b="40793"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1322293" y="7283823"/>
+          <a:ext cx="8516472" cy="5487123"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>141193</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>186018</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>17928</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>85165</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="正方形/長方形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B49300CC-1962-4087-8B46-5EE7E3CD78F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082487" y="7324165"/>
+          <a:ext cx="582706" cy="605118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>7</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>91886</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>159125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>203945</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>58272</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="正方形/長方形 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D66BDC58-905A-4830-8EF9-AD8468C7A7F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8328210" y="7297272"/>
+          <a:ext cx="582706" cy="605118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>6</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>136711</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>13447</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>13449</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="正方形/長方形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD26E92D-AA7E-474B-816B-76ED297C16B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2254623" y="8429066"/>
+          <a:ext cx="582706" cy="605118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>14</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>42581</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>154642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>154640</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>53790</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="正方形/長方形 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAF58C65-E591-441B-8A3D-44BB9472B873}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4043081" y="11057966"/>
+          <a:ext cx="582706" cy="605118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>15</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2979,7 +3389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CI53"/>
+  <dimension ref="A1:CI77"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="87" width="3.125" customWidth="1"/>
@@ -5861,7 +6271,7 @@
       <c r="CH32" s="84"/>
       <c r="CI32" s="85"/>
     </row>
-    <row r="33" spans="1:87" ht="19.5" thickBot="1">
+    <row r="33" spans="1:87">
       <c r="A33" s="84"/>
       <c r="B33" s="84"/>
       <c r="C33" s="84"/>
@@ -5950,2023 +6360,4201 @@
       <c r="CH33" s="84"/>
       <c r="CI33" s="85"/>
     </row>
-    <row r="34" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A34" s="25" t="s">
+    <row r="34" spans="1:87">
+      <c r="A34" s="84"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="84"/>
+      <c r="D34" s="84"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="84"/>
+      <c r="H34" s="84"/>
+      <c r="I34" s="84"/>
+      <c r="J34" s="84"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="84"/>
+      <c r="M34" s="84"/>
+      <c r="N34" s="84"/>
+      <c r="O34" s="84"/>
+      <c r="P34" s="84"/>
+      <c r="Q34" s="84"/>
+      <c r="R34" s="84"/>
+      <c r="S34" s="84"/>
+      <c r="T34" s="84"/>
+      <c r="U34" s="84"/>
+      <c r="V34" s="84"/>
+      <c r="W34" s="84"/>
+      <c r="X34" s="84"/>
+      <c r="Y34" s="84"/>
+      <c r="Z34" s="84"/>
+      <c r="AA34" s="84"/>
+      <c r="AB34" s="84"/>
+      <c r="AC34" s="84"/>
+      <c r="AD34" s="84"/>
+      <c r="AE34" s="84"/>
+      <c r="AF34" s="84"/>
+      <c r="AG34" s="84"/>
+      <c r="AH34" s="84"/>
+      <c r="AI34" s="84"/>
+      <c r="AJ34" s="84"/>
+      <c r="AK34" s="84"/>
+      <c r="AL34" s="84"/>
+      <c r="AM34" s="84"/>
+      <c r="AN34" s="84"/>
+      <c r="AO34" s="84"/>
+      <c r="AP34" s="84"/>
+      <c r="AQ34" s="84"/>
+      <c r="AR34" s="84"/>
+      <c r="AS34" s="84"/>
+      <c r="AT34" s="84"/>
+      <c r="AU34" s="84"/>
+      <c r="AV34" s="84"/>
+      <c r="AW34" s="84"/>
+      <c r="AX34" s="84"/>
+      <c r="AY34" s="84"/>
+      <c r="AZ34" s="84"/>
+      <c r="BA34" s="84"/>
+      <c r="BB34" s="84"/>
+      <c r="BC34" s="84"/>
+      <c r="BD34" s="84"/>
+      <c r="BE34" s="84"/>
+      <c r="BF34" s="84"/>
+      <c r="BG34" s="84"/>
+      <c r="BH34" s="84"/>
+      <c r="BI34" s="84"/>
+      <c r="BJ34" s="84"/>
+      <c r="BK34" s="84"/>
+      <c r="BL34" s="84"/>
+      <c r="BM34" s="84"/>
+      <c r="BN34" s="84"/>
+      <c r="BO34" s="84"/>
+      <c r="BP34" s="84"/>
+      <c r="BQ34" s="84"/>
+      <c r="BR34" s="84"/>
+      <c r="BS34" s="84"/>
+      <c r="BT34" s="84"/>
+      <c r="BU34" s="84"/>
+      <c r="BV34" s="84"/>
+      <c r="BW34" s="84"/>
+      <c r="BX34" s="84"/>
+      <c r="BY34" s="84"/>
+      <c r="BZ34" s="84"/>
+      <c r="CA34" s="84"/>
+      <c r="CB34" s="84"/>
+      <c r="CC34" s="84"/>
+      <c r="CD34" s="84"/>
+      <c r="CE34" s="84"/>
+      <c r="CF34" s="84"/>
+      <c r="CG34" s="84"/>
+      <c r="CH34" s="84"/>
+      <c r="CI34" s="85"/>
+    </row>
+    <row r="35" spans="1:87">
+      <c r="A35" s="84"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="84"/>
+      <c r="J35" s="84"/>
+      <c r="K35" s="84"/>
+      <c r="L35" s="84"/>
+      <c r="M35" s="84"/>
+      <c r="N35" s="84"/>
+      <c r="O35" s="84"/>
+      <c r="P35" s="84"/>
+      <c r="Q35" s="84"/>
+      <c r="R35" s="84"/>
+      <c r="S35" s="84"/>
+      <c r="T35" s="84"/>
+      <c r="U35" s="84"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="84"/>
+      <c r="X35" s="84"/>
+      <c r="Y35" s="84"/>
+      <c r="Z35" s="84"/>
+      <c r="AA35" s="84"/>
+      <c r="AB35" s="84"/>
+      <c r="AC35" s="84"/>
+      <c r="AD35" s="84"/>
+      <c r="AE35" s="84"/>
+      <c r="AF35" s="84"/>
+      <c r="AG35" s="84"/>
+      <c r="AH35" s="84"/>
+      <c r="AI35" s="84"/>
+      <c r="AJ35" s="84"/>
+      <c r="AK35" s="84"/>
+      <c r="AL35" s="84"/>
+      <c r="AM35" s="84"/>
+      <c r="AN35" s="84"/>
+      <c r="AO35" s="84"/>
+      <c r="AP35" s="84"/>
+      <c r="AQ35" s="84"/>
+      <c r="AR35" s="84"/>
+      <c r="AS35" s="84"/>
+      <c r="AT35" s="84"/>
+      <c r="AU35" s="84"/>
+      <c r="AV35" s="84"/>
+      <c r="AW35" s="84"/>
+      <c r="AX35" s="84"/>
+      <c r="AY35" s="84"/>
+      <c r="AZ35" s="84"/>
+      <c r="BA35" s="84"/>
+      <c r="BB35" s="84"/>
+      <c r="BC35" s="84"/>
+      <c r="BD35" s="84"/>
+      <c r="BE35" s="84"/>
+      <c r="BF35" s="84"/>
+      <c r="BG35" s="84"/>
+      <c r="BH35" s="84"/>
+      <c r="BI35" s="84"/>
+      <c r="BJ35" s="84"/>
+      <c r="BK35" s="84"/>
+      <c r="BL35" s="84"/>
+      <c r="BM35" s="84"/>
+      <c r="BN35" s="84"/>
+      <c r="BO35" s="84"/>
+      <c r="BP35" s="84"/>
+      <c r="BQ35" s="84"/>
+      <c r="BR35" s="84"/>
+      <c r="BS35" s="84"/>
+      <c r="BT35" s="84"/>
+      <c r="BU35" s="84"/>
+      <c r="BV35" s="84"/>
+      <c r="BW35" s="84"/>
+      <c r="BX35" s="84"/>
+      <c r="BY35" s="84"/>
+      <c r="BZ35" s="84"/>
+      <c r="CA35" s="84"/>
+      <c r="CB35" s="84"/>
+      <c r="CC35" s="84"/>
+      <c r="CD35" s="84"/>
+      <c r="CE35" s="84"/>
+      <c r="CF35" s="84"/>
+      <c r="CG35" s="84"/>
+      <c r="CH35" s="84"/>
+      <c r="CI35" s="85"/>
+    </row>
+    <row r="36" spans="1:87">
+      <c r="A36" s="84"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="84"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="84"/>
+      <c r="J36" s="84"/>
+      <c r="K36" s="84"/>
+      <c r="L36" s="84"/>
+      <c r="M36" s="84"/>
+      <c r="N36" s="84"/>
+      <c r="O36" s="84"/>
+      <c r="P36" s="84"/>
+      <c r="Q36" s="84"/>
+      <c r="R36" s="84"/>
+      <c r="S36" s="84"/>
+      <c r="T36" s="84"/>
+      <c r="U36" s="84"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="84"/>
+      <c r="X36" s="84"/>
+      <c r="Y36" s="84"/>
+      <c r="Z36" s="84"/>
+      <c r="AA36" s="84"/>
+      <c r="AB36" s="84"/>
+      <c r="AC36" s="84"/>
+      <c r="AD36" s="84"/>
+      <c r="AE36" s="84"/>
+      <c r="AF36" s="84"/>
+      <c r="AG36" s="84"/>
+      <c r="AH36" s="84"/>
+      <c r="AI36" s="84"/>
+      <c r="AJ36" s="84"/>
+      <c r="AK36" s="84"/>
+      <c r="AL36" s="84"/>
+      <c r="AM36" s="84"/>
+      <c r="AN36" s="84"/>
+      <c r="AO36" s="84"/>
+      <c r="AP36" s="84"/>
+      <c r="AQ36" s="84"/>
+      <c r="AR36" s="84"/>
+      <c r="AS36" s="84"/>
+      <c r="AT36" s="84"/>
+      <c r="AU36" s="84"/>
+      <c r="AV36" s="84"/>
+      <c r="AW36" s="84"/>
+      <c r="AX36" s="84"/>
+      <c r="AY36" s="84"/>
+      <c r="AZ36" s="84"/>
+      <c r="BA36" s="84"/>
+      <c r="BB36" s="84"/>
+      <c r="BC36" s="84"/>
+      <c r="BD36" s="84"/>
+      <c r="BE36" s="84"/>
+      <c r="BF36" s="84"/>
+      <c r="BG36" s="84"/>
+      <c r="BH36" s="84"/>
+      <c r="BI36" s="84"/>
+      <c r="BJ36" s="84"/>
+      <c r="BK36" s="84"/>
+      <c r="BL36" s="84"/>
+      <c r="BM36" s="84"/>
+      <c r="BN36" s="84"/>
+      <c r="BO36" s="84"/>
+      <c r="BP36" s="84"/>
+      <c r="BQ36" s="84"/>
+      <c r="BR36" s="84"/>
+      <c r="BS36" s="84"/>
+      <c r="BT36" s="84"/>
+      <c r="BU36" s="84"/>
+      <c r="BV36" s="84"/>
+      <c r="BW36" s="84"/>
+      <c r="BX36" s="84"/>
+      <c r="BY36" s="84"/>
+      <c r="BZ36" s="84"/>
+      <c r="CA36" s="84"/>
+      <c r="CB36" s="84"/>
+      <c r="CC36" s="84"/>
+      <c r="CD36" s="84"/>
+      <c r="CE36" s="84"/>
+      <c r="CF36" s="84"/>
+      <c r="CG36" s="84"/>
+      <c r="CH36" s="84"/>
+      <c r="CI36" s="85"/>
+    </row>
+    <row r="37" spans="1:87">
+      <c r="A37" s="84"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="84"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84"/>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84"/>
+      <c r="J37" s="84"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="84"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="84"/>
+      <c r="O37" s="84"/>
+      <c r="P37" s="84"/>
+      <c r="Q37" s="84"/>
+      <c r="R37" s="84"/>
+      <c r="S37" s="84"/>
+      <c r="T37" s="84"/>
+      <c r="U37" s="84"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="84"/>
+      <c r="X37" s="84"/>
+      <c r="Y37" s="84"/>
+      <c r="Z37" s="84"/>
+      <c r="AA37" s="84"/>
+      <c r="AB37" s="84"/>
+      <c r="AC37" s="84"/>
+      <c r="AD37" s="84"/>
+      <c r="AE37" s="84"/>
+      <c r="AF37" s="84"/>
+      <c r="AG37" s="84"/>
+      <c r="AH37" s="84"/>
+      <c r="AI37" s="84"/>
+      <c r="AJ37" s="84"/>
+      <c r="AK37" s="84"/>
+      <c r="AL37" s="84"/>
+      <c r="AM37" s="84"/>
+      <c r="AN37" s="84"/>
+      <c r="AO37" s="84"/>
+      <c r="AP37" s="84"/>
+      <c r="AQ37" s="84"/>
+      <c r="AR37" s="84"/>
+      <c r="AS37" s="84"/>
+      <c r="AT37" s="84"/>
+      <c r="AU37" s="84"/>
+      <c r="AV37" s="84"/>
+      <c r="AW37" s="84"/>
+      <c r="AX37" s="84"/>
+      <c r="AY37" s="84"/>
+      <c r="AZ37" s="84"/>
+      <c r="BA37" s="84"/>
+      <c r="BB37" s="84"/>
+      <c r="BC37" s="84"/>
+      <c r="BD37" s="84"/>
+      <c r="BE37" s="84"/>
+      <c r="BF37" s="84"/>
+      <c r="BG37" s="84"/>
+      <c r="BH37" s="84"/>
+      <c r="BI37" s="84"/>
+      <c r="BJ37" s="84"/>
+      <c r="BK37" s="84"/>
+      <c r="BL37" s="84"/>
+      <c r="BM37" s="84"/>
+      <c r="BN37" s="84"/>
+      <c r="BO37" s="84"/>
+      <c r="BP37" s="84"/>
+      <c r="BQ37" s="84"/>
+      <c r="BR37" s="84"/>
+      <c r="BS37" s="84"/>
+      <c r="BT37" s="84"/>
+      <c r="BU37" s="84"/>
+      <c r="BV37" s="84"/>
+      <c r="BW37" s="84"/>
+      <c r="BX37" s="84"/>
+      <c r="BY37" s="84"/>
+      <c r="BZ37" s="84"/>
+      <c r="CA37" s="84"/>
+      <c r="CB37" s="84"/>
+      <c r="CC37" s="84"/>
+      <c r="CD37" s="84"/>
+      <c r="CE37" s="84"/>
+      <c r="CF37" s="84"/>
+      <c r="CG37" s="84"/>
+      <c r="CH37" s="84"/>
+      <c r="CI37" s="85"/>
+    </row>
+    <row r="38" spans="1:87">
+      <c r="A38" s="84"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84"/>
+      <c r="G38" s="84"/>
+      <c r="H38" s="84"/>
+      <c r="I38" s="84"/>
+      <c r="J38" s="84"/>
+      <c r="K38" s="84"/>
+      <c r="L38" s="84"/>
+      <c r="M38" s="84"/>
+      <c r="N38" s="84"/>
+      <c r="O38" s="84"/>
+      <c r="P38" s="84"/>
+      <c r="Q38" s="84"/>
+      <c r="R38" s="84"/>
+      <c r="S38" s="84"/>
+      <c r="T38" s="84"/>
+      <c r="U38" s="84"/>
+      <c r="V38" s="84"/>
+      <c r="W38" s="84"/>
+      <c r="X38" s="84"/>
+      <c r="Y38" s="84"/>
+      <c r="Z38" s="84"/>
+      <c r="AA38" s="84"/>
+      <c r="AB38" s="84"/>
+      <c r="AC38" s="84"/>
+      <c r="AD38" s="84"/>
+      <c r="AE38" s="84"/>
+      <c r="AF38" s="84"/>
+      <c r="AG38" s="84"/>
+      <c r="AH38" s="84"/>
+      <c r="AI38" s="84"/>
+      <c r="AJ38" s="84"/>
+      <c r="AK38" s="84"/>
+      <c r="AL38" s="84"/>
+      <c r="AM38" s="84"/>
+      <c r="AN38" s="84"/>
+      <c r="AO38" s="84"/>
+      <c r="AP38" s="84"/>
+      <c r="AQ38" s="84"/>
+      <c r="AR38" s="84"/>
+      <c r="AS38" s="84"/>
+      <c r="AT38" s="84"/>
+      <c r="AU38" s="84"/>
+      <c r="AV38" s="84"/>
+      <c r="AW38" s="84"/>
+      <c r="AX38" s="84"/>
+      <c r="AY38" s="84"/>
+      <c r="AZ38" s="84"/>
+      <c r="BA38" s="84"/>
+      <c r="BB38" s="84"/>
+      <c r="BC38" s="84"/>
+      <c r="BD38" s="84"/>
+      <c r="BE38" s="84"/>
+      <c r="BF38" s="84"/>
+      <c r="BG38" s="84"/>
+      <c r="BH38" s="84"/>
+      <c r="BI38" s="84"/>
+      <c r="BJ38" s="84"/>
+      <c r="BK38" s="84"/>
+      <c r="BL38" s="84"/>
+      <c r="BM38" s="84"/>
+      <c r="BN38" s="84"/>
+      <c r="BO38" s="84"/>
+      <c r="BP38" s="84"/>
+      <c r="BQ38" s="84"/>
+      <c r="BR38" s="84"/>
+      <c r="BS38" s="84"/>
+      <c r="BT38" s="84"/>
+      <c r="BU38" s="84"/>
+      <c r="BV38" s="84"/>
+      <c r="BW38" s="84"/>
+      <c r="BX38" s="84"/>
+      <c r="BY38" s="84"/>
+      <c r="BZ38" s="84"/>
+      <c r="CA38" s="84"/>
+      <c r="CB38" s="84"/>
+      <c r="CC38" s="84"/>
+      <c r="CD38" s="84"/>
+      <c r="CE38" s="84"/>
+      <c r="CF38" s="84"/>
+      <c r="CG38" s="84"/>
+      <c r="CH38" s="84"/>
+      <c r="CI38" s="85"/>
+    </row>
+    <row r="39" spans="1:87">
+      <c r="A39" s="84"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="84"/>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
+      <c r="J39" s="84"/>
+      <c r="K39" s="84"/>
+      <c r="L39" s="84"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="84"/>
+      <c r="O39" s="84"/>
+      <c r="P39" s="84"/>
+      <c r="Q39" s="84"/>
+      <c r="R39" s="84"/>
+      <c r="S39" s="84"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
+      <c r="Z39" s="84"/>
+      <c r="AA39" s="84"/>
+      <c r="AB39" s="84"/>
+      <c r="AC39" s="84"/>
+      <c r="AD39" s="84"/>
+      <c r="AE39" s="84"/>
+      <c r="AF39" s="84"/>
+      <c r="AG39" s="84"/>
+      <c r="AH39" s="84"/>
+      <c r="AI39" s="84"/>
+      <c r="AJ39" s="84"/>
+      <c r="AK39" s="84"/>
+      <c r="AL39" s="84"/>
+      <c r="AM39" s="84"/>
+      <c r="AN39" s="84"/>
+      <c r="AO39" s="84"/>
+      <c r="AP39" s="84"/>
+      <c r="AQ39" s="84"/>
+      <c r="AR39" s="84"/>
+      <c r="AS39" s="84"/>
+      <c r="AT39" s="84"/>
+      <c r="AU39" s="84"/>
+      <c r="AV39" s="84"/>
+      <c r="AW39" s="84"/>
+      <c r="AX39" s="84"/>
+      <c r="AY39" s="84"/>
+      <c r="AZ39" s="84"/>
+      <c r="BA39" s="84"/>
+      <c r="BB39" s="84"/>
+      <c r="BC39" s="84"/>
+      <c r="BD39" s="84"/>
+      <c r="BE39" s="84"/>
+      <c r="BF39" s="84"/>
+      <c r="BG39" s="84"/>
+      <c r="BH39" s="84"/>
+      <c r="BI39" s="84"/>
+      <c r="BJ39" s="84"/>
+      <c r="BK39" s="84"/>
+      <c r="BL39" s="84"/>
+      <c r="BM39" s="84"/>
+      <c r="BN39" s="84"/>
+      <c r="BO39" s="84"/>
+      <c r="BP39" s="84"/>
+      <c r="BQ39" s="84"/>
+      <c r="BR39" s="84"/>
+      <c r="BS39" s="84"/>
+      <c r="BT39" s="84"/>
+      <c r="BU39" s="84"/>
+      <c r="BV39" s="84"/>
+      <c r="BW39" s="84"/>
+      <c r="BX39" s="84"/>
+      <c r="BY39" s="84"/>
+      <c r="BZ39" s="84"/>
+      <c r="CA39" s="84"/>
+      <c r="CB39" s="84"/>
+      <c r="CC39" s="84"/>
+      <c r="CD39" s="84"/>
+      <c r="CE39" s="84"/>
+      <c r="CF39" s="84"/>
+      <c r="CG39" s="84"/>
+      <c r="CH39" s="84"/>
+      <c r="CI39" s="85"/>
+    </row>
+    <row r="40" spans="1:87">
+      <c r="A40" s="84"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="84"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
+      <c r="J40" s="84"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="84"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="84"/>
+      <c r="O40" s="84"/>
+      <c r="P40" s="84"/>
+      <c r="Q40" s="84"/>
+      <c r="R40" s="84"/>
+      <c r="S40" s="84"/>
+      <c r="T40" s="84"/>
+      <c r="U40" s="84"/>
+      <c r="V40" s="84"/>
+      <c r="W40" s="84"/>
+      <c r="X40" s="84"/>
+      <c r="Y40" s="84"/>
+      <c r="Z40" s="84"/>
+      <c r="AA40" s="84"/>
+      <c r="AB40" s="84"/>
+      <c r="AC40" s="84"/>
+      <c r="AD40" s="84"/>
+      <c r="AE40" s="84"/>
+      <c r="AF40" s="84"/>
+      <c r="AG40" s="84"/>
+      <c r="AH40" s="84"/>
+      <c r="AI40" s="84"/>
+      <c r="AJ40" s="84"/>
+      <c r="AK40" s="84"/>
+      <c r="AL40" s="84"/>
+      <c r="AM40" s="84"/>
+      <c r="AN40" s="84"/>
+      <c r="AO40" s="84"/>
+      <c r="AP40" s="84"/>
+      <c r="AQ40" s="84"/>
+      <c r="AR40" s="84"/>
+      <c r="AS40" s="84"/>
+      <c r="AT40" s="84"/>
+      <c r="AU40" s="84"/>
+      <c r="AV40" s="84"/>
+      <c r="AW40" s="84"/>
+      <c r="AX40" s="84"/>
+      <c r="AY40" s="84"/>
+      <c r="AZ40" s="84"/>
+      <c r="BA40" s="84"/>
+      <c r="BB40" s="84"/>
+      <c r="BC40" s="84"/>
+      <c r="BD40" s="84"/>
+      <c r="BE40" s="84"/>
+      <c r="BF40" s="84"/>
+      <c r="BG40" s="84"/>
+      <c r="BH40" s="84"/>
+      <c r="BI40" s="84"/>
+      <c r="BJ40" s="84"/>
+      <c r="BK40" s="84"/>
+      <c r="BL40" s="84"/>
+      <c r="BM40" s="84"/>
+      <c r="BN40" s="84"/>
+      <c r="BO40" s="84"/>
+      <c r="BP40" s="84"/>
+      <c r="BQ40" s="84"/>
+      <c r="BR40" s="84"/>
+      <c r="BS40" s="84"/>
+      <c r="BT40" s="84"/>
+      <c r="BU40" s="84"/>
+      <c r="BV40" s="84"/>
+      <c r="BW40" s="84"/>
+      <c r="BX40" s="84"/>
+      <c r="BY40" s="84"/>
+      <c r="BZ40" s="84"/>
+      <c r="CA40" s="84"/>
+      <c r="CB40" s="84"/>
+      <c r="CC40" s="84"/>
+      <c r="CD40" s="84"/>
+      <c r="CE40" s="84"/>
+      <c r="CF40" s="84"/>
+      <c r="CG40" s="84"/>
+      <c r="CH40" s="84"/>
+      <c r="CI40" s="85"/>
+    </row>
+    <row r="41" spans="1:87">
+      <c r="A41" s="84"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
+      <c r="N41" s="84"/>
+      <c r="O41" s="84"/>
+      <c r="P41" s="84"/>
+      <c r="Q41" s="84"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="84"/>
+      <c r="T41" s="84"/>
+      <c r="U41" s="84"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="84"/>
+      <c r="Z41" s="84"/>
+      <c r="AA41" s="84"/>
+      <c r="AB41" s="84"/>
+      <c r="AC41" s="84"/>
+      <c r="AD41" s="84"/>
+      <c r="AE41" s="84"/>
+      <c r="AF41" s="84"/>
+      <c r="AG41" s="84"/>
+      <c r="AH41" s="84"/>
+      <c r="AI41" s="84"/>
+      <c r="AJ41" s="84"/>
+      <c r="AK41" s="84"/>
+      <c r="AL41" s="84"/>
+      <c r="AM41" s="84"/>
+      <c r="AN41" s="84"/>
+      <c r="AO41" s="84"/>
+      <c r="AP41" s="84"/>
+      <c r="AQ41" s="84"/>
+      <c r="AR41" s="84"/>
+      <c r="AS41" s="84"/>
+      <c r="AT41" s="84"/>
+      <c r="AU41" s="84"/>
+      <c r="AV41" s="84"/>
+      <c r="AW41" s="84"/>
+      <c r="AX41" s="84"/>
+      <c r="AY41" s="84"/>
+      <c r="AZ41" s="84"/>
+      <c r="BA41" s="84"/>
+      <c r="BB41" s="84"/>
+      <c r="BC41" s="84"/>
+      <c r="BD41" s="84"/>
+      <c r="BE41" s="84"/>
+      <c r="BF41" s="84"/>
+      <c r="BG41" s="84"/>
+      <c r="BH41" s="84"/>
+      <c r="BI41" s="84"/>
+      <c r="BJ41" s="84"/>
+      <c r="BK41" s="84"/>
+      <c r="BL41" s="84"/>
+      <c r="BM41" s="84"/>
+      <c r="BN41" s="84"/>
+      <c r="BO41" s="84"/>
+      <c r="BP41" s="84"/>
+      <c r="BQ41" s="84"/>
+      <c r="BR41" s="84"/>
+      <c r="BS41" s="84"/>
+      <c r="BT41" s="84"/>
+      <c r="BU41" s="84"/>
+      <c r="BV41" s="84"/>
+      <c r="BW41" s="84"/>
+      <c r="BX41" s="84"/>
+      <c r="BY41" s="84"/>
+      <c r="BZ41" s="84"/>
+      <c r="CA41" s="84"/>
+      <c r="CB41" s="84"/>
+      <c r="CC41" s="84"/>
+      <c r="CD41" s="84"/>
+      <c r="CE41" s="84"/>
+      <c r="CF41" s="84"/>
+      <c r="CG41" s="84"/>
+      <c r="CH41" s="84"/>
+      <c r="CI41" s="85"/>
+    </row>
+    <row r="42" spans="1:87">
+      <c r="A42" s="84"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="84"/>
+      <c r="I42" s="84"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="84"/>
+      <c r="O42" s="84"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="84"/>
+      <c r="R42" s="84"/>
+      <c r="S42" s="84"/>
+      <c r="T42" s="84"/>
+      <c r="U42" s="84"/>
+      <c r="V42" s="84"/>
+      <c r="W42" s="84"/>
+      <c r="X42" s="84"/>
+      <c r="Y42" s="84"/>
+      <c r="Z42" s="84"/>
+      <c r="AA42" s="84"/>
+      <c r="AB42" s="84"/>
+      <c r="AC42" s="84"/>
+      <c r="AD42" s="84"/>
+      <c r="AE42" s="84"/>
+      <c r="AF42" s="84"/>
+      <c r="AG42" s="84"/>
+      <c r="AH42" s="84"/>
+      <c r="AI42" s="84"/>
+      <c r="AJ42" s="84"/>
+      <c r="AK42" s="84"/>
+      <c r="AL42" s="84"/>
+      <c r="AM42" s="84"/>
+      <c r="AN42" s="84"/>
+      <c r="AO42" s="84"/>
+      <c r="AP42" s="84"/>
+      <c r="AQ42" s="84"/>
+      <c r="AR42" s="84"/>
+      <c r="AS42" s="84"/>
+      <c r="AT42" s="84"/>
+      <c r="AU42" s="84"/>
+      <c r="AV42" s="84"/>
+      <c r="AW42" s="84"/>
+      <c r="AX42" s="84"/>
+      <c r="AY42" s="84"/>
+      <c r="AZ42" s="84"/>
+      <c r="BA42" s="84"/>
+      <c r="BB42" s="84"/>
+      <c r="BC42" s="84"/>
+      <c r="BD42" s="84"/>
+      <c r="BE42" s="84"/>
+      <c r="BF42" s="84"/>
+      <c r="BG42" s="84"/>
+      <c r="BH42" s="84"/>
+      <c r="BI42" s="84"/>
+      <c r="BJ42" s="84"/>
+      <c r="BK42" s="84"/>
+      <c r="BL42" s="84"/>
+      <c r="BM42" s="84"/>
+      <c r="BN42" s="84"/>
+      <c r="BO42" s="84"/>
+      <c r="BP42" s="84"/>
+      <c r="BQ42" s="84"/>
+      <c r="BR42" s="84"/>
+      <c r="BS42" s="84"/>
+      <c r="BT42" s="84"/>
+      <c r="BU42" s="84"/>
+      <c r="BV42" s="84"/>
+      <c r="BW42" s="84"/>
+      <c r="BX42" s="84"/>
+      <c r="BY42" s="84"/>
+      <c r="BZ42" s="84"/>
+      <c r="CA42" s="84"/>
+      <c r="CB42" s="84"/>
+      <c r="CC42" s="84"/>
+      <c r="CD42" s="84"/>
+      <c r="CE42" s="84"/>
+      <c r="CF42" s="84"/>
+      <c r="CG42" s="84"/>
+      <c r="CH42" s="84"/>
+      <c r="CI42" s="85"/>
+    </row>
+    <row r="43" spans="1:87">
+      <c r="A43" s="84"/>
+      <c r="B43" s="84"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+      <c r="O43" s="84"/>
+      <c r="P43" s="84"/>
+      <c r="Q43" s="84"/>
+      <c r="R43" s="84"/>
+      <c r="S43" s="84"/>
+      <c r="T43" s="84"/>
+      <c r="U43" s="84"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="84"/>
+      <c r="X43" s="84"/>
+      <c r="Y43" s="84"/>
+      <c r="Z43" s="84"/>
+      <c r="AA43" s="84"/>
+      <c r="AB43" s="84"/>
+      <c r="AC43" s="84"/>
+      <c r="AD43" s="84"/>
+      <c r="AE43" s="84"/>
+      <c r="AF43" s="84"/>
+      <c r="AG43" s="84"/>
+      <c r="AH43" s="84"/>
+      <c r="AI43" s="84"/>
+      <c r="AJ43" s="84"/>
+      <c r="AK43" s="84"/>
+      <c r="AL43" s="84"/>
+      <c r="AM43" s="84"/>
+      <c r="AN43" s="84"/>
+      <c r="AO43" s="84"/>
+      <c r="AP43" s="84"/>
+      <c r="AQ43" s="84"/>
+      <c r="AR43" s="84"/>
+      <c r="AS43" s="84"/>
+      <c r="AT43" s="84"/>
+      <c r="AU43" s="84"/>
+      <c r="AV43" s="84"/>
+      <c r="AW43" s="84"/>
+      <c r="AX43" s="84"/>
+      <c r="AY43" s="84"/>
+      <c r="AZ43" s="84"/>
+      <c r="BA43" s="84"/>
+      <c r="BB43" s="84"/>
+      <c r="BC43" s="84"/>
+      <c r="BD43" s="84"/>
+      <c r="BE43" s="84"/>
+      <c r="BF43" s="84"/>
+      <c r="BG43" s="84"/>
+      <c r="BH43" s="84"/>
+      <c r="BI43" s="84"/>
+      <c r="BJ43" s="84"/>
+      <c r="BK43" s="84"/>
+      <c r="BL43" s="84"/>
+      <c r="BM43" s="84"/>
+      <c r="BN43" s="84"/>
+      <c r="BO43" s="84"/>
+      <c r="BP43" s="84"/>
+      <c r="BQ43" s="84"/>
+      <c r="BR43" s="84"/>
+      <c r="BS43" s="84"/>
+      <c r="BT43" s="84"/>
+      <c r="BU43" s="84"/>
+      <c r="BV43" s="84"/>
+      <c r="BW43" s="84"/>
+      <c r="BX43" s="84"/>
+      <c r="BY43" s="84"/>
+      <c r="BZ43" s="84"/>
+      <c r="CA43" s="84"/>
+      <c r="CB43" s="84"/>
+      <c r="CC43" s="84"/>
+      <c r="CD43" s="84"/>
+      <c r="CE43" s="84"/>
+      <c r="CF43" s="84"/>
+      <c r="CG43" s="84"/>
+      <c r="CH43" s="84"/>
+      <c r="CI43" s="85"/>
+    </row>
+    <row r="44" spans="1:87">
+      <c r="A44" s="84"/>
+      <c r="B44" s="84"/>
+      <c r="C44" s="84"/>
+      <c r="D44" s="84"/>
+      <c r="E44" s="84"/>
+      <c r="F44" s="84"/>
+      <c r="G44" s="84"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="84"/>
+      <c r="J44" s="84"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="84"/>
+      <c r="M44" s="84"/>
+      <c r="N44" s="84"/>
+      <c r="O44" s="84"/>
+      <c r="P44" s="84"/>
+      <c r="Q44" s="84"/>
+      <c r="R44" s="84"/>
+      <c r="S44" s="84"/>
+      <c r="T44" s="84"/>
+      <c r="U44" s="84"/>
+      <c r="V44" s="84"/>
+      <c r="W44" s="84"/>
+      <c r="X44" s="84"/>
+      <c r="Y44" s="84"/>
+      <c r="Z44" s="84"/>
+      <c r="AA44" s="84"/>
+      <c r="AB44" s="84"/>
+      <c r="AC44" s="84"/>
+      <c r="AD44" s="84"/>
+      <c r="AE44" s="84"/>
+      <c r="AF44" s="84"/>
+      <c r="AG44" s="84"/>
+      <c r="AH44" s="84"/>
+      <c r="AI44" s="84"/>
+      <c r="AJ44" s="84"/>
+      <c r="AK44" s="84"/>
+      <c r="AL44" s="84"/>
+      <c r="AM44" s="84"/>
+      <c r="AN44" s="84"/>
+      <c r="AO44" s="84"/>
+      <c r="AP44" s="84"/>
+      <c r="AQ44" s="84"/>
+      <c r="AR44" s="84"/>
+      <c r="AS44" s="84"/>
+      <c r="AT44" s="84"/>
+      <c r="AU44" s="84"/>
+      <c r="AV44" s="84"/>
+      <c r="AW44" s="84"/>
+      <c r="AX44" s="84"/>
+      <c r="AY44" s="84"/>
+      <c r="AZ44" s="84"/>
+      <c r="BA44" s="84"/>
+      <c r="BB44" s="84"/>
+      <c r="BC44" s="84"/>
+      <c r="BD44" s="84"/>
+      <c r="BE44" s="84"/>
+      <c r="BF44" s="84"/>
+      <c r="BG44" s="84"/>
+      <c r="BH44" s="84"/>
+      <c r="BI44" s="84"/>
+      <c r="BJ44" s="84"/>
+      <c r="BK44" s="84"/>
+      <c r="BL44" s="84"/>
+      <c r="BM44" s="84"/>
+      <c r="BN44" s="84"/>
+      <c r="BO44" s="84"/>
+      <c r="BP44" s="84"/>
+      <c r="BQ44" s="84"/>
+      <c r="BR44" s="84"/>
+      <c r="BS44" s="84"/>
+      <c r="BT44" s="84"/>
+      <c r="BU44" s="84"/>
+      <c r="BV44" s="84"/>
+      <c r="BW44" s="84"/>
+      <c r="BX44" s="84"/>
+      <c r="BY44" s="84"/>
+      <c r="BZ44" s="84"/>
+      <c r="CA44" s="84"/>
+      <c r="CB44" s="84"/>
+      <c r="CC44" s="84"/>
+      <c r="CD44" s="84"/>
+      <c r="CE44" s="84"/>
+      <c r="CF44" s="84"/>
+      <c r="CG44" s="84"/>
+      <c r="CH44" s="84"/>
+      <c r="CI44" s="85"/>
+    </row>
+    <row r="45" spans="1:87">
+      <c r="A45" s="84"/>
+      <c r="B45" s="84"/>
+      <c r="C45" s="84"/>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="84"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="84"/>
+      <c r="J45" s="84"/>
+      <c r="K45" s="84"/>
+      <c r="L45" s="84"/>
+      <c r="M45" s="84"/>
+      <c r="N45" s="84"/>
+      <c r="O45" s="84"/>
+      <c r="P45" s="84"/>
+      <c r="Q45" s="84"/>
+      <c r="R45" s="84"/>
+      <c r="S45" s="84"/>
+      <c r="T45" s="84"/>
+      <c r="U45" s="84"/>
+      <c r="V45" s="84"/>
+      <c r="W45" s="84"/>
+      <c r="X45" s="84"/>
+      <c r="Y45" s="84"/>
+      <c r="Z45" s="84"/>
+      <c r="AA45" s="84"/>
+      <c r="AB45" s="84"/>
+      <c r="AC45" s="84"/>
+      <c r="AD45" s="84"/>
+      <c r="AE45" s="84"/>
+      <c r="AF45" s="84"/>
+      <c r="AG45" s="84"/>
+      <c r="AH45" s="84"/>
+      <c r="AI45" s="84"/>
+      <c r="AJ45" s="84"/>
+      <c r="AK45" s="84"/>
+      <c r="AL45" s="84"/>
+      <c r="AM45" s="84"/>
+      <c r="AN45" s="84"/>
+      <c r="AO45" s="84"/>
+      <c r="AP45" s="84"/>
+      <c r="AQ45" s="84"/>
+      <c r="AR45" s="84"/>
+      <c r="AS45" s="84"/>
+      <c r="AT45" s="84"/>
+      <c r="AU45" s="84"/>
+      <c r="AV45" s="84"/>
+      <c r="AW45" s="84"/>
+      <c r="AX45" s="84"/>
+      <c r="AY45" s="84"/>
+      <c r="AZ45" s="84"/>
+      <c r="BA45" s="84"/>
+      <c r="BB45" s="84"/>
+      <c r="BC45" s="84"/>
+      <c r="BD45" s="84"/>
+      <c r="BE45" s="84"/>
+      <c r="BF45" s="84"/>
+      <c r="BG45" s="84"/>
+      <c r="BH45" s="84"/>
+      <c r="BI45" s="84"/>
+      <c r="BJ45" s="84"/>
+      <c r="BK45" s="84"/>
+      <c r="BL45" s="84"/>
+      <c r="BM45" s="84"/>
+      <c r="BN45" s="84"/>
+      <c r="BO45" s="84"/>
+      <c r="BP45" s="84"/>
+      <c r="BQ45" s="84"/>
+      <c r="BR45" s="84"/>
+      <c r="BS45" s="84"/>
+      <c r="BT45" s="84"/>
+      <c r="BU45" s="84"/>
+      <c r="BV45" s="84"/>
+      <c r="BW45" s="84"/>
+      <c r="BX45" s="84"/>
+      <c r="BY45" s="84"/>
+      <c r="BZ45" s="84"/>
+      <c r="CA45" s="84"/>
+      <c r="CB45" s="84"/>
+      <c r="CC45" s="84"/>
+      <c r="CD45" s="84"/>
+      <c r="CE45" s="84"/>
+      <c r="CF45" s="84"/>
+      <c r="CG45" s="84"/>
+      <c r="CH45" s="84"/>
+      <c r="CI45" s="85"/>
+    </row>
+    <row r="46" spans="1:87">
+      <c r="A46" s="84"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="84"/>
+      <c r="D46" s="84"/>
+      <c r="E46" s="84"/>
+      <c r="F46" s="84"/>
+      <c r="G46" s="84"/>
+      <c r="H46" s="84"/>
+      <c r="I46" s="84"/>
+      <c r="J46" s="84"/>
+      <c r="K46" s="84"/>
+      <c r="L46" s="84"/>
+      <c r="M46" s="84"/>
+      <c r="N46" s="84"/>
+      <c r="O46" s="84"/>
+      <c r="P46" s="84"/>
+      <c r="Q46" s="84"/>
+      <c r="R46" s="84"/>
+      <c r="S46" s="84"/>
+      <c r="T46" s="84"/>
+      <c r="U46" s="84"/>
+      <c r="V46" s="84"/>
+      <c r="W46" s="84"/>
+      <c r="X46" s="84"/>
+      <c r="Y46" s="84"/>
+      <c r="Z46" s="84"/>
+      <c r="AA46" s="84"/>
+      <c r="AB46" s="84"/>
+      <c r="AC46" s="84"/>
+      <c r="AD46" s="84"/>
+      <c r="AE46" s="84"/>
+      <c r="AF46" s="84"/>
+      <c r="AG46" s="84"/>
+      <c r="AH46" s="84"/>
+      <c r="AI46" s="84"/>
+      <c r="AJ46" s="84"/>
+      <c r="AK46" s="84"/>
+      <c r="AL46" s="84"/>
+      <c r="AM46" s="84"/>
+      <c r="AN46" s="84"/>
+      <c r="AO46" s="84"/>
+      <c r="AP46" s="84"/>
+      <c r="AQ46" s="84"/>
+      <c r="AR46" s="84"/>
+      <c r="AS46" s="84"/>
+      <c r="AT46" s="84"/>
+      <c r="AU46" s="84"/>
+      <c r="AV46" s="84"/>
+      <c r="AW46" s="84"/>
+      <c r="AX46" s="84"/>
+      <c r="AY46" s="84"/>
+      <c r="AZ46" s="84"/>
+      <c r="BA46" s="84"/>
+      <c r="BB46" s="84"/>
+      <c r="BC46" s="84"/>
+      <c r="BD46" s="84"/>
+      <c r="BE46" s="84"/>
+      <c r="BF46" s="84"/>
+      <c r="BG46" s="84"/>
+      <c r="BH46" s="84"/>
+      <c r="BI46" s="84"/>
+      <c r="BJ46" s="84"/>
+      <c r="BK46" s="84"/>
+      <c r="BL46" s="84"/>
+      <c r="BM46" s="84"/>
+      <c r="BN46" s="84"/>
+      <c r="BO46" s="84"/>
+      <c r="BP46" s="84"/>
+      <c r="BQ46" s="84"/>
+      <c r="BR46" s="84"/>
+      <c r="BS46" s="84"/>
+      <c r="BT46" s="84"/>
+      <c r="BU46" s="84"/>
+      <c r="BV46" s="84"/>
+      <c r="BW46" s="84"/>
+      <c r="BX46" s="84"/>
+      <c r="BY46" s="84"/>
+      <c r="BZ46" s="84"/>
+      <c r="CA46" s="84"/>
+      <c r="CB46" s="84"/>
+      <c r="CC46" s="84"/>
+      <c r="CD46" s="84"/>
+      <c r="CE46" s="84"/>
+      <c r="CF46" s="84"/>
+      <c r="CG46" s="84"/>
+      <c r="CH46" s="84"/>
+      <c r="CI46" s="85"/>
+    </row>
+    <row r="47" spans="1:87">
+      <c r="A47" s="84"/>
+      <c r="B47" s="84"/>
+      <c r="C47" s="84"/>
+      <c r="D47" s="84"/>
+      <c r="E47" s="84"/>
+      <c r="F47" s="84"/>
+      <c r="G47" s="84"/>
+      <c r="H47" s="84"/>
+      <c r="I47" s="84"/>
+      <c r="J47" s="84"/>
+      <c r="K47" s="84"/>
+      <c r="L47" s="84"/>
+      <c r="M47" s="84"/>
+      <c r="N47" s="84"/>
+      <c r="O47" s="84"/>
+      <c r="P47" s="84"/>
+      <c r="Q47" s="84"/>
+      <c r="R47" s="84"/>
+      <c r="S47" s="84"/>
+      <c r="T47" s="84"/>
+      <c r="U47" s="84"/>
+      <c r="V47" s="84"/>
+      <c r="W47" s="84"/>
+      <c r="X47" s="84"/>
+      <c r="Y47" s="84"/>
+      <c r="Z47" s="84"/>
+      <c r="AA47" s="84"/>
+      <c r="AB47" s="84"/>
+      <c r="AC47" s="84"/>
+      <c r="AD47" s="84"/>
+      <c r="AE47" s="84"/>
+      <c r="AF47" s="84"/>
+      <c r="AG47" s="84"/>
+      <c r="AH47" s="84"/>
+      <c r="AI47" s="84"/>
+      <c r="AJ47" s="84"/>
+      <c r="AK47" s="84"/>
+      <c r="AL47" s="84"/>
+      <c r="AM47" s="84"/>
+      <c r="AN47" s="84"/>
+      <c r="AO47" s="84"/>
+      <c r="AP47" s="84"/>
+      <c r="AQ47" s="84"/>
+      <c r="AR47" s="84"/>
+      <c r="AS47" s="84"/>
+      <c r="AT47" s="84"/>
+      <c r="AU47" s="84"/>
+      <c r="AV47" s="84"/>
+      <c r="AW47" s="84"/>
+      <c r="AX47" s="84"/>
+      <c r="AY47" s="84"/>
+      <c r="AZ47" s="84"/>
+      <c r="BA47" s="84"/>
+      <c r="BB47" s="84"/>
+      <c r="BC47" s="84"/>
+      <c r="BD47" s="84"/>
+      <c r="BE47" s="84"/>
+      <c r="BF47" s="84"/>
+      <c r="BG47" s="84"/>
+      <c r="BH47" s="84"/>
+      <c r="BI47" s="84"/>
+      <c r="BJ47" s="84"/>
+      <c r="BK47" s="84"/>
+      <c r="BL47" s="84"/>
+      <c r="BM47" s="84"/>
+      <c r="BN47" s="84"/>
+      <c r="BO47" s="84"/>
+      <c r="BP47" s="84"/>
+      <c r="BQ47" s="84"/>
+      <c r="BR47" s="84"/>
+      <c r="BS47" s="84"/>
+      <c r="BT47" s="84"/>
+      <c r="BU47" s="84"/>
+      <c r="BV47" s="84"/>
+      <c r="BW47" s="84"/>
+      <c r="BX47" s="84"/>
+      <c r="BY47" s="84"/>
+      <c r="BZ47" s="84"/>
+      <c r="CA47" s="84"/>
+      <c r="CB47" s="84"/>
+      <c r="CC47" s="84"/>
+      <c r="CD47" s="84"/>
+      <c r="CE47" s="84"/>
+      <c r="CF47" s="84"/>
+      <c r="CG47" s="84"/>
+      <c r="CH47" s="84"/>
+      <c r="CI47" s="85"/>
+    </row>
+    <row r="48" spans="1:87">
+      <c r="A48" s="84"/>
+      <c r="B48" s="84"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="84"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="84"/>
+      <c r="I48" s="84"/>
+      <c r="J48" s="84"/>
+      <c r="K48" s="84"/>
+      <c r="L48" s="84"/>
+      <c r="M48" s="84"/>
+      <c r="N48" s="84"/>
+      <c r="O48" s="84"/>
+      <c r="P48" s="84"/>
+      <c r="Q48" s="84"/>
+      <c r="R48" s="84"/>
+      <c r="S48" s="84"/>
+      <c r="T48" s="84"/>
+      <c r="U48" s="84"/>
+      <c r="V48" s="84"/>
+      <c r="W48" s="84"/>
+      <c r="X48" s="84"/>
+      <c r="Y48" s="84"/>
+      <c r="Z48" s="84"/>
+      <c r="AA48" s="84"/>
+      <c r="AB48" s="84"/>
+      <c r="AC48" s="84"/>
+      <c r="AD48" s="84"/>
+      <c r="AE48" s="84"/>
+      <c r="AF48" s="84"/>
+      <c r="AG48" s="84"/>
+      <c r="AH48" s="84"/>
+      <c r="AI48" s="84"/>
+      <c r="AJ48" s="84"/>
+      <c r="AK48" s="84"/>
+      <c r="AL48" s="84"/>
+      <c r="AM48" s="84"/>
+      <c r="AN48" s="84"/>
+      <c r="AO48" s="84"/>
+      <c r="AP48" s="84"/>
+      <c r="AQ48" s="84"/>
+      <c r="AR48" s="84"/>
+      <c r="AS48" s="84"/>
+      <c r="AT48" s="84"/>
+      <c r="AU48" s="84"/>
+      <c r="AV48" s="84"/>
+      <c r="AW48" s="84"/>
+      <c r="AX48" s="84"/>
+      <c r="AY48" s="84"/>
+      <c r="AZ48" s="84"/>
+      <c r="BA48" s="84"/>
+      <c r="BB48" s="84"/>
+      <c r="BC48" s="84"/>
+      <c r="BD48" s="84"/>
+      <c r="BE48" s="84"/>
+      <c r="BF48" s="84"/>
+      <c r="BG48" s="84"/>
+      <c r="BH48" s="84"/>
+      <c r="BI48" s="84"/>
+      <c r="BJ48" s="84"/>
+      <c r="BK48" s="84"/>
+      <c r="BL48" s="84"/>
+      <c r="BM48" s="84"/>
+      <c r="BN48" s="84"/>
+      <c r="BO48" s="84"/>
+      <c r="BP48" s="84"/>
+      <c r="BQ48" s="84"/>
+      <c r="BR48" s="84"/>
+      <c r="BS48" s="84"/>
+      <c r="BT48" s="84"/>
+      <c r="BU48" s="84"/>
+      <c r="BV48" s="84"/>
+      <c r="BW48" s="84"/>
+      <c r="BX48" s="84"/>
+      <c r="BY48" s="84"/>
+      <c r="BZ48" s="84"/>
+      <c r="CA48" s="84"/>
+      <c r="CB48" s="84"/>
+      <c r="CC48" s="84"/>
+      <c r="CD48" s="84"/>
+      <c r="CE48" s="84"/>
+      <c r="CF48" s="84"/>
+      <c r="CG48" s="84"/>
+      <c r="CH48" s="84"/>
+      <c r="CI48" s="85"/>
+    </row>
+    <row r="49" spans="1:87">
+      <c r="A49" s="84"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="84"/>
+      <c r="E49" s="84"/>
+      <c r="F49" s="84"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="84"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="84"/>
+      <c r="K49" s="84"/>
+      <c r="L49" s="84"/>
+      <c r="M49" s="84"/>
+      <c r="N49" s="84"/>
+      <c r="O49" s="84"/>
+      <c r="P49" s="84"/>
+      <c r="Q49" s="84"/>
+      <c r="R49" s="84"/>
+      <c r="S49" s="84"/>
+      <c r="T49" s="84"/>
+      <c r="U49" s="84"/>
+      <c r="V49" s="84"/>
+      <c r="W49" s="84"/>
+      <c r="X49" s="84"/>
+      <c r="Y49" s="84"/>
+      <c r="Z49" s="84"/>
+      <c r="AA49" s="84"/>
+      <c r="AB49" s="84"/>
+      <c r="AC49" s="84"/>
+      <c r="AD49" s="84"/>
+      <c r="AE49" s="84"/>
+      <c r="AF49" s="84"/>
+      <c r="AG49" s="84"/>
+      <c r="AH49" s="84"/>
+      <c r="AI49" s="84"/>
+      <c r="AJ49" s="84"/>
+      <c r="AK49" s="84"/>
+      <c r="AL49" s="84"/>
+      <c r="AM49" s="84"/>
+      <c r="AN49" s="84"/>
+      <c r="AO49" s="84"/>
+      <c r="AP49" s="84"/>
+      <c r="AQ49" s="84"/>
+      <c r="AR49" s="84"/>
+      <c r="AS49" s="84"/>
+      <c r="AT49" s="84"/>
+      <c r="AU49" s="84"/>
+      <c r="AV49" s="84"/>
+      <c r="AW49" s="84"/>
+      <c r="AX49" s="84"/>
+      <c r="AY49" s="84"/>
+      <c r="AZ49" s="84"/>
+      <c r="BA49" s="84"/>
+      <c r="BB49" s="84"/>
+      <c r="BC49" s="84"/>
+      <c r="BD49" s="84"/>
+      <c r="BE49" s="84"/>
+      <c r="BF49" s="84"/>
+      <c r="BG49" s="84"/>
+      <c r="BH49" s="84"/>
+      <c r="BI49" s="84"/>
+      <c r="BJ49" s="84"/>
+      <c r="BK49" s="84"/>
+      <c r="BL49" s="84"/>
+      <c r="BM49" s="84"/>
+      <c r="BN49" s="84"/>
+      <c r="BO49" s="84"/>
+      <c r="BP49" s="84"/>
+      <c r="BQ49" s="84"/>
+      <c r="BR49" s="84"/>
+      <c r="BS49" s="84"/>
+      <c r="BT49" s="84"/>
+      <c r="BU49" s="84"/>
+      <c r="BV49" s="84"/>
+      <c r="BW49" s="84"/>
+      <c r="BX49" s="84"/>
+      <c r="BY49" s="84"/>
+      <c r="BZ49" s="84"/>
+      <c r="CA49" s="84"/>
+      <c r="CB49" s="84"/>
+      <c r="CC49" s="84"/>
+      <c r="CD49" s="84"/>
+      <c r="CE49" s="84"/>
+      <c r="CF49" s="84"/>
+      <c r="CG49" s="84"/>
+      <c r="CH49" s="84"/>
+      <c r="CI49" s="85"/>
+    </row>
+    <row r="50" spans="1:87">
+      <c r="A50" s="84"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="84"/>
+      <c r="D50" s="84"/>
+      <c r="E50" s="84"/>
+      <c r="F50" s="84"/>
+      <c r="G50" s="84"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="84"/>
+      <c r="J50" s="84"/>
+      <c r="K50" s="84"/>
+      <c r="L50" s="84"/>
+      <c r="M50" s="84"/>
+      <c r="N50" s="84"/>
+      <c r="O50" s="84"/>
+      <c r="P50" s="84"/>
+      <c r="Q50" s="84"/>
+      <c r="R50" s="84"/>
+      <c r="S50" s="84"/>
+      <c r="T50" s="84"/>
+      <c r="U50" s="84"/>
+      <c r="V50" s="84"/>
+      <c r="W50" s="84"/>
+      <c r="X50" s="84"/>
+      <c r="Y50" s="84"/>
+      <c r="Z50" s="84"/>
+      <c r="AA50" s="84"/>
+      <c r="AB50" s="84"/>
+      <c r="AC50" s="84"/>
+      <c r="AD50" s="84"/>
+      <c r="AE50" s="84"/>
+      <c r="AF50" s="84"/>
+      <c r="AG50" s="84"/>
+      <c r="AH50" s="84"/>
+      <c r="AI50" s="84"/>
+      <c r="AJ50" s="84"/>
+      <c r="AK50" s="84"/>
+      <c r="AL50" s="84"/>
+      <c r="AM50" s="84"/>
+      <c r="AN50" s="84"/>
+      <c r="AO50" s="84"/>
+      <c r="AP50" s="84"/>
+      <c r="AQ50" s="84"/>
+      <c r="AR50" s="84"/>
+      <c r="AS50" s="84"/>
+      <c r="AT50" s="84"/>
+      <c r="AU50" s="84"/>
+      <c r="AV50" s="84"/>
+      <c r="AW50" s="84"/>
+      <c r="AX50" s="84"/>
+      <c r="AY50" s="84"/>
+      <c r="AZ50" s="84"/>
+      <c r="BA50" s="84"/>
+      <c r="BB50" s="84"/>
+      <c r="BC50" s="84"/>
+      <c r="BD50" s="84"/>
+      <c r="BE50" s="84"/>
+      <c r="BF50" s="84"/>
+      <c r="BG50" s="84"/>
+      <c r="BH50" s="84"/>
+      <c r="BI50" s="84"/>
+      <c r="BJ50" s="84"/>
+      <c r="BK50" s="84"/>
+      <c r="BL50" s="84"/>
+      <c r="BM50" s="84"/>
+      <c r="BN50" s="84"/>
+      <c r="BO50" s="84"/>
+      <c r="BP50" s="84"/>
+      <c r="BQ50" s="84"/>
+      <c r="BR50" s="84"/>
+      <c r="BS50" s="84"/>
+      <c r="BT50" s="84"/>
+      <c r="BU50" s="84"/>
+      <c r="BV50" s="84"/>
+      <c r="BW50" s="84"/>
+      <c r="BX50" s="84"/>
+      <c r="BY50" s="84"/>
+      <c r="BZ50" s="84"/>
+      <c r="CA50" s="84"/>
+      <c r="CB50" s="84"/>
+      <c r="CC50" s="84"/>
+      <c r="CD50" s="84"/>
+      <c r="CE50" s="84"/>
+      <c r="CF50" s="84"/>
+      <c r="CG50" s="84"/>
+      <c r="CH50" s="84"/>
+      <c r="CI50" s="85"/>
+    </row>
+    <row r="51" spans="1:87">
+      <c r="A51" s="84"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="84"/>
+      <c r="D51" s="84"/>
+      <c r="E51" s="84"/>
+      <c r="F51" s="84"/>
+      <c r="G51" s="84"/>
+      <c r="H51" s="84"/>
+      <c r="I51" s="84"/>
+      <c r="J51" s="84"/>
+      <c r="K51" s="84"/>
+      <c r="L51" s="84"/>
+      <c r="M51" s="84"/>
+      <c r="N51" s="84"/>
+      <c r="O51" s="84"/>
+      <c r="P51" s="84"/>
+      <c r="Q51" s="84"/>
+      <c r="R51" s="84"/>
+      <c r="S51" s="84"/>
+      <c r="T51" s="84"/>
+      <c r="U51" s="84"/>
+      <c r="V51" s="84"/>
+      <c r="W51" s="84"/>
+      <c r="X51" s="84"/>
+      <c r="Y51" s="84"/>
+      <c r="Z51" s="84"/>
+      <c r="AA51" s="84"/>
+      <c r="AB51" s="84"/>
+      <c r="AC51" s="84"/>
+      <c r="AD51" s="84"/>
+      <c r="AE51" s="84"/>
+      <c r="AF51" s="84"/>
+      <c r="AG51" s="84"/>
+      <c r="AH51" s="84"/>
+      <c r="AI51" s="84"/>
+      <c r="AJ51" s="84"/>
+      <c r="AK51" s="84"/>
+      <c r="AL51" s="84"/>
+      <c r="AM51" s="84"/>
+      <c r="AN51" s="84"/>
+      <c r="AO51" s="84"/>
+      <c r="AP51" s="84"/>
+      <c r="AQ51" s="84"/>
+      <c r="AR51" s="84"/>
+      <c r="AS51" s="84"/>
+      <c r="AT51" s="84"/>
+      <c r="AU51" s="84"/>
+      <c r="AV51" s="84"/>
+      <c r="AW51" s="84"/>
+      <c r="AX51" s="84"/>
+      <c r="AY51" s="84"/>
+      <c r="AZ51" s="84"/>
+      <c r="BA51" s="84"/>
+      <c r="BB51" s="84"/>
+      <c r="BC51" s="84"/>
+      <c r="BD51" s="84"/>
+      <c r="BE51" s="84"/>
+      <c r="BF51" s="84"/>
+      <c r="BG51" s="84"/>
+      <c r="BH51" s="84"/>
+      <c r="BI51" s="84"/>
+      <c r="BJ51" s="84"/>
+      <c r="BK51" s="84"/>
+      <c r="BL51" s="84"/>
+      <c r="BM51" s="84"/>
+      <c r="BN51" s="84"/>
+      <c r="BO51" s="84"/>
+      <c r="BP51" s="84"/>
+      <c r="BQ51" s="84"/>
+      <c r="BR51" s="84"/>
+      <c r="BS51" s="84"/>
+      <c r="BT51" s="84"/>
+      <c r="BU51" s="84"/>
+      <c r="BV51" s="84"/>
+      <c r="BW51" s="84"/>
+      <c r="BX51" s="84"/>
+      <c r="BY51" s="84"/>
+      <c r="BZ51" s="84"/>
+      <c r="CA51" s="84"/>
+      <c r="CB51" s="84"/>
+      <c r="CC51" s="84"/>
+      <c r="CD51" s="84"/>
+      <c r="CE51" s="84"/>
+      <c r="CF51" s="84"/>
+      <c r="CG51" s="84"/>
+      <c r="CH51" s="84"/>
+      <c r="CI51" s="85"/>
+    </row>
+    <row r="52" spans="1:87">
+      <c r="A52" s="84"/>
+      <c r="B52" s="84"/>
+      <c r="C52" s="84"/>
+      <c r="D52" s="84"/>
+      <c r="E52" s="84"/>
+      <c r="F52" s="84"/>
+      <c r="G52" s="84"/>
+      <c r="H52" s="84"/>
+      <c r="I52" s="84"/>
+      <c r="J52" s="84"/>
+      <c r="K52" s="84"/>
+      <c r="L52" s="84"/>
+      <c r="M52" s="84"/>
+      <c r="N52" s="84"/>
+      <c r="O52" s="84"/>
+      <c r="P52" s="84"/>
+      <c r="Q52" s="84"/>
+      <c r="R52" s="84"/>
+      <c r="S52" s="84"/>
+      <c r="T52" s="84"/>
+      <c r="U52" s="84"/>
+      <c r="V52" s="84"/>
+      <c r="W52" s="84"/>
+      <c r="X52" s="84"/>
+      <c r="Y52" s="84"/>
+      <c r="Z52" s="84"/>
+      <c r="AA52" s="84"/>
+      <c r="AB52" s="84"/>
+      <c r="AC52" s="84"/>
+      <c r="AD52" s="84"/>
+      <c r="AE52" s="84"/>
+      <c r="AF52" s="84"/>
+      <c r="AG52" s="84"/>
+      <c r="AH52" s="84"/>
+      <c r="AI52" s="84"/>
+      <c r="AJ52" s="84"/>
+      <c r="AK52" s="84"/>
+      <c r="AL52" s="84"/>
+      <c r="AM52" s="84"/>
+      <c r="AN52" s="84"/>
+      <c r="AO52" s="84"/>
+      <c r="AP52" s="84"/>
+      <c r="AQ52" s="84"/>
+      <c r="AR52" s="84"/>
+      <c r="AS52" s="84"/>
+      <c r="AT52" s="84"/>
+      <c r="AU52" s="84"/>
+      <c r="AV52" s="84"/>
+      <c r="AW52" s="84"/>
+      <c r="AX52" s="84"/>
+      <c r="AY52" s="84"/>
+      <c r="AZ52" s="84"/>
+      <c r="BA52" s="84"/>
+      <c r="BB52" s="84"/>
+      <c r="BC52" s="84"/>
+      <c r="BD52" s="84"/>
+      <c r="BE52" s="84"/>
+      <c r="BF52" s="84"/>
+      <c r="BG52" s="84"/>
+      <c r="BH52" s="84"/>
+      <c r="BI52" s="84"/>
+      <c r="BJ52" s="84"/>
+      <c r="BK52" s="84"/>
+      <c r="BL52" s="84"/>
+      <c r="BM52" s="84"/>
+      <c r="BN52" s="84"/>
+      <c r="BO52" s="84"/>
+      <c r="BP52" s="84"/>
+      <c r="BQ52" s="84"/>
+      <c r="BR52" s="84"/>
+      <c r="BS52" s="84"/>
+      <c r="BT52" s="84"/>
+      <c r="BU52" s="84"/>
+      <c r="BV52" s="84"/>
+      <c r="BW52" s="84"/>
+      <c r="BX52" s="84"/>
+      <c r="BY52" s="84"/>
+      <c r="BZ52" s="84"/>
+      <c r="CA52" s="84"/>
+      <c r="CB52" s="84"/>
+      <c r="CC52" s="84"/>
+      <c r="CD52" s="84"/>
+      <c r="CE52" s="84"/>
+      <c r="CF52" s="84"/>
+      <c r="CG52" s="84"/>
+      <c r="CH52" s="84"/>
+      <c r="CI52" s="85"/>
+    </row>
+    <row r="53" spans="1:87">
+      <c r="A53" s="84"/>
+      <c r="B53" s="84"/>
+      <c r="C53" s="84"/>
+      <c r="D53" s="84"/>
+      <c r="E53" s="84"/>
+      <c r="F53" s="84"/>
+      <c r="G53" s="84"/>
+      <c r="H53" s="84"/>
+      <c r="I53" s="84"/>
+      <c r="J53" s="84"/>
+      <c r="K53" s="84"/>
+      <c r="L53" s="84"/>
+      <c r="M53" s="84"/>
+      <c r="N53" s="84"/>
+      <c r="O53" s="84"/>
+      <c r="P53" s="84"/>
+      <c r="Q53" s="84"/>
+      <c r="R53" s="84"/>
+      <c r="S53" s="84"/>
+      <c r="T53" s="84"/>
+      <c r="U53" s="84"/>
+      <c r="V53" s="84"/>
+      <c r="W53" s="84"/>
+      <c r="X53" s="84"/>
+      <c r="Y53" s="84"/>
+      <c r="Z53" s="84"/>
+      <c r="AA53" s="84"/>
+      <c r="AB53" s="84"/>
+      <c r="AC53" s="84"/>
+      <c r="AD53" s="84"/>
+      <c r="AE53" s="84"/>
+      <c r="AF53" s="84"/>
+      <c r="AG53" s="84"/>
+      <c r="AH53" s="84"/>
+      <c r="AI53" s="84"/>
+      <c r="AJ53" s="84"/>
+      <c r="AK53" s="84"/>
+      <c r="AL53" s="84"/>
+      <c r="AM53" s="84"/>
+      <c r="AN53" s="84"/>
+      <c r="AO53" s="84"/>
+      <c r="AP53" s="84"/>
+      <c r="AQ53" s="84"/>
+      <c r="AR53" s="84"/>
+      <c r="AS53" s="84"/>
+      <c r="AT53" s="84"/>
+      <c r="AU53" s="84"/>
+      <c r="AV53" s="84"/>
+      <c r="AW53" s="84"/>
+      <c r="AX53" s="84"/>
+      <c r="AY53" s="84"/>
+      <c r="AZ53" s="84"/>
+      <c r="BA53" s="84"/>
+      <c r="BB53" s="84"/>
+      <c r="BC53" s="84"/>
+      <c r="BD53" s="84"/>
+      <c r="BE53" s="84"/>
+      <c r="BF53" s="84"/>
+      <c r="BG53" s="84"/>
+      <c r="BH53" s="84"/>
+      <c r="BI53" s="84"/>
+      <c r="BJ53" s="84"/>
+      <c r="BK53" s="84"/>
+      <c r="BL53" s="84"/>
+      <c r="BM53" s="84"/>
+      <c r="BN53" s="84"/>
+      <c r="BO53" s="84"/>
+      <c r="BP53" s="84"/>
+      <c r="BQ53" s="84"/>
+      <c r="BR53" s="84"/>
+      <c r="BS53" s="84"/>
+      <c r="BT53" s="84"/>
+      <c r="BU53" s="84"/>
+      <c r="BV53" s="84"/>
+      <c r="BW53" s="84"/>
+      <c r="BX53" s="84"/>
+      <c r="BY53" s="84"/>
+      <c r="BZ53" s="84"/>
+      <c r="CA53" s="84"/>
+      <c r="CB53" s="84"/>
+      <c r="CC53" s="84"/>
+      <c r="CD53" s="84"/>
+      <c r="CE53" s="84"/>
+      <c r="CF53" s="84"/>
+      <c r="CG53" s="84"/>
+      <c r="CH53" s="84"/>
+      <c r="CI53" s="85"/>
+    </row>
+    <row r="54" spans="1:87">
+      <c r="A54" s="84"/>
+      <c r="B54" s="84"/>
+      <c r="C54" s="84"/>
+      <c r="D54" s="84"/>
+      <c r="E54" s="84"/>
+      <c r="F54" s="84"/>
+      <c r="G54" s="84"/>
+      <c r="H54" s="84"/>
+      <c r="I54" s="84"/>
+      <c r="J54" s="84"/>
+      <c r="K54" s="84"/>
+      <c r="L54" s="84"/>
+      <c r="M54" s="84"/>
+      <c r="N54" s="84"/>
+      <c r="O54" s="84"/>
+      <c r="P54" s="84"/>
+      <c r="Q54" s="84"/>
+      <c r="R54" s="84"/>
+      <c r="S54" s="84"/>
+      <c r="T54" s="84"/>
+      <c r="U54" s="84"/>
+      <c r="V54" s="84"/>
+      <c r="W54" s="84"/>
+      <c r="X54" s="84"/>
+      <c r="Y54" s="84"/>
+      <c r="Z54" s="84"/>
+      <c r="AA54" s="84"/>
+      <c r="AB54" s="84"/>
+      <c r="AC54" s="84"/>
+      <c r="AD54" s="84"/>
+      <c r="AE54" s="84"/>
+      <c r="AF54" s="84"/>
+      <c r="AG54" s="84"/>
+      <c r="AH54" s="84"/>
+      <c r="AI54" s="84"/>
+      <c r="AJ54" s="84"/>
+      <c r="AK54" s="84"/>
+      <c r="AL54" s="84"/>
+      <c r="AM54" s="84"/>
+      <c r="AN54" s="84"/>
+      <c r="AO54" s="84"/>
+      <c r="AP54" s="84"/>
+      <c r="AQ54" s="84"/>
+      <c r="AR54" s="84"/>
+      <c r="AS54" s="84"/>
+      <c r="AT54" s="84"/>
+      <c r="AU54" s="84"/>
+      <c r="AV54" s="84"/>
+      <c r="AW54" s="84"/>
+      <c r="AX54" s="84"/>
+      <c r="AY54" s="84"/>
+      <c r="AZ54" s="84"/>
+      <c r="BA54" s="84"/>
+      <c r="BB54" s="84"/>
+      <c r="BC54" s="84"/>
+      <c r="BD54" s="84"/>
+      <c r="BE54" s="84"/>
+      <c r="BF54" s="84"/>
+      <c r="BG54" s="84"/>
+      <c r="BH54" s="84"/>
+      <c r="BI54" s="84"/>
+      <c r="BJ54" s="84"/>
+      <c r="BK54" s="84"/>
+      <c r="BL54" s="84"/>
+      <c r="BM54" s="84"/>
+      <c r="BN54" s="84"/>
+      <c r="BO54" s="84"/>
+      <c r="BP54" s="84"/>
+      <c r="BQ54" s="84"/>
+      <c r="BR54" s="84"/>
+      <c r="BS54" s="84"/>
+      <c r="BT54" s="84"/>
+      <c r="BU54" s="84"/>
+      <c r="BV54" s="84"/>
+      <c r="BW54" s="84"/>
+      <c r="BX54" s="84"/>
+      <c r="BY54" s="84"/>
+      <c r="BZ54" s="84"/>
+      <c r="CA54" s="84"/>
+      <c r="CB54" s="84"/>
+      <c r="CC54" s="84"/>
+      <c r="CD54" s="84"/>
+      <c r="CE54" s="84"/>
+      <c r="CF54" s="84"/>
+      <c r="CG54" s="84"/>
+      <c r="CH54" s="84"/>
+      <c r="CI54" s="85"/>
+    </row>
+    <row r="55" spans="1:87" ht="19.5" thickBot="1">
+      <c r="A55" s="84"/>
+      <c r="B55" s="84"/>
+      <c r="C55" s="84"/>
+      <c r="D55" s="84"/>
+      <c r="E55" s="84"/>
+      <c r="F55" s="84"/>
+      <c r="G55" s="84"/>
+      <c r="H55" s="84"/>
+      <c r="I55" s="84"/>
+      <c r="J55" s="84"/>
+      <c r="K55" s="84"/>
+      <c r="L55" s="84"/>
+      <c r="M55" s="84"/>
+      <c r="N55" s="84"/>
+      <c r="O55" s="84"/>
+      <c r="P55" s="84"/>
+      <c r="Q55" s="84"/>
+      <c r="R55" s="84"/>
+      <c r="S55" s="84"/>
+      <c r="T55" s="84"/>
+      <c r="U55" s="84"/>
+      <c r="V55" s="84"/>
+      <c r="W55" s="84"/>
+      <c r="X55" s="84"/>
+      <c r="Y55" s="84"/>
+      <c r="Z55" s="84"/>
+      <c r="AA55" s="84"/>
+      <c r="AB55" s="84"/>
+      <c r="AC55" s="84"/>
+      <c r="AD55" s="84"/>
+      <c r="AE55" s="84"/>
+      <c r="AF55" s="84"/>
+      <c r="AG55" s="84"/>
+      <c r="AH55" s="84"/>
+      <c r="AI55" s="84"/>
+      <c r="AJ55" s="84"/>
+      <c r="AK55" s="84"/>
+      <c r="AL55" s="84"/>
+      <c r="AM55" s="84"/>
+      <c r="AN55" s="84"/>
+      <c r="AO55" s="84"/>
+      <c r="AP55" s="84"/>
+      <c r="AQ55" s="84"/>
+      <c r="AR55" s="84"/>
+      <c r="AS55" s="84"/>
+      <c r="AT55" s="84"/>
+      <c r="AU55" s="84"/>
+      <c r="AV55" s="84"/>
+      <c r="AW55" s="84"/>
+      <c r="AX55" s="84"/>
+      <c r="AY55" s="84"/>
+      <c r="AZ55" s="84"/>
+      <c r="BA55" s="84"/>
+      <c r="BB55" s="84"/>
+      <c r="BC55" s="84"/>
+      <c r="BD55" s="84"/>
+      <c r="BE55" s="84"/>
+      <c r="BF55" s="84"/>
+      <c r="BG55" s="84"/>
+      <c r="BH55" s="84"/>
+      <c r="BI55" s="84"/>
+      <c r="BJ55" s="84"/>
+      <c r="BK55" s="84"/>
+      <c r="BL55" s="84"/>
+      <c r="BM55" s="84"/>
+      <c r="BN55" s="84"/>
+      <c r="BO55" s="84"/>
+      <c r="BP55" s="84"/>
+      <c r="BQ55" s="84"/>
+      <c r="BR55" s="84"/>
+      <c r="BS55" s="84"/>
+      <c r="BT55" s="84"/>
+      <c r="BU55" s="84"/>
+      <c r="BV55" s="84"/>
+      <c r="BW55" s="84"/>
+      <c r="BX55" s="84"/>
+      <c r="BY55" s="84"/>
+      <c r="BZ55" s="84"/>
+      <c r="CA55" s="84"/>
+      <c r="CB55" s="84"/>
+      <c r="CC55" s="84"/>
+      <c r="CD55" s="84"/>
+      <c r="CE55" s="84"/>
+      <c r="CF55" s="84"/>
+      <c r="CG55" s="84"/>
+      <c r="CH55" s="84"/>
+      <c r="CI55" s="85"/>
+    </row>
+    <row r="56" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A56" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27">
+      <c r="B56" s="26"/>
+      <c r="C56" s="27">
         <v>2</v>
       </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="29" t="s">
+      <c r="D56" s="28"/>
+      <c r="E56" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="30"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="32" t="s">
+      <c r="F56" s="30"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33"/>
-      <c r="W34" s="33"/>
-      <c r="X34" s="33"/>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="33"/>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
-      <c r="AD34" s="33"/>
-      <c r="AE34" s="33"/>
-      <c r="AF34" s="33"/>
-      <c r="AG34" s="33"/>
-      <c r="AH34" s="33"/>
-      <c r="AI34" s="33"/>
-      <c r="AJ34" s="33"/>
-      <c r="AK34" s="33"/>
-      <c r="AL34" s="33"/>
-      <c r="AM34" s="33"/>
-      <c r="AN34" s="33"/>
-      <c r="AO34" s="33"/>
-      <c r="AP34" s="33"/>
-      <c r="AQ34" s="33"/>
-      <c r="AR34" s="33"/>
-      <c r="AS34" s="33"/>
-      <c r="AT34" s="33"/>
-      <c r="AU34" s="33"/>
-      <c r="AV34" s="33"/>
-      <c r="AW34" s="33"/>
-      <c r="AX34" s="33"/>
-      <c r="AY34" s="33"/>
-      <c r="AZ34" s="33"/>
-      <c r="BA34" s="33"/>
-      <c r="BB34" s="33"/>
-      <c r="BC34" s="33"/>
-      <c r="BD34" s="33"/>
-      <c r="BE34" s="33"/>
-      <c r="BF34" s="33"/>
-      <c r="BG34" s="33"/>
-      <c r="BH34" s="33"/>
-      <c r="BI34" s="33"/>
-      <c r="BJ34" s="33"/>
-      <c r="BK34" s="33"/>
-      <c r="BL34" s="33"/>
-      <c r="BM34" s="33"/>
-      <c r="BN34" s="33"/>
-      <c r="BO34" s="33"/>
-      <c r="BP34" s="33"/>
-      <c r="BQ34" s="33"/>
-      <c r="BR34" s="33"/>
-      <c r="BS34" s="33"/>
-      <c r="BT34" s="33"/>
-      <c r="BU34" s="33"/>
-      <c r="BV34" s="33"/>
-      <c r="BW34" s="33"/>
-      <c r="BX34" s="33"/>
-      <c r="BY34" s="33"/>
-      <c r="BZ34" s="33"/>
-      <c r="CA34" s="33"/>
-      <c r="CB34" s="33"/>
-      <c r="CC34" s="33"/>
-      <c r="CD34" s="33"/>
-      <c r="CE34" s="33"/>
-      <c r="CF34" s="33"/>
-      <c r="CG34" s="33"/>
-      <c r="CH34" s="33"/>
-      <c r="CI34" s="34"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
+      <c r="K56" s="33"/>
+      <c r="L56" s="33"/>
+      <c r="M56" s="33"/>
+      <c r="N56" s="33"/>
+      <c r="O56" s="33"/>
+      <c r="P56" s="33"/>
+      <c r="Q56" s="33"/>
+      <c r="R56" s="33"/>
+      <c r="S56" s="33"/>
+      <c r="T56" s="33"/>
+      <c r="U56" s="33"/>
+      <c r="V56" s="33"/>
+      <c r="W56" s="33"/>
+      <c r="X56" s="33"/>
+      <c r="Y56" s="33"/>
+      <c r="Z56" s="33"/>
+      <c r="AA56" s="33"/>
+      <c r="AB56" s="33"/>
+      <c r="AC56" s="33"/>
+      <c r="AD56" s="33"/>
+      <c r="AE56" s="33"/>
+      <c r="AF56" s="33"/>
+      <c r="AG56" s="33"/>
+      <c r="AH56" s="33"/>
+      <c r="AI56" s="33"/>
+      <c r="AJ56" s="33"/>
+      <c r="AK56" s="33"/>
+      <c r="AL56" s="33"/>
+      <c r="AM56" s="33"/>
+      <c r="AN56" s="33"/>
+      <c r="AO56" s="33"/>
+      <c r="AP56" s="33"/>
+      <c r="AQ56" s="33"/>
+      <c r="AR56" s="33"/>
+      <c r="AS56" s="33"/>
+      <c r="AT56" s="33"/>
+      <c r="AU56" s="33"/>
+      <c r="AV56" s="33"/>
+      <c r="AW56" s="33"/>
+      <c r="AX56" s="33"/>
+      <c r="AY56" s="33"/>
+      <c r="AZ56" s="33"/>
+      <c r="BA56" s="33"/>
+      <c r="BB56" s="33"/>
+      <c r="BC56" s="33"/>
+      <c r="BD56" s="33"/>
+      <c r="BE56" s="33"/>
+      <c r="BF56" s="33"/>
+      <c r="BG56" s="33"/>
+      <c r="BH56" s="33"/>
+      <c r="BI56" s="33"/>
+      <c r="BJ56" s="33"/>
+      <c r="BK56" s="33"/>
+      <c r="BL56" s="33"/>
+      <c r="BM56" s="33"/>
+      <c r="BN56" s="33"/>
+      <c r="BO56" s="33"/>
+      <c r="BP56" s="33"/>
+      <c r="BQ56" s="33"/>
+      <c r="BR56" s="33"/>
+      <c r="BS56" s="33"/>
+      <c r="BT56" s="33"/>
+      <c r="BU56" s="33"/>
+      <c r="BV56" s="33"/>
+      <c r="BW56" s="33"/>
+      <c r="BX56" s="33"/>
+      <c r="BY56" s="33"/>
+      <c r="BZ56" s="33"/>
+      <c r="CA56" s="33"/>
+      <c r="CB56" s="33"/>
+      <c r="CC56" s="33"/>
+      <c r="CD56" s="33"/>
+      <c r="CE56" s="33"/>
+      <c r="CF56" s="33"/>
+      <c r="CG56" s="33"/>
+      <c r="CH56" s="33"/>
+      <c r="CI56" s="34"/>
     </row>
-    <row r="35" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A35" s="75"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="76"/>
-      <c r="L35" s="76"/>
-      <c r="M35" s="76"/>
-      <c r="N35" s="76"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="76"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="76"/>
-      <c r="T35" s="76"/>
-      <c r="U35" s="76"/>
-      <c r="V35" s="76"/>
-      <c r="W35" s="76"/>
-      <c r="X35" s="76"/>
-      <c r="Y35" s="76"/>
-      <c r="Z35" s="76"/>
-      <c r="AA35" s="76"/>
-      <c r="AB35" s="76"/>
-      <c r="AC35" s="76"/>
-      <c r="AD35" s="76"/>
-      <c r="AE35" s="76"/>
-      <c r="AF35" s="76"/>
-      <c r="AG35" s="76"/>
-      <c r="AH35" s="76"/>
-      <c r="AI35" s="76"/>
-      <c r="AJ35" s="76"/>
-      <c r="AK35" s="76"/>
-      <c r="AL35" s="76"/>
-      <c r="AM35" s="76"/>
-      <c r="AN35" s="76"/>
-      <c r="AO35" s="76"/>
-      <c r="AP35" s="76"/>
-      <c r="AQ35" s="76"/>
-      <c r="AR35" s="76"/>
-      <c r="AS35" s="76"/>
-      <c r="AT35" s="76"/>
-      <c r="AU35" s="76"/>
-      <c r="AV35" s="76"/>
-      <c r="AW35" s="76"/>
-      <c r="AX35" s="76"/>
-      <c r="AY35" s="76"/>
-      <c r="AZ35" s="76"/>
-      <c r="BA35" s="76"/>
-      <c r="BB35" s="76"/>
-      <c r="BC35" s="76"/>
-      <c r="BD35" s="76"/>
-      <c r="BE35" s="76"/>
-      <c r="BF35" s="76"/>
-      <c r="BG35" s="76"/>
-      <c r="BH35" s="76"/>
-      <c r="BI35" s="76"/>
-      <c r="BJ35" s="76"/>
-      <c r="BK35" s="76"/>
-      <c r="BL35" s="76"/>
-      <c r="BM35" s="76"/>
-      <c r="BN35" s="76"/>
-      <c r="BO35" s="76"/>
-      <c r="BP35" s="76"/>
-      <c r="BQ35" s="76"/>
-      <c r="BR35" s="76"/>
-      <c r="BS35" s="76"/>
-      <c r="BT35" s="76"/>
-      <c r="BU35" s="76"/>
-      <c r="BV35" s="76"/>
-      <c r="BW35" s="76"/>
-      <c r="BX35" s="76"/>
-      <c r="BY35" s="76"/>
-      <c r="BZ35" s="76"/>
-      <c r="CA35" s="76"/>
-      <c r="CB35" s="76"/>
-      <c r="CC35" s="76"/>
-      <c r="CD35" s="76"/>
-      <c r="CE35" s="76"/>
-      <c r="CF35" s="76"/>
-      <c r="CG35" s="76"/>
-      <c r="CH35" s="76"/>
-      <c r="CI35" s="77"/>
+    <row r="57" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A57" s="75"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="76"/>
+      <c r="D57" s="76"/>
+      <c r="E57" s="76"/>
+      <c r="F57" s="76"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="76"/>
+      <c r="I57" s="76"/>
+      <c r="J57" s="76"/>
+      <c r="K57" s="76"/>
+      <c r="L57" s="76"/>
+      <c r="M57" s="76"/>
+      <c r="N57" s="76"/>
+      <c r="O57" s="76"/>
+      <c r="P57" s="76"/>
+      <c r="Q57" s="76"/>
+      <c r="R57" s="76"/>
+      <c r="S57" s="76"/>
+      <c r="T57" s="76"/>
+      <c r="U57" s="76"/>
+      <c r="V57" s="76"/>
+      <c r="W57" s="76"/>
+      <c r="X57" s="76"/>
+      <c r="Y57" s="76"/>
+      <c r="Z57" s="76"/>
+      <c r="AA57" s="76"/>
+      <c r="AB57" s="76"/>
+      <c r="AC57" s="76"/>
+      <c r="AD57" s="76"/>
+      <c r="AE57" s="76"/>
+      <c r="AF57" s="76"/>
+      <c r="AG57" s="76"/>
+      <c r="AH57" s="76"/>
+      <c r="AI57" s="76"/>
+      <c r="AJ57" s="76"/>
+      <c r="AK57" s="76"/>
+      <c r="AL57" s="76"/>
+      <c r="AM57" s="76"/>
+      <c r="AN57" s="76"/>
+      <c r="AO57" s="76"/>
+      <c r="AP57" s="76"/>
+      <c r="AQ57" s="76"/>
+      <c r="AR57" s="76"/>
+      <c r="AS57" s="76"/>
+      <c r="AT57" s="76"/>
+      <c r="AU57" s="76"/>
+      <c r="AV57" s="76"/>
+      <c r="AW57" s="76"/>
+      <c r="AX57" s="76"/>
+      <c r="AY57" s="76"/>
+      <c r="AZ57" s="76"/>
+      <c r="BA57" s="76"/>
+      <c r="BB57" s="76"/>
+      <c r="BC57" s="76"/>
+      <c r="BD57" s="76"/>
+      <c r="BE57" s="76"/>
+      <c r="BF57" s="76"/>
+      <c r="BG57" s="76"/>
+      <c r="BH57" s="76"/>
+      <c r="BI57" s="76"/>
+      <c r="BJ57" s="76"/>
+      <c r="BK57" s="76"/>
+      <c r="BL57" s="76"/>
+      <c r="BM57" s="76"/>
+      <c r="BN57" s="76"/>
+      <c r="BO57" s="76"/>
+      <c r="BP57" s="76"/>
+      <c r="BQ57" s="76"/>
+      <c r="BR57" s="76"/>
+      <c r="BS57" s="76"/>
+      <c r="BT57" s="76"/>
+      <c r="BU57" s="76"/>
+      <c r="BV57" s="76"/>
+      <c r="BW57" s="76"/>
+      <c r="BX57" s="76"/>
+      <c r="BY57" s="76"/>
+      <c r="BZ57" s="76"/>
+      <c r="CA57" s="76"/>
+      <c r="CB57" s="76"/>
+      <c r="CC57" s="76"/>
+      <c r="CD57" s="76"/>
+      <c r="CE57" s="76"/>
+      <c r="CF57" s="76"/>
+      <c r="CG57" s="76"/>
+      <c r="CH57" s="76"/>
+      <c r="CI57" s="77"/>
     </row>
-    <row r="36" spans="1:87" ht="27" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A36" s="78"/>
-      <c r="B36" s="35" t="s">
+    <row r="58" spans="1:87" ht="27" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A58" s="78"/>
+      <c r="B58" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="36"/>
-      <c r="D36" s="47" t="s">
+      <c r="C58" s="36"/>
+      <c r="D58" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="E36" s="48"/>
-      <c r="F36" s="37" t="s">
+      <c r="E58" s="48"/>
+      <c r="F58" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G36" s="38"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="39" t="s">
+      <c r="G58" s="38"/>
+      <c r="H58" s="36"/>
+      <c r="I58" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="40"/>
-      <c r="Q36" s="40"/>
-      <c r="R36" s="40"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="40"/>
-      <c r="U36" s="40"/>
-      <c r="V36" s="40"/>
-      <c r="W36" s="40"/>
-      <c r="X36" s="40"/>
-      <c r="Y36" s="40"/>
-      <c r="Z36" s="40"/>
-      <c r="AA36" s="40"/>
-      <c r="AB36" s="40"/>
-      <c r="AC36" s="40"/>
-      <c r="AD36" s="40"/>
-      <c r="AE36" s="40"/>
-      <c r="AF36" s="40"/>
-      <c r="AG36" s="40"/>
-      <c r="AH36" s="40"/>
-      <c r="AI36" s="40"/>
-      <c r="AJ36" s="40"/>
-      <c r="AK36" s="40"/>
-      <c r="AL36" s="40"/>
-      <c r="AM36" s="40"/>
-      <c r="AN36" s="40"/>
-      <c r="AO36" s="40"/>
-      <c r="AP36" s="40"/>
-      <c r="AQ36" s="40"/>
-      <c r="AR36" s="40"/>
-      <c r="AS36" s="40"/>
-      <c r="AT36" s="40"/>
-      <c r="AU36" s="40"/>
-      <c r="AV36" s="40"/>
-      <c r="AW36" s="40"/>
-      <c r="AX36" s="40"/>
-      <c r="AY36" s="40"/>
-      <c r="AZ36" s="40"/>
-      <c r="BA36" s="40"/>
-      <c r="BB36" s="40"/>
-      <c r="BC36" s="40"/>
-      <c r="BD36" s="40"/>
-      <c r="BE36" s="40"/>
-      <c r="BF36" s="40"/>
-      <c r="BG36" s="40"/>
-      <c r="BH36" s="40"/>
-      <c r="BI36" s="40"/>
-      <c r="BJ36" s="40"/>
-      <c r="BK36" s="40"/>
-      <c r="BL36" s="40"/>
-      <c r="BM36" s="40"/>
-      <c r="BN36" s="40"/>
-      <c r="BO36" s="40"/>
-      <c r="BP36" s="40"/>
-      <c r="BQ36" s="40"/>
-      <c r="BR36" s="40"/>
-      <c r="BS36" s="40"/>
-      <c r="BT36" s="40"/>
-      <c r="BU36" s="40"/>
-      <c r="BV36" s="40"/>
-      <c r="BW36" s="40"/>
-      <c r="BX36" s="40"/>
-      <c r="BY36" s="40"/>
-      <c r="BZ36" s="40"/>
-      <c r="CA36" s="40"/>
-      <c r="CB36" s="40"/>
-      <c r="CC36" s="40"/>
-      <c r="CD36" s="40"/>
-      <c r="CE36" s="40"/>
-      <c r="CF36" s="40"/>
-      <c r="CG36" s="40"/>
-      <c r="CH36" s="40"/>
-      <c r="CI36" s="41"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="40"/>
+      <c r="M58" s="40"/>
+      <c r="N58" s="40"/>
+      <c r="O58" s="40"/>
+      <c r="P58" s="40"/>
+      <c r="Q58" s="40"/>
+      <c r="R58" s="40"/>
+      <c r="S58" s="40"/>
+      <c r="T58" s="40"/>
+      <c r="U58" s="40"/>
+      <c r="V58" s="40"/>
+      <c r="W58" s="40"/>
+      <c r="X58" s="40"/>
+      <c r="Y58" s="40"/>
+      <c r="Z58" s="40"/>
+      <c r="AA58" s="40"/>
+      <c r="AB58" s="40"/>
+      <c r="AC58" s="40"/>
+      <c r="AD58" s="40"/>
+      <c r="AE58" s="40"/>
+      <c r="AF58" s="40"/>
+      <c r="AG58" s="40"/>
+      <c r="AH58" s="40"/>
+      <c r="AI58" s="40"/>
+      <c r="AJ58" s="40"/>
+      <c r="AK58" s="40"/>
+      <c r="AL58" s="40"/>
+      <c r="AM58" s="40"/>
+      <c r="AN58" s="40"/>
+      <c r="AO58" s="40"/>
+      <c r="AP58" s="40"/>
+      <c r="AQ58" s="40"/>
+      <c r="AR58" s="40"/>
+      <c r="AS58" s="40"/>
+      <c r="AT58" s="40"/>
+      <c r="AU58" s="40"/>
+      <c r="AV58" s="40"/>
+      <c r="AW58" s="40"/>
+      <c r="AX58" s="40"/>
+      <c r="AY58" s="40"/>
+      <c r="AZ58" s="40"/>
+      <c r="BA58" s="40"/>
+      <c r="BB58" s="40"/>
+      <c r="BC58" s="40"/>
+      <c r="BD58" s="40"/>
+      <c r="BE58" s="40"/>
+      <c r="BF58" s="40"/>
+      <c r="BG58" s="40"/>
+      <c r="BH58" s="40"/>
+      <c r="BI58" s="40"/>
+      <c r="BJ58" s="40"/>
+      <c r="BK58" s="40"/>
+      <c r="BL58" s="40"/>
+      <c r="BM58" s="40"/>
+      <c r="BN58" s="40"/>
+      <c r="BO58" s="40"/>
+      <c r="BP58" s="40"/>
+      <c r="BQ58" s="40"/>
+      <c r="BR58" s="40"/>
+      <c r="BS58" s="40"/>
+      <c r="BT58" s="40"/>
+      <c r="BU58" s="40"/>
+      <c r="BV58" s="40"/>
+      <c r="BW58" s="40"/>
+      <c r="BX58" s="40"/>
+      <c r="BY58" s="40"/>
+      <c r="BZ58" s="40"/>
+      <c r="CA58" s="40"/>
+      <c r="CB58" s="40"/>
+      <c r="CC58" s="40"/>
+      <c r="CD58" s="40"/>
+      <c r="CE58" s="40"/>
+      <c r="CF58" s="40"/>
+      <c r="CG58" s="40"/>
+      <c r="CH58" s="40"/>
+      <c r="CI58" s="41"/>
     </row>
-    <row r="37" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A37" s="79"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="70"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="70"/>
-      <c r="N37" s="70"/>
-      <c r="O37" s="70"/>
-      <c r="P37" s="70"/>
-      <c r="Q37" s="70"/>
-      <c r="R37" s="70"/>
-      <c r="S37" s="70"/>
-      <c r="T37" s="70"/>
-      <c r="U37" s="70"/>
-      <c r="V37" s="70"/>
-      <c r="W37" s="70"/>
-      <c r="X37" s="70"/>
-      <c r="Y37" s="70"/>
-      <c r="Z37" s="70"/>
-      <c r="AA37" s="70"/>
-      <c r="AB37" s="70"/>
-      <c r="AC37" s="70"/>
-      <c r="AD37" s="70"/>
-      <c r="AE37" s="70"/>
-      <c r="AF37" s="70"/>
-      <c r="AG37" s="70"/>
-      <c r="AH37" s="70"/>
-      <c r="AI37" s="70"/>
-      <c r="AJ37" s="70"/>
-      <c r="AK37" s="70"/>
-      <c r="AL37" s="70"/>
-      <c r="AM37" s="70"/>
-      <c r="AN37" s="70"/>
-      <c r="AO37" s="70"/>
-      <c r="AP37" s="70"/>
-      <c r="AQ37" s="70"/>
-      <c r="AR37" s="70"/>
-      <c r="AS37" s="70"/>
-      <c r="AT37" s="70"/>
-      <c r="AU37" s="70"/>
-      <c r="AV37" s="70"/>
-      <c r="AW37" s="70"/>
-      <c r="AX37" s="70"/>
-      <c r="AY37" s="70"/>
-      <c r="AZ37" s="70"/>
-      <c r="BA37" s="70"/>
-      <c r="BB37" s="70"/>
-      <c r="BC37" s="70"/>
-      <c r="BD37" s="70"/>
-      <c r="BE37" s="70"/>
-      <c r="BF37" s="70"/>
-      <c r="BG37" s="70"/>
-      <c r="BH37" s="70"/>
-      <c r="BI37" s="70"/>
-      <c r="BJ37" s="70"/>
-      <c r="BK37" s="70"/>
-      <c r="BL37" s="70"/>
-      <c r="BM37" s="70"/>
-      <c r="BN37" s="70"/>
-      <c r="BO37" s="70"/>
-      <c r="BP37" s="70"/>
-      <c r="BQ37" s="70"/>
-      <c r="BR37" s="70"/>
-      <c r="BS37" s="70"/>
-      <c r="BT37" s="70"/>
-      <c r="BU37" s="70"/>
-      <c r="BV37" s="70"/>
-      <c r="BW37" s="70"/>
-      <c r="BX37" s="70"/>
-      <c r="BY37" s="70"/>
-      <c r="BZ37" s="70"/>
-      <c r="CA37" s="70"/>
-      <c r="CB37" s="70"/>
-      <c r="CC37" s="70"/>
-      <c r="CD37" s="70"/>
-      <c r="CE37" s="70"/>
-      <c r="CF37" s="70"/>
-      <c r="CG37" s="70"/>
-      <c r="CH37" s="70"/>
-      <c r="CI37" s="71"/>
+    <row r="59" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A59" s="79"/>
+      <c r="B59" s="69"/>
+      <c r="C59" s="70"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="70"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="70"/>
+      <c r="I59" s="70"/>
+      <c r="J59" s="70"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="70"/>
+      <c r="M59" s="70"/>
+      <c r="N59" s="70"/>
+      <c r="O59" s="70"/>
+      <c r="P59" s="70"/>
+      <c r="Q59" s="70"/>
+      <c r="R59" s="70"/>
+      <c r="S59" s="70"/>
+      <c r="T59" s="70"/>
+      <c r="U59" s="70"/>
+      <c r="V59" s="70"/>
+      <c r="W59" s="70"/>
+      <c r="X59" s="70"/>
+      <c r="Y59" s="70"/>
+      <c r="Z59" s="70"/>
+      <c r="AA59" s="70"/>
+      <c r="AB59" s="70"/>
+      <c r="AC59" s="70"/>
+      <c r="AD59" s="70"/>
+      <c r="AE59" s="70"/>
+      <c r="AF59" s="70"/>
+      <c r="AG59" s="70"/>
+      <c r="AH59" s="70"/>
+      <c r="AI59" s="70"/>
+      <c r="AJ59" s="70"/>
+      <c r="AK59" s="70"/>
+      <c r="AL59" s="70"/>
+      <c r="AM59" s="70"/>
+      <c r="AN59" s="70"/>
+      <c r="AO59" s="70"/>
+      <c r="AP59" s="70"/>
+      <c r="AQ59" s="70"/>
+      <c r="AR59" s="70"/>
+      <c r="AS59" s="70"/>
+      <c r="AT59" s="70"/>
+      <c r="AU59" s="70"/>
+      <c r="AV59" s="70"/>
+      <c r="AW59" s="70"/>
+      <c r="AX59" s="70"/>
+      <c r="AY59" s="70"/>
+      <c r="AZ59" s="70"/>
+      <c r="BA59" s="70"/>
+      <c r="BB59" s="70"/>
+      <c r="BC59" s="70"/>
+      <c r="BD59" s="70"/>
+      <c r="BE59" s="70"/>
+      <c r="BF59" s="70"/>
+      <c r="BG59" s="70"/>
+      <c r="BH59" s="70"/>
+      <c r="BI59" s="70"/>
+      <c r="BJ59" s="70"/>
+      <c r="BK59" s="70"/>
+      <c r="BL59" s="70"/>
+      <c r="BM59" s="70"/>
+      <c r="BN59" s="70"/>
+      <c r="BO59" s="70"/>
+      <c r="BP59" s="70"/>
+      <c r="BQ59" s="70"/>
+      <c r="BR59" s="70"/>
+      <c r="BS59" s="70"/>
+      <c r="BT59" s="70"/>
+      <c r="BU59" s="70"/>
+      <c r="BV59" s="70"/>
+      <c r="BW59" s="70"/>
+      <c r="BX59" s="70"/>
+      <c r="BY59" s="70"/>
+      <c r="BZ59" s="70"/>
+      <c r="CA59" s="70"/>
+      <c r="CB59" s="70"/>
+      <c r="CC59" s="70"/>
+      <c r="CD59" s="70"/>
+      <c r="CE59" s="70"/>
+      <c r="CF59" s="70"/>
+      <c r="CG59" s="70"/>
+      <c r="CH59" s="70"/>
+      <c r="CI59" s="71"/>
     </row>
-    <row r="38" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A38" s="79"/>
-      <c r="B38" s="72"/>
-      <c r="C38" s="35" t="s">
+    <row r="60" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A60" s="79"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="37" t="s">
+      <c r="D60" s="36"/>
+      <c r="E60" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="36"/>
-      <c r="O38" s="37" t="s">
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="38"/>
+      <c r="K60" s="38"/>
+      <c r="L60" s="38"/>
+      <c r="M60" s="38"/>
+      <c r="N60" s="36"/>
+      <c r="O60" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="P38" s="38"/>
-      <c r="Q38" s="38"/>
-      <c r="R38" s="38"/>
-      <c r="S38" s="38"/>
-      <c r="T38" s="38"/>
-      <c r="U38" s="38"/>
-      <c r="V38" s="38"/>
-      <c r="W38" s="38"/>
-      <c r="X38" s="38"/>
-      <c r="Y38" s="38"/>
-      <c r="Z38" s="38"/>
-      <c r="AA38" s="38"/>
-      <c r="AB38" s="38"/>
-      <c r="AC38" s="38"/>
-      <c r="AD38" s="38"/>
-      <c r="AE38" s="38"/>
-      <c r="AF38" s="38"/>
-      <c r="AG38" s="38"/>
-      <c r="AH38" s="38"/>
-      <c r="AI38" s="38"/>
-      <c r="AJ38" s="38"/>
-      <c r="AK38" s="38"/>
-      <c r="AL38" s="38"/>
-      <c r="AM38" s="38"/>
-      <c r="AN38" s="38"/>
-      <c r="AO38" s="36"/>
-      <c r="AP38" s="37" t="s">
+      <c r="P60" s="38"/>
+      <c r="Q60" s="38"/>
+      <c r="R60" s="38"/>
+      <c r="S60" s="38"/>
+      <c r="T60" s="38"/>
+      <c r="U60" s="38"/>
+      <c r="V60" s="38"/>
+      <c r="W60" s="38"/>
+      <c r="X60" s="38"/>
+      <c r="Y60" s="38"/>
+      <c r="Z60" s="38"/>
+      <c r="AA60" s="38"/>
+      <c r="AB60" s="38"/>
+      <c r="AC60" s="38"/>
+      <c r="AD60" s="38"/>
+      <c r="AE60" s="38"/>
+      <c r="AF60" s="38"/>
+      <c r="AG60" s="38"/>
+      <c r="AH60" s="38"/>
+      <c r="AI60" s="38"/>
+      <c r="AJ60" s="38"/>
+      <c r="AK60" s="38"/>
+      <c r="AL60" s="38"/>
+      <c r="AM60" s="38"/>
+      <c r="AN60" s="38"/>
+      <c r="AO60" s="36"/>
+      <c r="AP60" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AQ38" s="38"/>
-      <c r="AR38" s="36"/>
-      <c r="AS38" s="37" t="s">
+      <c r="AQ60" s="38"/>
+      <c r="AR60" s="36"/>
+      <c r="AS60" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="AT38" s="38"/>
-      <c r="AU38" s="38"/>
-      <c r="AV38" s="38"/>
-      <c r="AW38" s="36"/>
-      <c r="AX38" s="37" t="s">
+      <c r="AT60" s="38"/>
+      <c r="AU60" s="38"/>
+      <c r="AV60" s="38"/>
+      <c r="AW60" s="36"/>
+      <c r="AX60" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="AY38" s="38"/>
-      <c r="AZ38" s="38"/>
-      <c r="BA38" s="38"/>
-      <c r="BB38" s="38"/>
-      <c r="BC38" s="38"/>
-      <c r="BD38" s="38"/>
-      <c r="BE38" s="38"/>
-      <c r="BF38" s="38"/>
-      <c r="BG38" s="38"/>
-      <c r="BH38" s="38"/>
-      <c r="BI38" s="38"/>
-      <c r="BJ38" s="38"/>
-      <c r="BK38" s="38"/>
-      <c r="BL38" s="36"/>
-      <c r="BM38" s="37" t="s">
+      <c r="AY60" s="38"/>
+      <c r="AZ60" s="38"/>
+      <c r="BA60" s="38"/>
+      <c r="BB60" s="38"/>
+      <c r="BC60" s="38"/>
+      <c r="BD60" s="38"/>
+      <c r="BE60" s="38"/>
+      <c r="BF60" s="38"/>
+      <c r="BG60" s="38"/>
+      <c r="BH60" s="38"/>
+      <c r="BI60" s="38"/>
+      <c r="BJ60" s="38"/>
+      <c r="BK60" s="38"/>
+      <c r="BL60" s="36"/>
+      <c r="BM60" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="BN38" s="38"/>
-      <c r="BO38" s="38"/>
-      <c r="BP38" s="38"/>
-      <c r="BQ38" s="38"/>
-      <c r="BR38" s="38"/>
-      <c r="BS38" s="38"/>
-      <c r="BT38" s="38"/>
-      <c r="BU38" s="38"/>
-      <c r="BV38" s="38"/>
-      <c r="BW38" s="38"/>
-      <c r="BX38" s="38"/>
-      <c r="BY38" s="38"/>
-      <c r="BZ38" s="38"/>
-      <c r="CA38" s="38"/>
-      <c r="CB38" s="38"/>
-      <c r="CC38" s="38"/>
-      <c r="CD38" s="38"/>
-      <c r="CE38" s="38"/>
-      <c r="CF38" s="38"/>
-      <c r="CG38" s="38"/>
-      <c r="CH38" s="38"/>
-      <c r="CI38" s="42"/>
+      <c r="BN60" s="38"/>
+      <c r="BO60" s="38"/>
+      <c r="BP60" s="38"/>
+      <c r="BQ60" s="38"/>
+      <c r="BR60" s="38"/>
+      <c r="BS60" s="38"/>
+      <c r="BT60" s="38"/>
+      <c r="BU60" s="38"/>
+      <c r="BV60" s="38"/>
+      <c r="BW60" s="38"/>
+      <c r="BX60" s="38"/>
+      <c r="BY60" s="38"/>
+      <c r="BZ60" s="38"/>
+      <c r="CA60" s="38"/>
+      <c r="CB60" s="38"/>
+      <c r="CC60" s="38"/>
+      <c r="CD60" s="38"/>
+      <c r="CE60" s="38"/>
+      <c r="CF60" s="38"/>
+      <c r="CG60" s="38"/>
+      <c r="CH60" s="38"/>
+      <c r="CI60" s="42"/>
     </row>
-    <row r="39" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A39" s="79"/>
-      <c r="B39" s="73"/>
-      <c r="C39" s="43">
+    <row r="61" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A61" s="79"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="43">
         <v>1</v>
       </c>
-      <c r="D39" s="44"/>
-      <c r="E39" s="53" t="s">
+      <c r="D61" s="44"/>
+      <c r="E61" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="54"/>
-      <c r="J39" s="54"/>
-      <c r="K39" s="54"/>
-      <c r="L39" s="54"/>
-      <c r="M39" s="54"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="53" t="s">
+      <c r="F61" s="54"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="54"/>
+      <c r="M61" s="54"/>
+      <c r="N61" s="55"/>
+      <c r="O61" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="54"/>
-      <c r="T39" s="54"/>
-      <c r="U39" s="54"/>
-      <c r="V39" s="54"/>
-      <c r="W39" s="54"/>
-      <c r="X39" s="54"/>
-      <c r="Y39" s="54"/>
-      <c r="Z39" s="54"/>
-      <c r="AA39" s="54"/>
-      <c r="AB39" s="54"/>
-      <c r="AC39" s="54"/>
-      <c r="AD39" s="54"/>
-      <c r="AE39" s="54"/>
-      <c r="AF39" s="54"/>
-      <c r="AG39" s="54"/>
-      <c r="AH39" s="54"/>
-      <c r="AI39" s="54"/>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
-      <c r="AP39" s="53" t="s">
+      <c r="P61" s="54"/>
+      <c r="Q61" s="54"/>
+      <c r="R61" s="54"/>
+      <c r="S61" s="54"/>
+      <c r="T61" s="54"/>
+      <c r="U61" s="54"/>
+      <c r="V61" s="54"/>
+      <c r="W61" s="54"/>
+      <c r="X61" s="54"/>
+      <c r="Y61" s="54"/>
+      <c r="Z61" s="54"/>
+      <c r="AA61" s="54"/>
+      <c r="AB61" s="54"/>
+      <c r="AC61" s="54"/>
+      <c r="AD61" s="54"/>
+      <c r="AE61" s="54"/>
+      <c r="AF61" s="54"/>
+      <c r="AG61" s="54"/>
+      <c r="AH61" s="54"/>
+      <c r="AI61" s="54"/>
+      <c r="AJ61" s="54"/>
+      <c r="AK61" s="54"/>
+      <c r="AL61" s="54"/>
+      <c r="AM61" s="54"/>
+      <c r="AN61" s="54"/>
+      <c r="AO61" s="55"/>
+      <c r="AP61" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="AQ39" s="54"/>
-      <c r="AR39" s="55"/>
-      <c r="AS39" s="53" t="s">
+      <c r="AQ61" s="54"/>
+      <c r="AR61" s="55"/>
+      <c r="AS61" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="AT39" s="54"/>
-      <c r="AU39" s="54"/>
-      <c r="AV39" s="54"/>
-      <c r="AW39" s="55"/>
-      <c r="AX39" s="53" t="s">
+      <c r="AT61" s="54"/>
+      <c r="AU61" s="54"/>
+      <c r="AV61" s="54"/>
+      <c r="AW61" s="55"/>
+      <c r="AX61" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="AY39" s="54"/>
-      <c r="AZ39" s="54"/>
-      <c r="BA39" s="54"/>
-      <c r="BB39" s="54"/>
-      <c r="BC39" s="54"/>
-      <c r="BD39" s="54"/>
-      <c r="BE39" s="54"/>
-      <c r="BF39" s="54"/>
-      <c r="BG39" s="54"/>
-      <c r="BH39" s="54"/>
-      <c r="BI39" s="54"/>
-      <c r="BJ39" s="54"/>
-      <c r="BK39" s="54"/>
-      <c r="BL39" s="55"/>
-      <c r="BM39" s="53" t="s">
+      <c r="AY61" s="54"/>
+      <c r="AZ61" s="54"/>
+      <c r="BA61" s="54"/>
+      <c r="BB61" s="54"/>
+      <c r="BC61" s="54"/>
+      <c r="BD61" s="54"/>
+      <c r="BE61" s="54"/>
+      <c r="BF61" s="54"/>
+      <c r="BG61" s="54"/>
+      <c r="BH61" s="54"/>
+      <c r="BI61" s="54"/>
+      <c r="BJ61" s="54"/>
+      <c r="BK61" s="54"/>
+      <c r="BL61" s="55"/>
+      <c r="BM61" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="BN39" s="54"/>
-      <c r="BO39" s="54"/>
-      <c r="BP39" s="54"/>
-      <c r="BQ39" s="54"/>
-      <c r="BR39" s="54"/>
-      <c r="BS39" s="54"/>
-      <c r="BT39" s="54"/>
-      <c r="BU39" s="54"/>
-      <c r="BV39" s="54"/>
-      <c r="BW39" s="54"/>
-      <c r="BX39" s="54"/>
-      <c r="BY39" s="54"/>
-      <c r="BZ39" s="54"/>
-      <c r="CA39" s="54"/>
-      <c r="CB39" s="54"/>
-      <c r="CC39" s="54"/>
-      <c r="CD39" s="54"/>
-      <c r="CE39" s="54"/>
-      <c r="CF39" s="54"/>
-      <c r="CG39" s="54"/>
-      <c r="CH39" s="54"/>
-      <c r="CI39" s="65"/>
+      <c r="BN61" s="54"/>
+      <c r="BO61" s="54"/>
+      <c r="BP61" s="54"/>
+      <c r="BQ61" s="54"/>
+      <c r="BR61" s="54"/>
+      <c r="BS61" s="54"/>
+      <c r="BT61" s="54"/>
+      <c r="BU61" s="54"/>
+      <c r="BV61" s="54"/>
+      <c r="BW61" s="54"/>
+      <c r="BX61" s="54"/>
+      <c r="BY61" s="54"/>
+      <c r="BZ61" s="54"/>
+      <c r="CA61" s="54"/>
+      <c r="CB61" s="54"/>
+      <c r="CC61" s="54"/>
+      <c r="CD61" s="54"/>
+      <c r="CE61" s="54"/>
+      <c r="CF61" s="54"/>
+      <c r="CG61" s="54"/>
+      <c r="CH61" s="54"/>
+      <c r="CI61" s="65"/>
     </row>
-    <row r="40" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A40" s="79"/>
-      <c r="B40" s="73"/>
-      <c r="C40" s="45">
+    <row r="62" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A62" s="79"/>
+      <c r="B62" s="73"/>
+      <c r="C62" s="45">
         <v>2</v>
       </c>
-      <c r="D40" s="46"/>
-      <c r="E40" s="56" t="s">
+      <c r="D62" s="46"/>
+      <c r="E62" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
-      <c r="K40" s="57"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="57"/>
-      <c r="N40" s="58"/>
-      <c r="O40" s="56" t="s">
+      <c r="F62" s="57"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="57"/>
+      <c r="K62" s="57"/>
+      <c r="L62" s="57"/>
+      <c r="M62" s="57"/>
+      <c r="N62" s="58"/>
+      <c r="O62" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="P40" s="57"/>
-      <c r="Q40" s="57"/>
-      <c r="R40" s="57"/>
-      <c r="S40" s="57"/>
-      <c r="T40" s="57"/>
-      <c r="U40" s="57"/>
-      <c r="V40" s="57"/>
-      <c r="W40" s="57"/>
-      <c r="X40" s="57"/>
-      <c r="Y40" s="57"/>
-      <c r="Z40" s="57"/>
-      <c r="AA40" s="57"/>
-      <c r="AB40" s="57"/>
-      <c r="AC40" s="57"/>
-      <c r="AD40" s="57"/>
-      <c r="AE40" s="57"/>
-      <c r="AF40" s="57"/>
-      <c r="AG40" s="57"/>
-      <c r="AH40" s="57"/>
-      <c r="AI40" s="57"/>
-      <c r="AJ40" s="57"/>
-      <c r="AK40" s="57"/>
-      <c r="AL40" s="57"/>
-      <c r="AM40" s="57"/>
-      <c r="AN40" s="57"/>
-      <c r="AO40" s="58"/>
-      <c r="AP40" s="56" t="s">
+      <c r="P62" s="57"/>
+      <c r="Q62" s="57"/>
+      <c r="R62" s="57"/>
+      <c r="S62" s="57"/>
+      <c r="T62" s="57"/>
+      <c r="U62" s="57"/>
+      <c r="V62" s="57"/>
+      <c r="W62" s="57"/>
+      <c r="X62" s="57"/>
+      <c r="Y62" s="57"/>
+      <c r="Z62" s="57"/>
+      <c r="AA62" s="57"/>
+      <c r="AB62" s="57"/>
+      <c r="AC62" s="57"/>
+      <c r="AD62" s="57"/>
+      <c r="AE62" s="57"/>
+      <c r="AF62" s="57"/>
+      <c r="AG62" s="57"/>
+      <c r="AH62" s="57"/>
+      <c r="AI62" s="57"/>
+      <c r="AJ62" s="57"/>
+      <c r="AK62" s="57"/>
+      <c r="AL62" s="57"/>
+      <c r="AM62" s="57"/>
+      <c r="AN62" s="57"/>
+      <c r="AO62" s="58"/>
+      <c r="AP62" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AQ40" s="57"/>
-      <c r="AR40" s="58"/>
-      <c r="AS40" s="56" t="s">
+      <c r="AQ62" s="57"/>
+      <c r="AR62" s="58"/>
+      <c r="AS62" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="AT40" s="57"/>
-      <c r="AU40" s="57"/>
-      <c r="AV40" s="57"/>
-      <c r="AW40" s="58"/>
-      <c r="AX40" s="56" t="s">
+      <c r="AT62" s="57"/>
+      <c r="AU62" s="57"/>
+      <c r="AV62" s="57"/>
+      <c r="AW62" s="58"/>
+      <c r="AX62" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY40" s="57"/>
-      <c r="AZ40" s="57"/>
-      <c r="BA40" s="57"/>
-      <c r="BB40" s="57"/>
-      <c r="BC40" s="57"/>
-      <c r="BD40" s="57"/>
-      <c r="BE40" s="57"/>
-      <c r="BF40" s="57"/>
-      <c r="BG40" s="57"/>
-      <c r="BH40" s="57"/>
-      <c r="BI40" s="57"/>
-      <c r="BJ40" s="57"/>
-      <c r="BK40" s="57"/>
-      <c r="BL40" s="58"/>
-      <c r="BM40" s="56" t="s">
+      <c r="AY62" s="57"/>
+      <c r="AZ62" s="57"/>
+      <c r="BA62" s="57"/>
+      <c r="BB62" s="57"/>
+      <c r="BC62" s="57"/>
+      <c r="BD62" s="57"/>
+      <c r="BE62" s="57"/>
+      <c r="BF62" s="57"/>
+      <c r="BG62" s="57"/>
+      <c r="BH62" s="57"/>
+      <c r="BI62" s="57"/>
+      <c r="BJ62" s="57"/>
+      <c r="BK62" s="57"/>
+      <c r="BL62" s="58"/>
+      <c r="BM62" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="BN40" s="57"/>
-      <c r="BO40" s="57"/>
-      <c r="BP40" s="57"/>
-      <c r="BQ40" s="57"/>
-      <c r="BR40" s="57"/>
-      <c r="BS40" s="57"/>
-      <c r="BT40" s="57"/>
-      <c r="BU40" s="57"/>
-      <c r="BV40" s="57"/>
-      <c r="BW40" s="57"/>
-      <c r="BX40" s="57"/>
-      <c r="BY40" s="57"/>
-      <c r="BZ40" s="57"/>
-      <c r="CA40" s="57"/>
-      <c r="CB40" s="57"/>
-      <c r="CC40" s="57"/>
-      <c r="CD40" s="57"/>
-      <c r="CE40" s="57"/>
-      <c r="CF40" s="57"/>
-      <c r="CG40" s="57"/>
-      <c r="CH40" s="57"/>
-      <c r="CI40" s="66"/>
+      <c r="BN62" s="57"/>
+      <c r="BO62" s="57"/>
+      <c r="BP62" s="57"/>
+      <c r="BQ62" s="57"/>
+      <c r="BR62" s="57"/>
+      <c r="BS62" s="57"/>
+      <c r="BT62" s="57"/>
+      <c r="BU62" s="57"/>
+      <c r="BV62" s="57"/>
+      <c r="BW62" s="57"/>
+      <c r="BX62" s="57"/>
+      <c r="BY62" s="57"/>
+      <c r="BZ62" s="57"/>
+      <c r="CA62" s="57"/>
+      <c r="CB62" s="57"/>
+      <c r="CC62" s="57"/>
+      <c r="CD62" s="57"/>
+      <c r="CE62" s="57"/>
+      <c r="CF62" s="57"/>
+      <c r="CG62" s="57"/>
+      <c r="CH62" s="57"/>
+      <c r="CI62" s="66"/>
     </row>
-    <row r="41" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A41" s="79"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="49">
+    <row r="63" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A63" s="79"/>
+      <c r="B63" s="73"/>
+      <c r="C63" s="49">
         <v>3</v>
       </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="59" t="s">
+      <c r="D63" s="50"/>
+      <c r="E63" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="F41" s="60"/>
-      <c r="G41" s="60"/>
-      <c r="H41" s="60"/>
-      <c r="I41" s="60"/>
-      <c r="J41" s="60"/>
-      <c r="K41" s="60"/>
-      <c r="L41" s="60"/>
-      <c r="M41" s="60"/>
-      <c r="N41" s="61"/>
-      <c r="O41" s="59" t="s">
+      <c r="F63" s="60"/>
+      <c r="G63" s="60"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="60"/>
+      <c r="J63" s="60"/>
+      <c r="K63" s="60"/>
+      <c r="L63" s="60"/>
+      <c r="M63" s="60"/>
+      <c r="N63" s="61"/>
+      <c r="O63" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="P41" s="60"/>
-      <c r="Q41" s="60"/>
-      <c r="R41" s="60"/>
-      <c r="S41" s="60"/>
-      <c r="T41" s="60"/>
-      <c r="U41" s="60"/>
-      <c r="V41" s="60"/>
-      <c r="W41" s="60"/>
-      <c r="X41" s="60"/>
-      <c r="Y41" s="60"/>
-      <c r="Z41" s="60"/>
-      <c r="AA41" s="60"/>
-      <c r="AB41" s="60"/>
-      <c r="AC41" s="60"/>
-      <c r="AD41" s="60"/>
-      <c r="AE41" s="60"/>
-      <c r="AF41" s="60"/>
-      <c r="AG41" s="60"/>
-      <c r="AH41" s="60"/>
-      <c r="AI41" s="60"/>
-      <c r="AJ41" s="60"/>
-      <c r="AK41" s="60"/>
-      <c r="AL41" s="60"/>
-      <c r="AM41" s="60"/>
-      <c r="AN41" s="60"/>
-      <c r="AO41" s="61"/>
-      <c r="AP41" s="59" t="s">
+      <c r="P63" s="60"/>
+      <c r="Q63" s="60"/>
+      <c r="R63" s="60"/>
+      <c r="S63" s="60"/>
+      <c r="T63" s="60"/>
+      <c r="U63" s="60"/>
+      <c r="V63" s="60"/>
+      <c r="W63" s="60"/>
+      <c r="X63" s="60"/>
+      <c r="Y63" s="60"/>
+      <c r="Z63" s="60"/>
+      <c r="AA63" s="60"/>
+      <c r="AB63" s="60"/>
+      <c r="AC63" s="60"/>
+      <c r="AD63" s="60"/>
+      <c r="AE63" s="60"/>
+      <c r="AF63" s="60"/>
+      <c r="AG63" s="60"/>
+      <c r="AH63" s="60"/>
+      <c r="AI63" s="60"/>
+      <c r="AJ63" s="60"/>
+      <c r="AK63" s="60"/>
+      <c r="AL63" s="60"/>
+      <c r="AM63" s="60"/>
+      <c r="AN63" s="60"/>
+      <c r="AO63" s="61"/>
+      <c r="AP63" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AQ41" s="60"/>
-      <c r="AR41" s="61"/>
-      <c r="AS41" s="59" t="s">
+      <c r="AQ63" s="60"/>
+      <c r="AR63" s="61"/>
+      <c r="AS63" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="AT41" s="60"/>
-      <c r="AU41" s="60"/>
-      <c r="AV41" s="60"/>
-      <c r="AW41" s="61"/>
-      <c r="AX41" s="59" t="s">
+      <c r="AT63" s="60"/>
+      <c r="AU63" s="60"/>
+      <c r="AV63" s="60"/>
+      <c r="AW63" s="61"/>
+      <c r="AX63" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY41" s="60"/>
-      <c r="AZ41" s="60"/>
-      <c r="BA41" s="60"/>
-      <c r="BB41" s="60"/>
-      <c r="BC41" s="60"/>
-      <c r="BD41" s="60"/>
-      <c r="BE41" s="60"/>
-      <c r="BF41" s="60"/>
-      <c r="BG41" s="60"/>
-      <c r="BH41" s="60"/>
-      <c r="BI41" s="60"/>
-      <c r="BJ41" s="60"/>
-      <c r="BK41" s="60"/>
-      <c r="BL41" s="61"/>
-      <c r="BM41" s="59" t="s">
+      <c r="AY63" s="60"/>
+      <c r="AZ63" s="60"/>
+      <c r="BA63" s="60"/>
+      <c r="BB63" s="60"/>
+      <c r="BC63" s="60"/>
+      <c r="BD63" s="60"/>
+      <c r="BE63" s="60"/>
+      <c r="BF63" s="60"/>
+      <c r="BG63" s="60"/>
+      <c r="BH63" s="60"/>
+      <c r="BI63" s="60"/>
+      <c r="BJ63" s="60"/>
+      <c r="BK63" s="60"/>
+      <c r="BL63" s="61"/>
+      <c r="BM63" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="BN41" s="60"/>
-      <c r="BO41" s="60"/>
-      <c r="BP41" s="60"/>
-      <c r="BQ41" s="60"/>
-      <c r="BR41" s="60"/>
-      <c r="BS41" s="60"/>
-      <c r="BT41" s="60"/>
-      <c r="BU41" s="60"/>
-      <c r="BV41" s="60"/>
-      <c r="BW41" s="60"/>
-      <c r="BX41" s="60"/>
-      <c r="BY41" s="60"/>
-      <c r="BZ41" s="60"/>
-      <c r="CA41" s="60"/>
-      <c r="CB41" s="60"/>
-      <c r="CC41" s="60"/>
-      <c r="CD41" s="60"/>
-      <c r="CE41" s="60"/>
-      <c r="CF41" s="60"/>
-      <c r="CG41" s="60"/>
-      <c r="CH41" s="60"/>
-      <c r="CI41" s="67"/>
+      <c r="BN63" s="60"/>
+      <c r="BO63" s="60"/>
+      <c r="BP63" s="60"/>
+      <c r="BQ63" s="60"/>
+      <c r="BR63" s="60"/>
+      <c r="BS63" s="60"/>
+      <c r="BT63" s="60"/>
+      <c r="BU63" s="60"/>
+      <c r="BV63" s="60"/>
+      <c r="BW63" s="60"/>
+      <c r="BX63" s="60"/>
+      <c r="BY63" s="60"/>
+      <c r="BZ63" s="60"/>
+      <c r="CA63" s="60"/>
+      <c r="CB63" s="60"/>
+      <c r="CC63" s="60"/>
+      <c r="CD63" s="60"/>
+      <c r="CE63" s="60"/>
+      <c r="CF63" s="60"/>
+      <c r="CG63" s="60"/>
+      <c r="CH63" s="60"/>
+      <c r="CI63" s="67"/>
     </row>
-    <row r="42" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A42" s="79"/>
-      <c r="B42" s="73"/>
-      <c r="C42" s="45">
+    <row r="64" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A64" s="79"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="45">
         <v>4</v>
       </c>
-      <c r="D42" s="46"/>
-      <c r="E42" s="56" t="s">
+      <c r="D64" s="46"/>
+      <c r="E64" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="57"/>
-      <c r="N42" s="58"/>
-      <c r="O42" s="56" t="s">
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="57"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="57"/>
+      <c r="N64" s="58"/>
+      <c r="O64" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="P42" s="57"/>
-      <c r="Q42" s="57"/>
-      <c r="R42" s="57"/>
-      <c r="S42" s="57"/>
-      <c r="T42" s="57"/>
-      <c r="U42" s="57"/>
-      <c r="V42" s="57"/>
-      <c r="W42" s="57"/>
-      <c r="X42" s="57"/>
-      <c r="Y42" s="57"/>
-      <c r="Z42" s="57"/>
-      <c r="AA42" s="57"/>
-      <c r="AB42" s="57"/>
-      <c r="AC42" s="57"/>
-      <c r="AD42" s="57"/>
-      <c r="AE42" s="57"/>
-      <c r="AF42" s="57"/>
-      <c r="AG42" s="57"/>
-      <c r="AH42" s="57"/>
-      <c r="AI42" s="57"/>
-      <c r="AJ42" s="57"/>
-      <c r="AK42" s="57"/>
-      <c r="AL42" s="57"/>
-      <c r="AM42" s="57"/>
-      <c r="AN42" s="57"/>
-      <c r="AO42" s="58"/>
-      <c r="AP42" s="56" t="s">
+      <c r="P64" s="57"/>
+      <c r="Q64" s="57"/>
+      <c r="R64" s="57"/>
+      <c r="S64" s="57"/>
+      <c r="T64" s="57"/>
+      <c r="U64" s="57"/>
+      <c r="V64" s="57"/>
+      <c r="W64" s="57"/>
+      <c r="X64" s="57"/>
+      <c r="Y64" s="57"/>
+      <c r="Z64" s="57"/>
+      <c r="AA64" s="57"/>
+      <c r="AB64" s="57"/>
+      <c r="AC64" s="57"/>
+      <c r="AD64" s="57"/>
+      <c r="AE64" s="57"/>
+      <c r="AF64" s="57"/>
+      <c r="AG64" s="57"/>
+      <c r="AH64" s="57"/>
+      <c r="AI64" s="57"/>
+      <c r="AJ64" s="57"/>
+      <c r="AK64" s="57"/>
+      <c r="AL64" s="57"/>
+      <c r="AM64" s="57"/>
+      <c r="AN64" s="57"/>
+      <c r="AO64" s="58"/>
+      <c r="AP64" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AQ42" s="57"/>
-      <c r="AR42" s="58"/>
-      <c r="AS42" s="56" t="s">
+      <c r="AQ64" s="57"/>
+      <c r="AR64" s="58"/>
+      <c r="AS64" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="AT42" s="57"/>
-      <c r="AU42" s="57"/>
-      <c r="AV42" s="57"/>
-      <c r="AW42" s="58"/>
-      <c r="AX42" s="56" t="s">
+      <c r="AT64" s="57"/>
+      <c r="AU64" s="57"/>
+      <c r="AV64" s="57"/>
+      <c r="AW64" s="58"/>
+      <c r="AX64" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY42" s="57"/>
-      <c r="AZ42" s="57"/>
-      <c r="BA42" s="57"/>
-      <c r="BB42" s="57"/>
-      <c r="BC42" s="57"/>
-      <c r="BD42" s="57"/>
-      <c r="BE42" s="57"/>
-      <c r="BF42" s="57"/>
-      <c r="BG42" s="57"/>
-      <c r="BH42" s="57"/>
-      <c r="BI42" s="57"/>
-      <c r="BJ42" s="57"/>
-      <c r="BK42" s="57"/>
-      <c r="BL42" s="58"/>
-      <c r="BM42" s="56" t="s">
+      <c r="AY64" s="57"/>
+      <c r="AZ64" s="57"/>
+      <c r="BA64" s="57"/>
+      <c r="BB64" s="57"/>
+      <c r="BC64" s="57"/>
+      <c r="BD64" s="57"/>
+      <c r="BE64" s="57"/>
+      <c r="BF64" s="57"/>
+      <c r="BG64" s="57"/>
+      <c r="BH64" s="57"/>
+      <c r="BI64" s="57"/>
+      <c r="BJ64" s="57"/>
+      <c r="BK64" s="57"/>
+      <c r="BL64" s="58"/>
+      <c r="BM64" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="BN42" s="57"/>
-      <c r="BO42" s="57"/>
-      <c r="BP42" s="57"/>
-      <c r="BQ42" s="57"/>
-      <c r="BR42" s="57"/>
-      <c r="BS42" s="57"/>
-      <c r="BT42" s="57"/>
-      <c r="BU42" s="57"/>
-      <c r="BV42" s="57"/>
-      <c r="BW42" s="57"/>
-      <c r="BX42" s="57"/>
-      <c r="BY42" s="57"/>
-      <c r="BZ42" s="57"/>
-      <c r="CA42" s="57"/>
-      <c r="CB42" s="57"/>
-      <c r="CC42" s="57"/>
-      <c r="CD42" s="57"/>
-      <c r="CE42" s="57"/>
-      <c r="CF42" s="57"/>
-      <c r="CG42" s="57"/>
-      <c r="CH42" s="57"/>
-      <c r="CI42" s="66"/>
+      <c r="BN64" s="57"/>
+      <c r="BO64" s="57"/>
+      <c r="BP64" s="57"/>
+      <c r="BQ64" s="57"/>
+      <c r="BR64" s="57"/>
+      <c r="BS64" s="57"/>
+      <c r="BT64" s="57"/>
+      <c r="BU64" s="57"/>
+      <c r="BV64" s="57"/>
+      <c r="BW64" s="57"/>
+      <c r="BX64" s="57"/>
+      <c r="BY64" s="57"/>
+      <c r="BZ64" s="57"/>
+      <c r="CA64" s="57"/>
+      <c r="CB64" s="57"/>
+      <c r="CC64" s="57"/>
+      <c r="CD64" s="57"/>
+      <c r="CE64" s="57"/>
+      <c r="CF64" s="57"/>
+      <c r="CG64" s="57"/>
+      <c r="CH64" s="57"/>
+      <c r="CI64" s="66"/>
     </row>
-    <row r="43" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A43" s="79"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="49">
+    <row r="65" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A65" s="79"/>
+      <c r="B65" s="73"/>
+      <c r="C65" s="49">
         <v>5</v>
       </c>
-      <c r="D43" s="50"/>
-      <c r="E43" s="59" t="s">
+      <c r="D65" s="50"/>
+      <c r="E65" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="F43" s="60"/>
-      <c r="G43" s="60"/>
-      <c r="H43" s="60"/>
-      <c r="I43" s="60"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="60"/>
-      <c r="L43" s="60"/>
-      <c r="M43" s="60"/>
-      <c r="N43" s="61"/>
-      <c r="O43" s="59" t="s">
+      <c r="F65" s="60"/>
+      <c r="G65" s="60"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="60"/>
+      <c r="L65" s="60"/>
+      <c r="M65" s="60"/>
+      <c r="N65" s="61"/>
+      <c r="O65" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="P43" s="60"/>
-      <c r="Q43" s="60"/>
-      <c r="R43" s="60"/>
-      <c r="S43" s="60"/>
-      <c r="T43" s="60"/>
-      <c r="U43" s="60"/>
-      <c r="V43" s="60"/>
-      <c r="W43" s="60"/>
-      <c r="X43" s="60"/>
-      <c r="Y43" s="60"/>
-      <c r="Z43" s="60"/>
-      <c r="AA43" s="60"/>
-      <c r="AB43" s="60"/>
-      <c r="AC43" s="60"/>
-      <c r="AD43" s="60"/>
-      <c r="AE43" s="60"/>
-      <c r="AF43" s="60"/>
-      <c r="AG43" s="60"/>
-      <c r="AH43" s="60"/>
-      <c r="AI43" s="60"/>
-      <c r="AJ43" s="60"/>
-      <c r="AK43" s="60"/>
-      <c r="AL43" s="60"/>
-      <c r="AM43" s="60"/>
-      <c r="AN43" s="60"/>
-      <c r="AO43" s="61"/>
-      <c r="AP43" s="59" t="s">
+      <c r="P65" s="60"/>
+      <c r="Q65" s="60"/>
+      <c r="R65" s="60"/>
+      <c r="S65" s="60"/>
+      <c r="T65" s="60"/>
+      <c r="U65" s="60"/>
+      <c r="V65" s="60"/>
+      <c r="W65" s="60"/>
+      <c r="X65" s="60"/>
+      <c r="Y65" s="60"/>
+      <c r="Z65" s="60"/>
+      <c r="AA65" s="60"/>
+      <c r="AB65" s="60"/>
+      <c r="AC65" s="60"/>
+      <c r="AD65" s="60"/>
+      <c r="AE65" s="60"/>
+      <c r="AF65" s="60"/>
+      <c r="AG65" s="60"/>
+      <c r="AH65" s="60"/>
+      <c r="AI65" s="60"/>
+      <c r="AJ65" s="60"/>
+      <c r="AK65" s="60"/>
+      <c r="AL65" s="60"/>
+      <c r="AM65" s="60"/>
+      <c r="AN65" s="60"/>
+      <c r="AO65" s="61"/>
+      <c r="AP65" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AQ43" s="60"/>
-      <c r="AR43" s="61"/>
-      <c r="AS43" s="59" t="s">
+      <c r="AQ65" s="60"/>
+      <c r="AR65" s="61"/>
+      <c r="AS65" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="AT43" s="60"/>
-      <c r="AU43" s="60"/>
-      <c r="AV43" s="60"/>
-      <c r="AW43" s="61"/>
-      <c r="AX43" s="59" t="s">
+      <c r="AT65" s="60"/>
+      <c r="AU65" s="60"/>
+      <c r="AV65" s="60"/>
+      <c r="AW65" s="61"/>
+      <c r="AX65" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY43" s="60"/>
-      <c r="AZ43" s="60"/>
-      <c r="BA43" s="60"/>
-      <c r="BB43" s="60"/>
-      <c r="BC43" s="60"/>
-      <c r="BD43" s="60"/>
-      <c r="BE43" s="60"/>
-      <c r="BF43" s="60"/>
-      <c r="BG43" s="60"/>
-      <c r="BH43" s="60"/>
-      <c r="BI43" s="60"/>
-      <c r="BJ43" s="60"/>
-      <c r="BK43" s="60"/>
-      <c r="BL43" s="61"/>
-      <c r="BM43" s="59" t="s">
+      <c r="AY65" s="60"/>
+      <c r="AZ65" s="60"/>
+      <c r="BA65" s="60"/>
+      <c r="BB65" s="60"/>
+      <c r="BC65" s="60"/>
+      <c r="BD65" s="60"/>
+      <c r="BE65" s="60"/>
+      <c r="BF65" s="60"/>
+      <c r="BG65" s="60"/>
+      <c r="BH65" s="60"/>
+      <c r="BI65" s="60"/>
+      <c r="BJ65" s="60"/>
+      <c r="BK65" s="60"/>
+      <c r="BL65" s="61"/>
+      <c r="BM65" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="BN43" s="60"/>
-      <c r="BO43" s="60"/>
-      <c r="BP43" s="60"/>
-      <c r="BQ43" s="60"/>
-      <c r="BR43" s="60"/>
-      <c r="BS43" s="60"/>
-      <c r="BT43" s="60"/>
-      <c r="BU43" s="60"/>
-      <c r="BV43" s="60"/>
-      <c r="BW43" s="60"/>
-      <c r="BX43" s="60"/>
-      <c r="BY43" s="60"/>
-      <c r="BZ43" s="60"/>
-      <c r="CA43" s="60"/>
-      <c r="CB43" s="60"/>
-      <c r="CC43" s="60"/>
-      <c r="CD43" s="60"/>
-      <c r="CE43" s="60"/>
-      <c r="CF43" s="60"/>
-      <c r="CG43" s="60"/>
-      <c r="CH43" s="60"/>
-      <c r="CI43" s="67"/>
+      <c r="BN65" s="60"/>
+      <c r="BO65" s="60"/>
+      <c r="BP65" s="60"/>
+      <c r="BQ65" s="60"/>
+      <c r="BR65" s="60"/>
+      <c r="BS65" s="60"/>
+      <c r="BT65" s="60"/>
+      <c r="BU65" s="60"/>
+      <c r="BV65" s="60"/>
+      <c r="BW65" s="60"/>
+      <c r="BX65" s="60"/>
+      <c r="BY65" s="60"/>
+      <c r="BZ65" s="60"/>
+      <c r="CA65" s="60"/>
+      <c r="CB65" s="60"/>
+      <c r="CC65" s="60"/>
+      <c r="CD65" s="60"/>
+      <c r="CE65" s="60"/>
+      <c r="CF65" s="60"/>
+      <c r="CG65" s="60"/>
+      <c r="CH65" s="60"/>
+      <c r="CI65" s="67"/>
     </row>
-    <row r="44" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A44" s="79"/>
-      <c r="B44" s="73"/>
-      <c r="C44" s="45">
+    <row r="66" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A66" s="79"/>
+      <c r="B66" s="73"/>
+      <c r="C66" s="45">
         <v>6</v>
       </c>
-      <c r="D44" s="46"/>
-      <c r="E44" s="56" t="s">
+      <c r="D66" s="46"/>
+      <c r="E66" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="57"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="57"/>
-      <c r="N44" s="58"/>
-      <c r="O44" s="56" t="s">
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="57"/>
+      <c r="K66" s="57"/>
+      <c r="L66" s="57"/>
+      <c r="M66" s="57"/>
+      <c r="N66" s="58"/>
+      <c r="O66" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="57"/>
-      <c r="R44" s="57"/>
-      <c r="S44" s="57"/>
-      <c r="T44" s="57"/>
-      <c r="U44" s="57"/>
-      <c r="V44" s="57"/>
-      <c r="W44" s="57"/>
-      <c r="X44" s="57"/>
-      <c r="Y44" s="57"/>
-      <c r="Z44" s="57"/>
-      <c r="AA44" s="57"/>
-      <c r="AB44" s="57"/>
-      <c r="AC44" s="57"/>
-      <c r="AD44" s="57"/>
-      <c r="AE44" s="57"/>
-      <c r="AF44" s="57"/>
-      <c r="AG44" s="57"/>
-      <c r="AH44" s="57"/>
-      <c r="AI44" s="57"/>
-      <c r="AJ44" s="57"/>
-      <c r="AK44" s="57"/>
-      <c r="AL44" s="57"/>
-      <c r="AM44" s="57"/>
-      <c r="AN44" s="57"/>
-      <c r="AO44" s="58"/>
-      <c r="AP44" s="56" t="s">
+      <c r="P66" s="57"/>
+      <c r="Q66" s="57"/>
+      <c r="R66" s="57"/>
+      <c r="S66" s="57"/>
+      <c r="T66" s="57"/>
+      <c r="U66" s="57"/>
+      <c r="V66" s="57"/>
+      <c r="W66" s="57"/>
+      <c r="X66" s="57"/>
+      <c r="Y66" s="57"/>
+      <c r="Z66" s="57"/>
+      <c r="AA66" s="57"/>
+      <c r="AB66" s="57"/>
+      <c r="AC66" s="57"/>
+      <c r="AD66" s="57"/>
+      <c r="AE66" s="57"/>
+      <c r="AF66" s="57"/>
+      <c r="AG66" s="57"/>
+      <c r="AH66" s="57"/>
+      <c r="AI66" s="57"/>
+      <c r="AJ66" s="57"/>
+      <c r="AK66" s="57"/>
+      <c r="AL66" s="57"/>
+      <c r="AM66" s="57"/>
+      <c r="AN66" s="57"/>
+      <c r="AO66" s="58"/>
+      <c r="AP66" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AQ44" s="57"/>
-      <c r="AR44" s="58"/>
-      <c r="AS44" s="56" t="s">
+      <c r="AQ66" s="57"/>
+      <c r="AR66" s="58"/>
+      <c r="AS66" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="AT44" s="57"/>
-      <c r="AU44" s="57"/>
-      <c r="AV44" s="57"/>
-      <c r="AW44" s="58"/>
-      <c r="AX44" s="56" t="s">
+      <c r="AT66" s="57"/>
+      <c r="AU66" s="57"/>
+      <c r="AV66" s="57"/>
+      <c r="AW66" s="58"/>
+      <c r="AX66" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY44" s="57"/>
-      <c r="AZ44" s="57"/>
-      <c r="BA44" s="57"/>
-      <c r="BB44" s="57"/>
-      <c r="BC44" s="57"/>
-      <c r="BD44" s="57"/>
-      <c r="BE44" s="57"/>
-      <c r="BF44" s="57"/>
-      <c r="BG44" s="57"/>
-      <c r="BH44" s="57"/>
-      <c r="BI44" s="57"/>
-      <c r="BJ44" s="57"/>
-      <c r="BK44" s="57"/>
-      <c r="BL44" s="58"/>
-      <c r="BM44" s="56" t="s">
+      <c r="AY66" s="57"/>
+      <c r="AZ66" s="57"/>
+      <c r="BA66" s="57"/>
+      <c r="BB66" s="57"/>
+      <c r="BC66" s="57"/>
+      <c r="BD66" s="57"/>
+      <c r="BE66" s="57"/>
+      <c r="BF66" s="57"/>
+      <c r="BG66" s="57"/>
+      <c r="BH66" s="57"/>
+      <c r="BI66" s="57"/>
+      <c r="BJ66" s="57"/>
+      <c r="BK66" s="57"/>
+      <c r="BL66" s="58"/>
+      <c r="BM66" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="BN44" s="57"/>
-      <c r="BO44" s="57"/>
-      <c r="BP44" s="57"/>
-      <c r="BQ44" s="57"/>
-      <c r="BR44" s="57"/>
-      <c r="BS44" s="57"/>
-      <c r="BT44" s="57"/>
-      <c r="BU44" s="57"/>
-      <c r="BV44" s="57"/>
-      <c r="BW44" s="57"/>
-      <c r="BX44" s="57"/>
-      <c r="BY44" s="57"/>
-      <c r="BZ44" s="57"/>
-      <c r="CA44" s="57"/>
-      <c r="CB44" s="57"/>
-      <c r="CC44" s="57"/>
-      <c r="CD44" s="57"/>
-      <c r="CE44" s="57"/>
-      <c r="CF44" s="57"/>
-      <c r="CG44" s="57"/>
-      <c r="CH44" s="57"/>
-      <c r="CI44" s="66"/>
+      <c r="BN66" s="57"/>
+      <c r="BO66" s="57"/>
+      <c r="BP66" s="57"/>
+      <c r="BQ66" s="57"/>
+      <c r="BR66" s="57"/>
+      <c r="BS66" s="57"/>
+      <c r="BT66" s="57"/>
+      <c r="BU66" s="57"/>
+      <c r="BV66" s="57"/>
+      <c r="BW66" s="57"/>
+      <c r="BX66" s="57"/>
+      <c r="BY66" s="57"/>
+      <c r="BZ66" s="57"/>
+      <c r="CA66" s="57"/>
+      <c r="CB66" s="57"/>
+      <c r="CC66" s="57"/>
+      <c r="CD66" s="57"/>
+      <c r="CE66" s="57"/>
+      <c r="CF66" s="57"/>
+      <c r="CG66" s="57"/>
+      <c r="CH66" s="57"/>
+      <c r="CI66" s="66"/>
     </row>
-    <row r="45" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A45" s="79"/>
-      <c r="B45" s="73"/>
-      <c r="C45" s="49">
+    <row r="67" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A67" s="79"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="49">
         <v>7</v>
       </c>
-      <c r="D45" s="50"/>
-      <c r="E45" s="59" t="s">
+      <c r="D67" s="50"/>
+      <c r="E67" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="F45" s="60"/>
-      <c r="G45" s="60"/>
-      <c r="H45" s="60"/>
-      <c r="I45" s="60"/>
-      <c r="J45" s="60"/>
-      <c r="K45" s="60"/>
-      <c r="L45" s="60"/>
-      <c r="M45" s="60"/>
-      <c r="N45" s="61"/>
-      <c r="O45" s="59" t="s">
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="60"/>
+      <c r="J67" s="60"/>
+      <c r="K67" s="60"/>
+      <c r="L67" s="60"/>
+      <c r="M67" s="60"/>
+      <c r="N67" s="61"/>
+      <c r="O67" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="P45" s="60"/>
-      <c r="Q45" s="60"/>
-      <c r="R45" s="60"/>
-      <c r="S45" s="60"/>
-      <c r="T45" s="60"/>
-      <c r="U45" s="60"/>
-      <c r="V45" s="60"/>
-      <c r="W45" s="60"/>
-      <c r="X45" s="60"/>
-      <c r="Y45" s="60"/>
-      <c r="Z45" s="60"/>
-      <c r="AA45" s="60"/>
-      <c r="AB45" s="60"/>
-      <c r="AC45" s="60"/>
-      <c r="AD45" s="60"/>
-      <c r="AE45" s="60"/>
-      <c r="AF45" s="60"/>
-      <c r="AG45" s="60"/>
-      <c r="AH45" s="60"/>
-      <c r="AI45" s="60"/>
-      <c r="AJ45" s="60"/>
-      <c r="AK45" s="60"/>
-      <c r="AL45" s="60"/>
-      <c r="AM45" s="60"/>
-      <c r="AN45" s="60"/>
-      <c r="AO45" s="61"/>
-      <c r="AP45" s="59" t="s">
+      <c r="P67" s="60"/>
+      <c r="Q67" s="60"/>
+      <c r="R67" s="60"/>
+      <c r="S67" s="60"/>
+      <c r="T67" s="60"/>
+      <c r="U67" s="60"/>
+      <c r="V67" s="60"/>
+      <c r="W67" s="60"/>
+      <c r="X67" s="60"/>
+      <c r="Y67" s="60"/>
+      <c r="Z67" s="60"/>
+      <c r="AA67" s="60"/>
+      <c r="AB67" s="60"/>
+      <c r="AC67" s="60"/>
+      <c r="AD67" s="60"/>
+      <c r="AE67" s="60"/>
+      <c r="AF67" s="60"/>
+      <c r="AG67" s="60"/>
+      <c r="AH67" s="60"/>
+      <c r="AI67" s="60"/>
+      <c r="AJ67" s="60"/>
+      <c r="AK67" s="60"/>
+      <c r="AL67" s="60"/>
+      <c r="AM67" s="60"/>
+      <c r="AN67" s="60"/>
+      <c r="AO67" s="61"/>
+      <c r="AP67" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AQ45" s="60"/>
-      <c r="AR45" s="61"/>
-      <c r="AS45" s="59" t="s">
+      <c r="AQ67" s="60"/>
+      <c r="AR67" s="61"/>
+      <c r="AS67" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="AT45" s="60"/>
-      <c r="AU45" s="60"/>
-      <c r="AV45" s="60"/>
-      <c r="AW45" s="61"/>
-      <c r="AX45" s="59" t="s">
+      <c r="AT67" s="60"/>
+      <c r="AU67" s="60"/>
+      <c r="AV67" s="60"/>
+      <c r="AW67" s="61"/>
+      <c r="AX67" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY45" s="60"/>
-      <c r="AZ45" s="60"/>
-      <c r="BA45" s="60"/>
-      <c r="BB45" s="60"/>
-      <c r="BC45" s="60"/>
-      <c r="BD45" s="60"/>
-      <c r="BE45" s="60"/>
-      <c r="BF45" s="60"/>
-      <c r="BG45" s="60"/>
-      <c r="BH45" s="60"/>
-      <c r="BI45" s="60"/>
-      <c r="BJ45" s="60"/>
-      <c r="BK45" s="60"/>
-      <c r="BL45" s="61"/>
-      <c r="BM45" s="59" t="s">
+      <c r="AY67" s="60"/>
+      <c r="AZ67" s="60"/>
+      <c r="BA67" s="60"/>
+      <c r="BB67" s="60"/>
+      <c r="BC67" s="60"/>
+      <c r="BD67" s="60"/>
+      <c r="BE67" s="60"/>
+      <c r="BF67" s="60"/>
+      <c r="BG67" s="60"/>
+      <c r="BH67" s="60"/>
+      <c r="BI67" s="60"/>
+      <c r="BJ67" s="60"/>
+      <c r="BK67" s="60"/>
+      <c r="BL67" s="61"/>
+      <c r="BM67" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="BN45" s="60"/>
-      <c r="BO45" s="60"/>
-      <c r="BP45" s="60"/>
-      <c r="BQ45" s="60"/>
-      <c r="BR45" s="60"/>
-      <c r="BS45" s="60"/>
-      <c r="BT45" s="60"/>
-      <c r="BU45" s="60"/>
-      <c r="BV45" s="60"/>
-      <c r="BW45" s="60"/>
-      <c r="BX45" s="60"/>
-      <c r="BY45" s="60"/>
-      <c r="BZ45" s="60"/>
-      <c r="CA45" s="60"/>
-      <c r="CB45" s="60"/>
-      <c r="CC45" s="60"/>
-      <c r="CD45" s="60"/>
-      <c r="CE45" s="60"/>
-      <c r="CF45" s="60"/>
-      <c r="CG45" s="60"/>
-      <c r="CH45" s="60"/>
-      <c r="CI45" s="67"/>
+      <c r="BN67" s="60"/>
+      <c r="BO67" s="60"/>
+      <c r="BP67" s="60"/>
+      <c r="BQ67" s="60"/>
+      <c r="BR67" s="60"/>
+      <c r="BS67" s="60"/>
+      <c r="BT67" s="60"/>
+      <c r="BU67" s="60"/>
+      <c r="BV67" s="60"/>
+      <c r="BW67" s="60"/>
+      <c r="BX67" s="60"/>
+      <c r="BY67" s="60"/>
+      <c r="BZ67" s="60"/>
+      <c r="CA67" s="60"/>
+      <c r="CB67" s="60"/>
+      <c r="CC67" s="60"/>
+      <c r="CD67" s="60"/>
+      <c r="CE67" s="60"/>
+      <c r="CF67" s="60"/>
+      <c r="CG67" s="60"/>
+      <c r="CH67" s="60"/>
+      <c r="CI67" s="67"/>
     </row>
-    <row r="46" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A46" s="79"/>
-      <c r="B46" s="73"/>
-      <c r="C46" s="45">
+    <row r="68" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A68" s="79"/>
+      <c r="B68" s="73"/>
+      <c r="C68" s="45">
         <v>8</v>
       </c>
-      <c r="D46" s="46"/>
-      <c r="E46" s="56" t="s">
+      <c r="D68" s="46"/>
+      <c r="E68" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
-      <c r="K46" s="57"/>
-      <c r="L46" s="57"/>
-      <c r="M46" s="57"/>
-      <c r="N46" s="58"/>
-      <c r="O46" s="56" t="s">
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
+      <c r="J68" s="57"/>
+      <c r="K68" s="57"/>
+      <c r="L68" s="57"/>
+      <c r="M68" s="57"/>
+      <c r="N68" s="58"/>
+      <c r="O68" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="P46" s="57"/>
-      <c r="Q46" s="57"/>
-      <c r="R46" s="57"/>
-      <c r="S46" s="57"/>
-      <c r="T46" s="57"/>
-      <c r="U46" s="57"/>
-      <c r="V46" s="57"/>
-      <c r="W46" s="57"/>
-      <c r="X46" s="57"/>
-      <c r="Y46" s="57"/>
-      <c r="Z46" s="57"/>
-      <c r="AA46" s="57"/>
-      <c r="AB46" s="57"/>
-      <c r="AC46" s="57"/>
-      <c r="AD46" s="57"/>
-      <c r="AE46" s="57"/>
-      <c r="AF46" s="57"/>
-      <c r="AG46" s="57"/>
-      <c r="AH46" s="57"/>
-      <c r="AI46" s="57"/>
-      <c r="AJ46" s="57"/>
-      <c r="AK46" s="57"/>
-      <c r="AL46" s="57"/>
-      <c r="AM46" s="57"/>
-      <c r="AN46" s="57"/>
-      <c r="AO46" s="58"/>
-      <c r="AP46" s="56" t="s">
+      <c r="P68" s="57"/>
+      <c r="Q68" s="57"/>
+      <c r="R68" s="57"/>
+      <c r="S68" s="57"/>
+      <c r="T68" s="57"/>
+      <c r="U68" s="57"/>
+      <c r="V68" s="57"/>
+      <c r="W68" s="57"/>
+      <c r="X68" s="57"/>
+      <c r="Y68" s="57"/>
+      <c r="Z68" s="57"/>
+      <c r="AA68" s="57"/>
+      <c r="AB68" s="57"/>
+      <c r="AC68" s="57"/>
+      <c r="AD68" s="57"/>
+      <c r="AE68" s="57"/>
+      <c r="AF68" s="57"/>
+      <c r="AG68" s="57"/>
+      <c r="AH68" s="57"/>
+      <c r="AI68" s="57"/>
+      <c r="AJ68" s="57"/>
+      <c r="AK68" s="57"/>
+      <c r="AL68" s="57"/>
+      <c r="AM68" s="57"/>
+      <c r="AN68" s="57"/>
+      <c r="AO68" s="58"/>
+      <c r="AP68" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="AQ46" s="57"/>
-      <c r="AR46" s="58"/>
-      <c r="AS46" s="56" t="s">
+      <c r="AQ68" s="57"/>
+      <c r="AR68" s="58"/>
+      <c r="AS68" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="AT46" s="57"/>
-      <c r="AU46" s="57"/>
-      <c r="AV46" s="57"/>
-      <c r="AW46" s="58"/>
-      <c r="AX46" s="56" t="s">
+      <c r="AT68" s="57"/>
+      <c r="AU68" s="57"/>
+      <c r="AV68" s="57"/>
+      <c r="AW68" s="58"/>
+      <c r="AX68" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY46" s="57"/>
-      <c r="AZ46" s="57"/>
-      <c r="BA46" s="57"/>
-      <c r="BB46" s="57"/>
-      <c r="BC46" s="57"/>
-      <c r="BD46" s="57"/>
-      <c r="BE46" s="57"/>
-      <c r="BF46" s="57"/>
-      <c r="BG46" s="57"/>
-      <c r="BH46" s="57"/>
-      <c r="BI46" s="57"/>
-      <c r="BJ46" s="57"/>
-      <c r="BK46" s="57"/>
-      <c r="BL46" s="58"/>
-      <c r="BM46" s="56" t="s">
+      <c r="AY68" s="57"/>
+      <c r="AZ68" s="57"/>
+      <c r="BA68" s="57"/>
+      <c r="BB68" s="57"/>
+      <c r="BC68" s="57"/>
+      <c r="BD68" s="57"/>
+      <c r="BE68" s="57"/>
+      <c r="BF68" s="57"/>
+      <c r="BG68" s="57"/>
+      <c r="BH68" s="57"/>
+      <c r="BI68" s="57"/>
+      <c r="BJ68" s="57"/>
+      <c r="BK68" s="57"/>
+      <c r="BL68" s="58"/>
+      <c r="BM68" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="BN46" s="57"/>
-      <c r="BO46" s="57"/>
-      <c r="BP46" s="57"/>
-      <c r="BQ46" s="57"/>
-      <c r="BR46" s="57"/>
-      <c r="BS46" s="57"/>
-      <c r="BT46" s="57"/>
-      <c r="BU46" s="57"/>
-      <c r="BV46" s="57"/>
-      <c r="BW46" s="57"/>
-      <c r="BX46" s="57"/>
-      <c r="BY46" s="57"/>
-      <c r="BZ46" s="57"/>
-      <c r="CA46" s="57"/>
-      <c r="CB46" s="57"/>
-      <c r="CC46" s="57"/>
-      <c r="CD46" s="57"/>
-      <c r="CE46" s="57"/>
-      <c r="CF46" s="57"/>
-      <c r="CG46" s="57"/>
-      <c r="CH46" s="57"/>
-      <c r="CI46" s="66"/>
+      <c r="BN68" s="57"/>
+      <c r="BO68" s="57"/>
+      <c r="BP68" s="57"/>
+      <c r="BQ68" s="57"/>
+      <c r="BR68" s="57"/>
+      <c r="BS68" s="57"/>
+      <c r="BT68" s="57"/>
+      <c r="BU68" s="57"/>
+      <c r="BV68" s="57"/>
+      <c r="BW68" s="57"/>
+      <c r="BX68" s="57"/>
+      <c r="BY68" s="57"/>
+      <c r="BZ68" s="57"/>
+      <c r="CA68" s="57"/>
+      <c r="CB68" s="57"/>
+      <c r="CC68" s="57"/>
+      <c r="CD68" s="57"/>
+      <c r="CE68" s="57"/>
+      <c r="CF68" s="57"/>
+      <c r="CG68" s="57"/>
+      <c r="CH68" s="57"/>
+      <c r="CI68" s="66"/>
     </row>
-    <row r="47" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A47" s="79"/>
-      <c r="B47" s="73"/>
-      <c r="C47" s="49">
+    <row r="69" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A69" s="79"/>
+      <c r="B69" s="73"/>
+      <c r="C69" s="49">
         <v>9</v>
       </c>
-      <c r="D47" s="50"/>
-      <c r="E47" s="59" t="s">
+      <c r="D69" s="50"/>
+      <c r="E69" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="F47" s="60"/>
-      <c r="G47" s="60"/>
-      <c r="H47" s="60"/>
-      <c r="I47" s="60"/>
-      <c r="J47" s="60"/>
-      <c r="K47" s="60"/>
-      <c r="L47" s="60"/>
-      <c r="M47" s="60"/>
-      <c r="N47" s="61"/>
-      <c r="O47" s="59" t="s">
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="60"/>
+      <c r="J69" s="60"/>
+      <c r="K69" s="60"/>
+      <c r="L69" s="60"/>
+      <c r="M69" s="60"/>
+      <c r="N69" s="61"/>
+      <c r="O69" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="P47" s="60"/>
-      <c r="Q47" s="60"/>
-      <c r="R47" s="60"/>
-      <c r="S47" s="60"/>
-      <c r="T47" s="60"/>
-      <c r="U47" s="60"/>
-      <c r="V47" s="60"/>
-      <c r="W47" s="60"/>
-      <c r="X47" s="60"/>
-      <c r="Y47" s="60"/>
-      <c r="Z47" s="60"/>
-      <c r="AA47" s="60"/>
-      <c r="AB47" s="60"/>
-      <c r="AC47" s="60"/>
-      <c r="AD47" s="60"/>
-      <c r="AE47" s="60"/>
-      <c r="AF47" s="60"/>
-      <c r="AG47" s="60"/>
-      <c r="AH47" s="60"/>
-      <c r="AI47" s="60"/>
-      <c r="AJ47" s="60"/>
-      <c r="AK47" s="60"/>
-      <c r="AL47" s="60"/>
-      <c r="AM47" s="60"/>
-      <c r="AN47" s="60"/>
-      <c r="AO47" s="61"/>
-      <c r="AP47" s="59" t="s">
+      <c r="P69" s="60"/>
+      <c r="Q69" s="60"/>
+      <c r="R69" s="60"/>
+      <c r="S69" s="60"/>
+      <c r="T69" s="60"/>
+      <c r="U69" s="60"/>
+      <c r="V69" s="60"/>
+      <c r="W69" s="60"/>
+      <c r="X69" s="60"/>
+      <c r="Y69" s="60"/>
+      <c r="Z69" s="60"/>
+      <c r="AA69" s="60"/>
+      <c r="AB69" s="60"/>
+      <c r="AC69" s="60"/>
+      <c r="AD69" s="60"/>
+      <c r="AE69" s="60"/>
+      <c r="AF69" s="60"/>
+      <c r="AG69" s="60"/>
+      <c r="AH69" s="60"/>
+      <c r="AI69" s="60"/>
+      <c r="AJ69" s="60"/>
+      <c r="AK69" s="60"/>
+      <c r="AL69" s="60"/>
+      <c r="AM69" s="60"/>
+      <c r="AN69" s="60"/>
+      <c r="AO69" s="61"/>
+      <c r="AP69" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="AQ47" s="60"/>
-      <c r="AR47" s="61"/>
-      <c r="AS47" s="59" t="s">
+      <c r="AQ69" s="60"/>
+      <c r="AR69" s="61"/>
+      <c r="AS69" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="AT47" s="60"/>
-      <c r="AU47" s="60"/>
-      <c r="AV47" s="60"/>
-      <c r="AW47" s="61"/>
-      <c r="AX47" s="59" t="s">
+      <c r="AT69" s="60"/>
+      <c r="AU69" s="60"/>
+      <c r="AV69" s="60"/>
+      <c r="AW69" s="61"/>
+      <c r="AX69" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY47" s="60"/>
-      <c r="AZ47" s="60"/>
-      <c r="BA47" s="60"/>
-      <c r="BB47" s="60"/>
-      <c r="BC47" s="60"/>
-      <c r="BD47" s="60"/>
-      <c r="BE47" s="60"/>
-      <c r="BF47" s="60"/>
-      <c r="BG47" s="60"/>
-      <c r="BH47" s="60"/>
-      <c r="BI47" s="60"/>
-      <c r="BJ47" s="60"/>
-      <c r="BK47" s="60"/>
-      <c r="BL47" s="61"/>
-      <c r="BM47" s="59" t="s">
+      <c r="AY69" s="60"/>
+      <c r="AZ69" s="60"/>
+      <c r="BA69" s="60"/>
+      <c r="BB69" s="60"/>
+      <c r="BC69" s="60"/>
+      <c r="BD69" s="60"/>
+      <c r="BE69" s="60"/>
+      <c r="BF69" s="60"/>
+      <c r="BG69" s="60"/>
+      <c r="BH69" s="60"/>
+      <c r="BI69" s="60"/>
+      <c r="BJ69" s="60"/>
+      <c r="BK69" s="60"/>
+      <c r="BL69" s="61"/>
+      <c r="BM69" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="BN47" s="60"/>
-      <c r="BO47" s="60"/>
-      <c r="BP47" s="60"/>
-      <c r="BQ47" s="60"/>
-      <c r="BR47" s="60"/>
-      <c r="BS47" s="60"/>
-      <c r="BT47" s="60"/>
-      <c r="BU47" s="60"/>
-      <c r="BV47" s="60"/>
-      <c r="BW47" s="60"/>
-      <c r="BX47" s="60"/>
-      <c r="BY47" s="60"/>
-      <c r="BZ47" s="60"/>
-      <c r="CA47" s="60"/>
-      <c r="CB47" s="60"/>
-      <c r="CC47" s="60"/>
-      <c r="CD47" s="60"/>
-      <c r="CE47" s="60"/>
-      <c r="CF47" s="60"/>
-      <c r="CG47" s="60"/>
-      <c r="CH47" s="60"/>
-      <c r="CI47" s="67"/>
+      <c r="BN69" s="60"/>
+      <c r="BO69" s="60"/>
+      <c r="BP69" s="60"/>
+      <c r="BQ69" s="60"/>
+      <c r="BR69" s="60"/>
+      <c r="BS69" s="60"/>
+      <c r="BT69" s="60"/>
+      <c r="BU69" s="60"/>
+      <c r="BV69" s="60"/>
+      <c r="BW69" s="60"/>
+      <c r="BX69" s="60"/>
+      <c r="BY69" s="60"/>
+      <c r="BZ69" s="60"/>
+      <c r="CA69" s="60"/>
+      <c r="CB69" s="60"/>
+      <c r="CC69" s="60"/>
+      <c r="CD69" s="60"/>
+      <c r="CE69" s="60"/>
+      <c r="CF69" s="60"/>
+      <c r="CG69" s="60"/>
+      <c r="CH69" s="60"/>
+      <c r="CI69" s="67"/>
     </row>
-    <row r="48" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A48" s="79"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="45">
+    <row r="70" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A70" s="79"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="45">
         <v>10</v>
       </c>
-      <c r="D48" s="46"/>
-      <c r="E48" s="56" t="s">
+      <c r="D70" s="46"/>
+      <c r="E70" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="57"/>
-      <c r="K48" s="57"/>
-      <c r="L48" s="57"/>
-      <c r="M48" s="57"/>
-      <c r="N48" s="58"/>
-      <c r="O48" s="56" t="s">
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
+      <c r="J70" s="57"/>
+      <c r="K70" s="57"/>
+      <c r="L70" s="57"/>
+      <c r="M70" s="57"/>
+      <c r="N70" s="58"/>
+      <c r="O70" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="P48" s="57"/>
-      <c r="Q48" s="57"/>
-      <c r="R48" s="57"/>
-      <c r="S48" s="57"/>
-      <c r="T48" s="57"/>
-      <c r="U48" s="57"/>
-      <c r="V48" s="57"/>
-      <c r="W48" s="57"/>
-      <c r="X48" s="57"/>
-      <c r="Y48" s="57"/>
-      <c r="Z48" s="57"/>
-      <c r="AA48" s="57"/>
-      <c r="AB48" s="57"/>
-      <c r="AC48" s="57"/>
-      <c r="AD48" s="57"/>
-      <c r="AE48" s="57"/>
-      <c r="AF48" s="57"/>
-      <c r="AG48" s="57"/>
-      <c r="AH48" s="57"/>
-      <c r="AI48" s="57"/>
-      <c r="AJ48" s="57"/>
-      <c r="AK48" s="57"/>
-      <c r="AL48" s="57"/>
-      <c r="AM48" s="57"/>
-      <c r="AN48" s="57"/>
-      <c r="AO48" s="58"/>
-      <c r="AP48" s="56" t="s">
+      <c r="P70" s="57"/>
+      <c r="Q70" s="57"/>
+      <c r="R70" s="57"/>
+      <c r="S70" s="57"/>
+      <c r="T70" s="57"/>
+      <c r="U70" s="57"/>
+      <c r="V70" s="57"/>
+      <c r="W70" s="57"/>
+      <c r="X70" s="57"/>
+      <c r="Y70" s="57"/>
+      <c r="Z70" s="57"/>
+      <c r="AA70" s="57"/>
+      <c r="AB70" s="57"/>
+      <c r="AC70" s="57"/>
+      <c r="AD70" s="57"/>
+      <c r="AE70" s="57"/>
+      <c r="AF70" s="57"/>
+      <c r="AG70" s="57"/>
+      <c r="AH70" s="57"/>
+      <c r="AI70" s="57"/>
+      <c r="AJ70" s="57"/>
+      <c r="AK70" s="57"/>
+      <c r="AL70" s="57"/>
+      <c r="AM70" s="57"/>
+      <c r="AN70" s="57"/>
+      <c r="AO70" s="58"/>
+      <c r="AP70" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="AQ48" s="57"/>
-      <c r="AR48" s="58"/>
-      <c r="AS48" s="56" t="s">
+      <c r="AQ70" s="57"/>
+      <c r="AR70" s="58"/>
+      <c r="AS70" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="AT48" s="57"/>
-      <c r="AU48" s="57"/>
-      <c r="AV48" s="57"/>
-      <c r="AW48" s="58"/>
-      <c r="AX48" s="56" t="s">
+      <c r="AT70" s="57"/>
+      <c r="AU70" s="57"/>
+      <c r="AV70" s="57"/>
+      <c r="AW70" s="58"/>
+      <c r="AX70" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY48" s="57"/>
-      <c r="AZ48" s="57"/>
-      <c r="BA48" s="57"/>
-      <c r="BB48" s="57"/>
-      <c r="BC48" s="57"/>
-      <c r="BD48" s="57"/>
-      <c r="BE48" s="57"/>
-      <c r="BF48" s="57"/>
-      <c r="BG48" s="57"/>
-      <c r="BH48" s="57"/>
-      <c r="BI48" s="57"/>
-      <c r="BJ48" s="57"/>
-      <c r="BK48" s="57"/>
-      <c r="BL48" s="58"/>
-      <c r="BM48" s="56" t="s">
+      <c r="AY70" s="57"/>
+      <c r="AZ70" s="57"/>
+      <c r="BA70" s="57"/>
+      <c r="BB70" s="57"/>
+      <c r="BC70" s="57"/>
+      <c r="BD70" s="57"/>
+      <c r="BE70" s="57"/>
+      <c r="BF70" s="57"/>
+      <c r="BG70" s="57"/>
+      <c r="BH70" s="57"/>
+      <c r="BI70" s="57"/>
+      <c r="BJ70" s="57"/>
+      <c r="BK70" s="57"/>
+      <c r="BL70" s="58"/>
+      <c r="BM70" s="56" t="s">
         <v>63</v>
       </c>
-      <c r="BN48" s="57"/>
-      <c r="BO48" s="57"/>
-      <c r="BP48" s="57"/>
-      <c r="BQ48" s="57"/>
-      <c r="BR48" s="57"/>
-      <c r="BS48" s="57"/>
-      <c r="BT48" s="57"/>
-      <c r="BU48" s="57"/>
-      <c r="BV48" s="57"/>
-      <c r="BW48" s="57"/>
-      <c r="BX48" s="57"/>
-      <c r="BY48" s="57"/>
-      <c r="BZ48" s="57"/>
-      <c r="CA48" s="57"/>
-      <c r="CB48" s="57"/>
-      <c r="CC48" s="57"/>
-      <c r="CD48" s="57"/>
-      <c r="CE48" s="57"/>
-      <c r="CF48" s="57"/>
-      <c r="CG48" s="57"/>
-      <c r="CH48" s="57"/>
-      <c r="CI48" s="66"/>
+      <c r="BN70" s="57"/>
+      <c r="BO70" s="57"/>
+      <c r="BP70" s="57"/>
+      <c r="BQ70" s="57"/>
+      <c r="BR70" s="57"/>
+      <c r="BS70" s="57"/>
+      <c r="BT70" s="57"/>
+      <c r="BU70" s="57"/>
+      <c r="BV70" s="57"/>
+      <c r="BW70" s="57"/>
+      <c r="BX70" s="57"/>
+      <c r="BY70" s="57"/>
+      <c r="BZ70" s="57"/>
+      <c r="CA70" s="57"/>
+      <c r="CB70" s="57"/>
+      <c r="CC70" s="57"/>
+      <c r="CD70" s="57"/>
+      <c r="CE70" s="57"/>
+      <c r="CF70" s="57"/>
+      <c r="CG70" s="57"/>
+      <c r="CH70" s="57"/>
+      <c r="CI70" s="66"/>
     </row>
-    <row r="49" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A49" s="79"/>
-      <c r="B49" s="73"/>
-      <c r="C49" s="49">
+    <row r="71" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A71" s="79"/>
+      <c r="B71" s="73"/>
+      <c r="C71" s="49">
         <v>11</v>
       </c>
-      <c r="D49" s="50"/>
-      <c r="E49" s="59" t="s">
+      <c r="D71" s="50"/>
+      <c r="E71" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="F49" s="60"/>
-      <c r="G49" s="60"/>
-      <c r="H49" s="60"/>
-      <c r="I49" s="60"/>
-      <c r="J49" s="60"/>
-      <c r="K49" s="60"/>
-      <c r="L49" s="60"/>
-      <c r="M49" s="60"/>
-      <c r="N49" s="61"/>
-      <c r="O49" s="59" t="s">
+      <c r="F71" s="60"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="60"/>
+      <c r="J71" s="60"/>
+      <c r="K71" s="60"/>
+      <c r="L71" s="60"/>
+      <c r="M71" s="60"/>
+      <c r="N71" s="61"/>
+      <c r="O71" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="P49" s="60"/>
-      <c r="Q49" s="60"/>
-      <c r="R49" s="60"/>
-      <c r="S49" s="60"/>
-      <c r="T49" s="60"/>
-      <c r="U49" s="60"/>
-      <c r="V49" s="60"/>
-      <c r="W49" s="60"/>
-      <c r="X49" s="60"/>
-      <c r="Y49" s="60"/>
-      <c r="Z49" s="60"/>
-      <c r="AA49" s="60"/>
-      <c r="AB49" s="60"/>
-      <c r="AC49" s="60"/>
-      <c r="AD49" s="60"/>
-      <c r="AE49" s="60"/>
-      <c r="AF49" s="60"/>
-      <c r="AG49" s="60"/>
-      <c r="AH49" s="60"/>
-      <c r="AI49" s="60"/>
-      <c r="AJ49" s="60"/>
-      <c r="AK49" s="60"/>
-      <c r="AL49" s="60"/>
-      <c r="AM49" s="60"/>
-      <c r="AN49" s="60"/>
-      <c r="AO49" s="61"/>
-      <c r="AP49" s="59" t="s">
+      <c r="P71" s="60"/>
+      <c r="Q71" s="60"/>
+      <c r="R71" s="60"/>
+      <c r="S71" s="60"/>
+      <c r="T71" s="60"/>
+      <c r="U71" s="60"/>
+      <c r="V71" s="60"/>
+      <c r="W71" s="60"/>
+      <c r="X71" s="60"/>
+      <c r="Y71" s="60"/>
+      <c r="Z71" s="60"/>
+      <c r="AA71" s="60"/>
+      <c r="AB71" s="60"/>
+      <c r="AC71" s="60"/>
+      <c r="AD71" s="60"/>
+      <c r="AE71" s="60"/>
+      <c r="AF71" s="60"/>
+      <c r="AG71" s="60"/>
+      <c r="AH71" s="60"/>
+      <c r="AI71" s="60"/>
+      <c r="AJ71" s="60"/>
+      <c r="AK71" s="60"/>
+      <c r="AL71" s="60"/>
+      <c r="AM71" s="60"/>
+      <c r="AN71" s="60"/>
+      <c r="AO71" s="61"/>
+      <c r="AP71" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="AQ49" s="60"/>
-      <c r="AR49" s="61"/>
-      <c r="AS49" s="59" t="s">
+      <c r="AQ71" s="60"/>
+      <c r="AR71" s="61"/>
+      <c r="AS71" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="AT49" s="60"/>
-      <c r="AU49" s="60"/>
-      <c r="AV49" s="60"/>
-      <c r="AW49" s="61"/>
-      <c r="AX49" s="59" t="s">
+      <c r="AT71" s="60"/>
+      <c r="AU71" s="60"/>
+      <c r="AV71" s="60"/>
+      <c r="AW71" s="61"/>
+      <c r="AX71" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY49" s="60"/>
-      <c r="AZ49" s="60"/>
-      <c r="BA49" s="60"/>
-      <c r="BB49" s="60"/>
-      <c r="BC49" s="60"/>
-      <c r="BD49" s="60"/>
-      <c r="BE49" s="60"/>
-      <c r="BF49" s="60"/>
-      <c r="BG49" s="60"/>
-      <c r="BH49" s="60"/>
-      <c r="BI49" s="60"/>
-      <c r="BJ49" s="60"/>
-      <c r="BK49" s="60"/>
-      <c r="BL49" s="61"/>
-      <c r="BM49" s="59" t="s">
+      <c r="AY71" s="60"/>
+      <c r="AZ71" s="60"/>
+      <c r="BA71" s="60"/>
+      <c r="BB71" s="60"/>
+      <c r="BC71" s="60"/>
+      <c r="BD71" s="60"/>
+      <c r="BE71" s="60"/>
+      <c r="BF71" s="60"/>
+      <c r="BG71" s="60"/>
+      <c r="BH71" s="60"/>
+      <c r="BI71" s="60"/>
+      <c r="BJ71" s="60"/>
+      <c r="BK71" s="60"/>
+      <c r="BL71" s="61"/>
+      <c r="BM71" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="BN49" s="60"/>
-      <c r="BO49" s="60"/>
-      <c r="BP49" s="60"/>
-      <c r="BQ49" s="60"/>
-      <c r="BR49" s="60"/>
-      <c r="BS49" s="60"/>
-      <c r="BT49" s="60"/>
-      <c r="BU49" s="60"/>
-      <c r="BV49" s="60"/>
-      <c r="BW49" s="60"/>
-      <c r="BX49" s="60"/>
-      <c r="BY49" s="60"/>
-      <c r="BZ49" s="60"/>
-      <c r="CA49" s="60"/>
-      <c r="CB49" s="60"/>
-      <c r="CC49" s="60"/>
-      <c r="CD49" s="60"/>
-      <c r="CE49" s="60"/>
-      <c r="CF49" s="60"/>
-      <c r="CG49" s="60"/>
-      <c r="CH49" s="60"/>
-      <c r="CI49" s="67"/>
+      <c r="BN71" s="60"/>
+      <c r="BO71" s="60"/>
+      <c r="BP71" s="60"/>
+      <c r="BQ71" s="60"/>
+      <c r="BR71" s="60"/>
+      <c r="BS71" s="60"/>
+      <c r="BT71" s="60"/>
+      <c r="BU71" s="60"/>
+      <c r="BV71" s="60"/>
+      <c r="BW71" s="60"/>
+      <c r="BX71" s="60"/>
+      <c r="BY71" s="60"/>
+      <c r="BZ71" s="60"/>
+      <c r="CA71" s="60"/>
+      <c r="CB71" s="60"/>
+      <c r="CC71" s="60"/>
+      <c r="CD71" s="60"/>
+      <c r="CE71" s="60"/>
+      <c r="CF71" s="60"/>
+      <c r="CG71" s="60"/>
+      <c r="CH71" s="60"/>
+      <c r="CI71" s="67"/>
     </row>
-    <row r="50" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A50" s="79"/>
-      <c r="B50" s="73"/>
-      <c r="C50" s="45">
+    <row r="72" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A72" s="79"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="45">
         <v>12</v>
       </c>
-      <c r="D50" s="46"/>
-      <c r="E50" s="56" t="s">
+      <c r="D72" s="46"/>
+      <c r="E72" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="57"/>
-      <c r="K50" s="57"/>
-      <c r="L50" s="57"/>
-      <c r="M50" s="57"/>
-      <c r="N50" s="58"/>
-      <c r="O50" s="56" t="s">
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="57"/>
+      <c r="L72" s="57"/>
+      <c r="M72" s="57"/>
+      <c r="N72" s="58"/>
+      <c r="O72" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="P50" s="57"/>
-      <c r="Q50" s="57"/>
-      <c r="R50" s="57"/>
-      <c r="S50" s="57"/>
-      <c r="T50" s="57"/>
-      <c r="U50" s="57"/>
-      <c r="V50" s="57"/>
-      <c r="W50" s="57"/>
-      <c r="X50" s="57"/>
-      <c r="Y50" s="57"/>
-      <c r="Z50" s="57"/>
-      <c r="AA50" s="57"/>
-      <c r="AB50" s="57"/>
-      <c r="AC50" s="57"/>
-      <c r="AD50" s="57"/>
-      <c r="AE50" s="57"/>
-      <c r="AF50" s="57"/>
-      <c r="AG50" s="57"/>
-      <c r="AH50" s="57"/>
-      <c r="AI50" s="57"/>
-      <c r="AJ50" s="57"/>
-      <c r="AK50" s="57"/>
-      <c r="AL50" s="57"/>
-      <c r="AM50" s="57"/>
-      <c r="AN50" s="57"/>
-      <c r="AO50" s="58"/>
-      <c r="AP50" s="56" t="s">
+      <c r="P72" s="57"/>
+      <c r="Q72" s="57"/>
+      <c r="R72" s="57"/>
+      <c r="S72" s="57"/>
+      <c r="T72" s="57"/>
+      <c r="U72" s="57"/>
+      <c r="V72" s="57"/>
+      <c r="W72" s="57"/>
+      <c r="X72" s="57"/>
+      <c r="Y72" s="57"/>
+      <c r="Z72" s="57"/>
+      <c r="AA72" s="57"/>
+      <c r="AB72" s="57"/>
+      <c r="AC72" s="57"/>
+      <c r="AD72" s="57"/>
+      <c r="AE72" s="57"/>
+      <c r="AF72" s="57"/>
+      <c r="AG72" s="57"/>
+      <c r="AH72" s="57"/>
+      <c r="AI72" s="57"/>
+      <c r="AJ72" s="57"/>
+      <c r="AK72" s="57"/>
+      <c r="AL72" s="57"/>
+      <c r="AM72" s="57"/>
+      <c r="AN72" s="57"/>
+      <c r="AO72" s="58"/>
+      <c r="AP72" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AQ50" s="57"/>
-      <c r="AR50" s="58"/>
-      <c r="AS50" s="56" t="s">
+      <c r="AQ72" s="57"/>
+      <c r="AR72" s="58"/>
+      <c r="AS72" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="AT50" s="57"/>
-      <c r="AU50" s="57"/>
-      <c r="AV50" s="57"/>
-      <c r="AW50" s="58"/>
-      <c r="AX50" s="56" t="s">
+      <c r="AT72" s="57"/>
+      <c r="AU72" s="57"/>
+      <c r="AV72" s="57"/>
+      <c r="AW72" s="58"/>
+      <c r="AX72" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY50" s="57"/>
-      <c r="AZ50" s="57"/>
-      <c r="BA50" s="57"/>
-      <c r="BB50" s="57"/>
-      <c r="BC50" s="57"/>
-      <c r="BD50" s="57"/>
-      <c r="BE50" s="57"/>
-      <c r="BF50" s="57"/>
-      <c r="BG50" s="57"/>
-      <c r="BH50" s="57"/>
-      <c r="BI50" s="57"/>
-      <c r="BJ50" s="57"/>
-      <c r="BK50" s="57"/>
-      <c r="BL50" s="58"/>
-      <c r="BM50" s="56" t="s">
+      <c r="AY72" s="57"/>
+      <c r="AZ72" s="57"/>
+      <c r="BA72" s="57"/>
+      <c r="BB72" s="57"/>
+      <c r="BC72" s="57"/>
+      <c r="BD72" s="57"/>
+      <c r="BE72" s="57"/>
+      <c r="BF72" s="57"/>
+      <c r="BG72" s="57"/>
+      <c r="BH72" s="57"/>
+      <c r="BI72" s="57"/>
+      <c r="BJ72" s="57"/>
+      <c r="BK72" s="57"/>
+      <c r="BL72" s="58"/>
+      <c r="BM72" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="BN50" s="57"/>
-      <c r="BO50" s="57"/>
-      <c r="BP50" s="57"/>
-      <c r="BQ50" s="57"/>
-      <c r="BR50" s="57"/>
-      <c r="BS50" s="57"/>
-      <c r="BT50" s="57"/>
-      <c r="BU50" s="57"/>
-      <c r="BV50" s="57"/>
-      <c r="BW50" s="57"/>
-      <c r="BX50" s="57"/>
-      <c r="BY50" s="57"/>
-      <c r="BZ50" s="57"/>
-      <c r="CA50" s="57"/>
-      <c r="CB50" s="57"/>
-      <c r="CC50" s="57"/>
-      <c r="CD50" s="57"/>
-      <c r="CE50" s="57"/>
-      <c r="CF50" s="57"/>
-      <c r="CG50" s="57"/>
-      <c r="CH50" s="57"/>
-      <c r="CI50" s="66"/>
+      <c r="BN72" s="57"/>
+      <c r="BO72" s="57"/>
+      <c r="BP72" s="57"/>
+      <c r="BQ72" s="57"/>
+      <c r="BR72" s="57"/>
+      <c r="BS72" s="57"/>
+      <c r="BT72" s="57"/>
+      <c r="BU72" s="57"/>
+      <c r="BV72" s="57"/>
+      <c r="BW72" s="57"/>
+      <c r="BX72" s="57"/>
+      <c r="BY72" s="57"/>
+      <c r="BZ72" s="57"/>
+      <c r="CA72" s="57"/>
+      <c r="CB72" s="57"/>
+      <c r="CC72" s="57"/>
+      <c r="CD72" s="57"/>
+      <c r="CE72" s="57"/>
+      <c r="CF72" s="57"/>
+      <c r="CG72" s="57"/>
+      <c r="CH72" s="57"/>
+      <c r="CI72" s="66"/>
     </row>
-    <row r="51" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A51" s="80"/>
-      <c r="B51" s="74"/>
-      <c r="C51" s="51">
+    <row r="73" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A73" s="79"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="49">
         <v>13</v>
       </c>
-      <c r="D51" s="52"/>
-      <c r="E51" s="62" t="s">
+      <c r="D73" s="50"/>
+      <c r="E73" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="F51" s="63"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="63"/>
-      <c r="I51" s="63"/>
-      <c r="J51" s="63"/>
-      <c r="K51" s="63"/>
-      <c r="L51" s="63"/>
-      <c r="M51" s="63"/>
-      <c r="N51" s="64"/>
-      <c r="O51" s="62" t="s">
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
+      <c r="J73" s="60"/>
+      <c r="K73" s="60"/>
+      <c r="L73" s="60"/>
+      <c r="M73" s="60"/>
+      <c r="N73" s="61"/>
+      <c r="O73" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="P51" s="63"/>
-      <c r="Q51" s="63"/>
-      <c r="R51" s="63"/>
-      <c r="S51" s="63"/>
-      <c r="T51" s="63"/>
-      <c r="U51" s="63"/>
-      <c r="V51" s="63"/>
-      <c r="W51" s="63"/>
-      <c r="X51" s="63"/>
-      <c r="Y51" s="63"/>
-      <c r="Z51" s="63"/>
-      <c r="AA51" s="63"/>
-      <c r="AB51" s="63"/>
-      <c r="AC51" s="63"/>
-      <c r="AD51" s="63"/>
-      <c r="AE51" s="63"/>
-      <c r="AF51" s="63"/>
-      <c r="AG51" s="63"/>
-      <c r="AH51" s="63"/>
-      <c r="AI51" s="63"/>
-      <c r="AJ51" s="63"/>
-      <c r="AK51" s="63"/>
-      <c r="AL51" s="63"/>
-      <c r="AM51" s="63"/>
-      <c r="AN51" s="63"/>
-      <c r="AO51" s="64"/>
-      <c r="AP51" s="62" t="s">
+      <c r="P73" s="60"/>
+      <c r="Q73" s="60"/>
+      <c r="R73" s="60"/>
+      <c r="S73" s="60"/>
+      <c r="T73" s="60"/>
+      <c r="U73" s="60"/>
+      <c r="V73" s="60"/>
+      <c r="W73" s="60"/>
+      <c r="X73" s="60"/>
+      <c r="Y73" s="60"/>
+      <c r="Z73" s="60"/>
+      <c r="AA73" s="60"/>
+      <c r="AB73" s="60"/>
+      <c r="AC73" s="60"/>
+      <c r="AD73" s="60"/>
+      <c r="AE73" s="60"/>
+      <c r="AF73" s="60"/>
+      <c r="AG73" s="60"/>
+      <c r="AH73" s="60"/>
+      <c r="AI73" s="60"/>
+      <c r="AJ73" s="60"/>
+      <c r="AK73" s="60"/>
+      <c r="AL73" s="60"/>
+      <c r="AM73" s="60"/>
+      <c r="AN73" s="60"/>
+      <c r="AO73" s="61"/>
+      <c r="AP73" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AQ51" s="63"/>
-      <c r="AR51" s="64"/>
-      <c r="AS51" s="62" t="s">
+      <c r="AQ73" s="60"/>
+      <c r="AR73" s="61"/>
+      <c r="AS73" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="AT51" s="63"/>
-      <c r="AU51" s="63"/>
-      <c r="AV51" s="63"/>
-      <c r="AW51" s="64"/>
-      <c r="AX51" s="62" t="s">
+      <c r="AT73" s="60"/>
+      <c r="AU73" s="60"/>
+      <c r="AV73" s="60"/>
+      <c r="AW73" s="61"/>
+      <c r="AX73" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY51" s="63"/>
-      <c r="AZ51" s="63"/>
-      <c r="BA51" s="63"/>
-      <c r="BB51" s="63"/>
-      <c r="BC51" s="63"/>
-      <c r="BD51" s="63"/>
-      <c r="BE51" s="63"/>
-      <c r="BF51" s="63"/>
-      <c r="BG51" s="63"/>
-      <c r="BH51" s="63"/>
-      <c r="BI51" s="63"/>
-      <c r="BJ51" s="63"/>
-      <c r="BK51" s="63"/>
-      <c r="BL51" s="64"/>
-      <c r="BM51" s="62" t="s">
+      <c r="AY73" s="60"/>
+      <c r="AZ73" s="60"/>
+      <c r="BA73" s="60"/>
+      <c r="BB73" s="60"/>
+      <c r="BC73" s="60"/>
+      <c r="BD73" s="60"/>
+      <c r="BE73" s="60"/>
+      <c r="BF73" s="60"/>
+      <c r="BG73" s="60"/>
+      <c r="BH73" s="60"/>
+      <c r="BI73" s="60"/>
+      <c r="BJ73" s="60"/>
+      <c r="BK73" s="60"/>
+      <c r="BL73" s="61"/>
+      <c r="BM73" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="BN51" s="63"/>
-      <c r="BO51" s="63"/>
-      <c r="BP51" s="63"/>
-      <c r="BQ51" s="63"/>
-      <c r="BR51" s="63"/>
-      <c r="BS51" s="63"/>
-      <c r="BT51" s="63"/>
-      <c r="BU51" s="63"/>
-      <c r="BV51" s="63"/>
-      <c r="BW51" s="63"/>
-      <c r="BX51" s="63"/>
-      <c r="BY51" s="63"/>
-      <c r="BZ51" s="63"/>
-      <c r="CA51" s="63"/>
-      <c r="CB51" s="63"/>
-      <c r="CC51" s="63"/>
-      <c r="CD51" s="63"/>
-      <c r="CE51" s="63"/>
-      <c r="CF51" s="63"/>
-      <c r="CG51" s="63"/>
-      <c r="CH51" s="63"/>
-      <c r="CI51" s="68"/>
+      <c r="BN73" s="60"/>
+      <c r="BO73" s="60"/>
+      <c r="BP73" s="60"/>
+      <c r="BQ73" s="60"/>
+      <c r="BR73" s="60"/>
+      <c r="BS73" s="60"/>
+      <c r="BT73" s="60"/>
+      <c r="BU73" s="60"/>
+      <c r="BV73" s="60"/>
+      <c r="BW73" s="60"/>
+      <c r="BX73" s="60"/>
+      <c r="BY73" s="60"/>
+      <c r="BZ73" s="60"/>
+      <c r="CA73" s="60"/>
+      <c r="CB73" s="60"/>
+      <c r="CC73" s="60"/>
+      <c r="CD73" s="60"/>
+      <c r="CE73" s="60"/>
+      <c r="CF73" s="60"/>
+      <c r="CG73" s="60"/>
+      <c r="CH73" s="60"/>
+      <c r="CI73" s="67"/>
     </row>
-    <row r="52" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A52" s="81"/>
-      <c r="B52" s="82"/>
-      <c r="C52" s="82"/>
-      <c r="D52" s="82"/>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
-      <c r="H52" s="82"/>
-      <c r="I52" s="82"/>
-      <c r="J52" s="82"/>
-      <c r="K52" s="82"/>
-      <c r="L52" s="82"/>
-      <c r="M52" s="82"/>
-      <c r="N52" s="82"/>
-      <c r="O52" s="82"/>
-      <c r="P52" s="82"/>
-      <c r="Q52" s="82"/>
-      <c r="R52" s="82"/>
-      <c r="S52" s="82"/>
-      <c r="T52" s="82"/>
-      <c r="U52" s="82"/>
-      <c r="V52" s="82"/>
-      <c r="W52" s="82"/>
-      <c r="X52" s="82"/>
-      <c r="Y52" s="82"/>
-      <c r="Z52" s="82"/>
-      <c r="AA52" s="82"/>
-      <c r="AB52" s="82"/>
-      <c r="AC52" s="82"/>
-      <c r="AD52" s="82"/>
-      <c r="AE52" s="82"/>
-      <c r="AF52" s="82"/>
-      <c r="AG52" s="82"/>
-      <c r="AH52" s="82"/>
-      <c r="AI52" s="82"/>
-      <c r="AJ52" s="82"/>
-      <c r="AK52" s="82"/>
-      <c r="AL52" s="82"/>
-      <c r="AM52" s="82"/>
-      <c r="AN52" s="82"/>
-      <c r="AO52" s="82"/>
-      <c r="AP52" s="82"/>
-      <c r="AQ52" s="82"/>
-      <c r="AR52" s="82"/>
-      <c r="AS52" s="82"/>
-      <c r="AT52" s="82"/>
-      <c r="AU52" s="82"/>
-      <c r="AV52" s="82"/>
-      <c r="AW52" s="82"/>
-      <c r="AX52" s="82"/>
-      <c r="AY52" s="82"/>
-      <c r="AZ52" s="82"/>
-      <c r="BA52" s="82"/>
-      <c r="BB52" s="82"/>
-      <c r="BC52" s="82"/>
-      <c r="BD52" s="82"/>
-      <c r="BE52" s="82"/>
-      <c r="BF52" s="82"/>
-      <c r="BG52" s="82"/>
-      <c r="BH52" s="82"/>
-      <c r="BI52" s="82"/>
-      <c r="BJ52" s="82"/>
-      <c r="BK52" s="82"/>
-      <c r="BL52" s="82"/>
-      <c r="BM52" s="82"/>
-      <c r="BN52" s="82"/>
-      <c r="BO52" s="82"/>
-      <c r="BP52" s="82"/>
-      <c r="BQ52" s="82"/>
-      <c r="BR52" s="82"/>
-      <c r="BS52" s="82"/>
-      <c r="BT52" s="82"/>
-      <c r="BU52" s="82"/>
-      <c r="BV52" s="82"/>
-      <c r="BW52" s="82"/>
-      <c r="BX52" s="82"/>
-      <c r="BY52" s="82"/>
-      <c r="BZ52" s="82"/>
-      <c r="CA52" s="82"/>
-      <c r="CB52" s="82"/>
-      <c r="CC52" s="82"/>
-      <c r="CD52" s="82"/>
-      <c r="CE52" s="82"/>
-      <c r="CF52" s="82"/>
-      <c r="CG52" s="82"/>
-      <c r="CH52" s="82"/>
-      <c r="CI52" s="83"/>
+    <row r="74" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A74" s="79"/>
+      <c r="B74" s="73"/>
+      <c r="C74" s="45">
+        <v>14</v>
+      </c>
+      <c r="D74" s="46"/>
+      <c r="E74" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="F74" s="57"/>
+      <c r="G74" s="57"/>
+      <c r="H74" s="57"/>
+      <c r="I74" s="57"/>
+      <c r="J74" s="57"/>
+      <c r="K74" s="57"/>
+      <c r="L74" s="57"/>
+      <c r="M74" s="57"/>
+      <c r="N74" s="58"/>
+      <c r="O74" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="P74" s="57"/>
+      <c r="Q74" s="57"/>
+      <c r="R74" s="57"/>
+      <c r="S74" s="57"/>
+      <c r="T74" s="57"/>
+      <c r="U74" s="57"/>
+      <c r="V74" s="57"/>
+      <c r="W74" s="57"/>
+      <c r="X74" s="57"/>
+      <c r="Y74" s="57"/>
+      <c r="Z74" s="57"/>
+      <c r="AA74" s="57"/>
+      <c r="AB74" s="57"/>
+      <c r="AC74" s="57"/>
+      <c r="AD74" s="57"/>
+      <c r="AE74" s="57"/>
+      <c r="AF74" s="57"/>
+      <c r="AG74" s="57"/>
+      <c r="AH74" s="57"/>
+      <c r="AI74" s="57"/>
+      <c r="AJ74" s="57"/>
+      <c r="AK74" s="57"/>
+      <c r="AL74" s="57"/>
+      <c r="AM74" s="57"/>
+      <c r="AN74" s="57"/>
+      <c r="AO74" s="58"/>
+      <c r="AP74" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ74" s="57"/>
+      <c r="AR74" s="58"/>
+      <c r="AS74" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT74" s="57"/>
+      <c r="AU74" s="57"/>
+      <c r="AV74" s="57"/>
+      <c r="AW74" s="58"/>
+      <c r="AX74" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY74" s="57"/>
+      <c r="AZ74" s="57"/>
+      <c r="BA74" s="57"/>
+      <c r="BB74" s="57"/>
+      <c r="BC74" s="57"/>
+      <c r="BD74" s="57"/>
+      <c r="BE74" s="57"/>
+      <c r="BF74" s="57"/>
+      <c r="BG74" s="57"/>
+      <c r="BH74" s="57"/>
+      <c r="BI74" s="57"/>
+      <c r="BJ74" s="57"/>
+      <c r="BK74" s="57"/>
+      <c r="BL74" s="58"/>
+      <c r="BM74" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="BN74" s="57"/>
+      <c r="BO74" s="57"/>
+      <c r="BP74" s="57"/>
+      <c r="BQ74" s="57"/>
+      <c r="BR74" s="57"/>
+      <c r="BS74" s="57"/>
+      <c r="BT74" s="57"/>
+      <c r="BU74" s="57"/>
+      <c r="BV74" s="57"/>
+      <c r="BW74" s="57"/>
+      <c r="BX74" s="57"/>
+      <c r="BY74" s="57"/>
+      <c r="BZ74" s="57"/>
+      <c r="CA74" s="57"/>
+      <c r="CB74" s="57"/>
+      <c r="CC74" s="57"/>
+      <c r="CD74" s="57"/>
+      <c r="CE74" s="57"/>
+      <c r="CF74" s="57"/>
+      <c r="CG74" s="57"/>
+      <c r="CH74" s="57"/>
+      <c r="CI74" s="66"/>
     </row>
-    <row r="53" spans="1:87" ht="19.5" thickTop="1"/>
+    <row r="75" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A75" s="80"/>
+      <c r="B75" s="74"/>
+      <c r="C75" s="51">
+        <v>15</v>
+      </c>
+      <c r="D75" s="52"/>
+      <c r="E75" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="F75" s="63"/>
+      <c r="G75" s="63"/>
+      <c r="H75" s="63"/>
+      <c r="I75" s="63"/>
+      <c r="J75" s="63"/>
+      <c r="K75" s="63"/>
+      <c r="L75" s="63"/>
+      <c r="M75" s="63"/>
+      <c r="N75" s="64"/>
+      <c r="O75" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="P75" s="63"/>
+      <c r="Q75" s="63"/>
+      <c r="R75" s="63"/>
+      <c r="S75" s="63"/>
+      <c r="T75" s="63"/>
+      <c r="U75" s="63"/>
+      <c r="V75" s="63"/>
+      <c r="W75" s="63"/>
+      <c r="X75" s="63"/>
+      <c r="Y75" s="63"/>
+      <c r="Z75" s="63"/>
+      <c r="AA75" s="63"/>
+      <c r="AB75" s="63"/>
+      <c r="AC75" s="63"/>
+      <c r="AD75" s="63"/>
+      <c r="AE75" s="63"/>
+      <c r="AF75" s="63"/>
+      <c r="AG75" s="63"/>
+      <c r="AH75" s="63"/>
+      <c r="AI75" s="63"/>
+      <c r="AJ75" s="63"/>
+      <c r="AK75" s="63"/>
+      <c r="AL75" s="63"/>
+      <c r="AM75" s="63"/>
+      <c r="AN75" s="63"/>
+      <c r="AO75" s="64"/>
+      <c r="AP75" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ75" s="63"/>
+      <c r="AR75" s="64"/>
+      <c r="AS75" s="62" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT75" s="63"/>
+      <c r="AU75" s="63"/>
+      <c r="AV75" s="63"/>
+      <c r="AW75" s="64"/>
+      <c r="AX75" s="62" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY75" s="63"/>
+      <c r="AZ75" s="63"/>
+      <c r="BA75" s="63"/>
+      <c r="BB75" s="63"/>
+      <c r="BC75" s="63"/>
+      <c r="BD75" s="63"/>
+      <c r="BE75" s="63"/>
+      <c r="BF75" s="63"/>
+      <c r="BG75" s="63"/>
+      <c r="BH75" s="63"/>
+      <c r="BI75" s="63"/>
+      <c r="BJ75" s="63"/>
+      <c r="BK75" s="63"/>
+      <c r="BL75" s="64"/>
+      <c r="BM75" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="BN75" s="63"/>
+      <c r="BO75" s="63"/>
+      <c r="BP75" s="63"/>
+      <c r="BQ75" s="63"/>
+      <c r="BR75" s="63"/>
+      <c r="BS75" s="63"/>
+      <c r="BT75" s="63"/>
+      <c r="BU75" s="63"/>
+      <c r="BV75" s="63"/>
+      <c r="BW75" s="63"/>
+      <c r="BX75" s="63"/>
+      <c r="BY75" s="63"/>
+      <c r="BZ75" s="63"/>
+      <c r="CA75" s="63"/>
+      <c r="CB75" s="63"/>
+      <c r="CC75" s="63"/>
+      <c r="CD75" s="63"/>
+      <c r="CE75" s="63"/>
+      <c r="CF75" s="63"/>
+      <c r="CG75" s="63"/>
+      <c r="CH75" s="63"/>
+      <c r="CI75" s="68"/>
+    </row>
+    <row r="76" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A76" s="81"/>
+      <c r="B76" s="82"/>
+      <c r="C76" s="82"/>
+      <c r="D76" s="82"/>
+      <c r="E76" s="82"/>
+      <c r="F76" s="82"/>
+      <c r="G76" s="82"/>
+      <c r="H76" s="82"/>
+      <c r="I76" s="82"/>
+      <c r="J76" s="82"/>
+      <c r="K76" s="82"/>
+      <c r="L76" s="82"/>
+      <c r="M76" s="82"/>
+      <c r="N76" s="82"/>
+      <c r="O76" s="82"/>
+      <c r="P76" s="82"/>
+      <c r="Q76" s="82"/>
+      <c r="R76" s="82"/>
+      <c r="S76" s="82"/>
+      <c r="T76" s="82"/>
+      <c r="U76" s="82"/>
+      <c r="V76" s="82"/>
+      <c r="W76" s="82"/>
+      <c r="X76" s="82"/>
+      <c r="Y76" s="82"/>
+      <c r="Z76" s="82"/>
+      <c r="AA76" s="82"/>
+      <c r="AB76" s="82"/>
+      <c r="AC76" s="82"/>
+      <c r="AD76" s="82"/>
+      <c r="AE76" s="82"/>
+      <c r="AF76" s="82"/>
+      <c r="AG76" s="82"/>
+      <c r="AH76" s="82"/>
+      <c r="AI76" s="82"/>
+      <c r="AJ76" s="82"/>
+      <c r="AK76" s="82"/>
+      <c r="AL76" s="82"/>
+      <c r="AM76" s="82"/>
+      <c r="AN76" s="82"/>
+      <c r="AO76" s="82"/>
+      <c r="AP76" s="82"/>
+      <c r="AQ76" s="82"/>
+      <c r="AR76" s="82"/>
+      <c r="AS76" s="82"/>
+      <c r="AT76" s="82"/>
+      <c r="AU76" s="82"/>
+      <c r="AV76" s="82"/>
+      <c r="AW76" s="82"/>
+      <c r="AX76" s="82"/>
+      <c r="AY76" s="82"/>
+      <c r="AZ76" s="82"/>
+      <c r="BA76" s="82"/>
+      <c r="BB76" s="82"/>
+      <c r="BC76" s="82"/>
+      <c r="BD76" s="82"/>
+      <c r="BE76" s="82"/>
+      <c r="BF76" s="82"/>
+      <c r="BG76" s="82"/>
+      <c r="BH76" s="82"/>
+      <c r="BI76" s="82"/>
+      <c r="BJ76" s="82"/>
+      <c r="BK76" s="82"/>
+      <c r="BL76" s="82"/>
+      <c r="BM76" s="82"/>
+      <c r="BN76" s="82"/>
+      <c r="BO76" s="82"/>
+      <c r="BP76" s="82"/>
+      <c r="BQ76" s="82"/>
+      <c r="BR76" s="82"/>
+      <c r="BS76" s="82"/>
+      <c r="BT76" s="82"/>
+      <c r="BU76" s="82"/>
+      <c r="BV76" s="82"/>
+      <c r="BW76" s="82"/>
+      <c r="BX76" s="82"/>
+      <c r="BY76" s="82"/>
+      <c r="BZ76" s="82"/>
+      <c r="CA76" s="82"/>
+      <c r="CB76" s="82"/>
+      <c r="CC76" s="82"/>
+      <c r="CD76" s="82"/>
+      <c r="CE76" s="82"/>
+      <c r="CF76" s="82"/>
+      <c r="CG76" s="82"/>
+      <c r="CH76" s="82"/>
+      <c r="CI76" s="83"/>
+    </row>
+    <row r="77" spans="1:87" ht="19.5" thickTop="1"/>
   </sheetData>
-  <mergeCells count="125">
-    <mergeCell ref="B37:CI37"/>
-    <mergeCell ref="B38:B51"/>
-    <mergeCell ref="A35:CI35"/>
-    <mergeCell ref="A36:A51"/>
-    <mergeCell ref="A52:CI52"/>
-    <mergeCell ref="AX44:BL44"/>
-    <mergeCell ref="AX43:BL43"/>
-    <mergeCell ref="BM49:CI49"/>
-    <mergeCell ref="BM48:CI48"/>
-    <mergeCell ref="BM47:CI47"/>
-    <mergeCell ref="BM46:CI46"/>
-    <mergeCell ref="BM45:CI45"/>
-    <mergeCell ref="BM44:CI44"/>
-    <mergeCell ref="BM43:CI43"/>
-    <mergeCell ref="AX49:BL49"/>
-    <mergeCell ref="AX48:BL48"/>
-    <mergeCell ref="AX47:BL47"/>
-    <mergeCell ref="AX46:BL46"/>
-    <mergeCell ref="AX45:BL45"/>
-    <mergeCell ref="AP45:AR45"/>
-    <mergeCell ref="AP44:AR44"/>
-    <mergeCell ref="AP43:AR43"/>
-    <mergeCell ref="AS49:AW49"/>
-    <mergeCell ref="AS48:AW48"/>
-    <mergeCell ref="AS47:AW47"/>
-    <mergeCell ref="AS46:AW46"/>
-    <mergeCell ref="AS45:AW45"/>
-    <mergeCell ref="AS44:AW44"/>
-    <mergeCell ref="AS43:AW43"/>
-    <mergeCell ref="O46:AO46"/>
-    <mergeCell ref="O47:AO47"/>
-    <mergeCell ref="O48:AO48"/>
-    <mergeCell ref="O49:AO49"/>
-    <mergeCell ref="AP49:AR49"/>
-    <mergeCell ref="AP48:AR48"/>
-    <mergeCell ref="AP47:AR47"/>
-    <mergeCell ref="AP46:AR46"/>
-    <mergeCell ref="E44:N44"/>
-    <mergeCell ref="E43:N43"/>
-    <mergeCell ref="O43:AO43"/>
-    <mergeCell ref="O44:AO44"/>
-    <mergeCell ref="O45:AO45"/>
-    <mergeCell ref="E49:N49"/>
-    <mergeCell ref="E48:N48"/>
-    <mergeCell ref="E47:N47"/>
-    <mergeCell ref="E46:N46"/>
-    <mergeCell ref="E45:N45"/>
-    <mergeCell ref="AX51:BL51"/>
-    <mergeCell ref="BM51:CI51"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E41:N41"/>
-    <mergeCell ref="E42:N42"/>
-    <mergeCell ref="O41:AO41"/>
-    <mergeCell ref="AP41:AR41"/>
-    <mergeCell ref="AS41:AW41"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:N51"/>
-    <mergeCell ref="O51:AO51"/>
-    <mergeCell ref="AP51:AR51"/>
-    <mergeCell ref="AS51:AW51"/>
-    <mergeCell ref="AX40:BL40"/>
-    <mergeCell ref="BM40:CI40"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E50:N50"/>
-    <mergeCell ref="O50:AO50"/>
-    <mergeCell ref="AP50:AR50"/>
-    <mergeCell ref="AS50:AW50"/>
-    <mergeCell ref="AX50:BL50"/>
-    <mergeCell ref="BM50:CI50"/>
-    <mergeCell ref="AX41:BL41"/>
-    <mergeCell ref="BM41:CI41"/>
-    <mergeCell ref="O42:AO42"/>
-    <mergeCell ref="AP42:AR42"/>
-    <mergeCell ref="AS42:AW42"/>
-    <mergeCell ref="AX42:BL42"/>
-    <mergeCell ref="BM42:CI42"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:N40"/>
-    <mergeCell ref="O40:AO40"/>
-    <mergeCell ref="AP40:AR40"/>
-    <mergeCell ref="AS40:AW40"/>
-    <mergeCell ref="AX38:BL38"/>
-    <mergeCell ref="BM38:CI38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:N39"/>
-    <mergeCell ref="O39:AO39"/>
-    <mergeCell ref="AP39:AR39"/>
-    <mergeCell ref="AS39:AW39"/>
-    <mergeCell ref="AX39:BL39"/>
-    <mergeCell ref="BM39:CI39"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="E38:N38"/>
-    <mergeCell ref="O38:AO38"/>
-    <mergeCell ref="AP38:AR38"/>
-    <mergeCell ref="AS38:AW38"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="H34:CI34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="I36:CI36"/>
+  <mergeCells count="139">
+    <mergeCell ref="AX73:BL73"/>
+    <mergeCell ref="AX74:BL74"/>
+    <mergeCell ref="BM73:CI73"/>
+    <mergeCell ref="BM74:CI74"/>
+    <mergeCell ref="B59:CI59"/>
+    <mergeCell ref="B60:B75"/>
+    <mergeCell ref="A57:CI57"/>
+    <mergeCell ref="A58:A75"/>
+    <mergeCell ref="A76:CI76"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="E73:N73"/>
+    <mergeCell ref="E74:N74"/>
+    <mergeCell ref="O73:AO73"/>
+    <mergeCell ref="O74:AO74"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="AP74:AR74"/>
+    <mergeCell ref="AS73:AW73"/>
+    <mergeCell ref="AS74:AW74"/>
+    <mergeCell ref="AX66:BL66"/>
+    <mergeCell ref="AX65:BL65"/>
+    <mergeCell ref="BM71:CI71"/>
+    <mergeCell ref="BM70:CI70"/>
+    <mergeCell ref="BM69:CI69"/>
+    <mergeCell ref="BM68:CI68"/>
+    <mergeCell ref="BM67:CI67"/>
+    <mergeCell ref="BM66:CI66"/>
+    <mergeCell ref="BM65:CI65"/>
+    <mergeCell ref="AX71:BL71"/>
+    <mergeCell ref="AX70:BL70"/>
+    <mergeCell ref="AX69:BL69"/>
+    <mergeCell ref="AX68:BL68"/>
+    <mergeCell ref="AX67:BL67"/>
+    <mergeCell ref="AP67:AR67"/>
+    <mergeCell ref="AP66:AR66"/>
+    <mergeCell ref="AP65:AR65"/>
+    <mergeCell ref="AS71:AW71"/>
+    <mergeCell ref="AS70:AW70"/>
+    <mergeCell ref="AS69:AW69"/>
+    <mergeCell ref="AS68:AW68"/>
+    <mergeCell ref="AS67:AW67"/>
+    <mergeCell ref="AS66:AW66"/>
+    <mergeCell ref="AS65:AW65"/>
+    <mergeCell ref="O68:AO68"/>
+    <mergeCell ref="O69:AO69"/>
+    <mergeCell ref="O70:AO70"/>
+    <mergeCell ref="O71:AO71"/>
+    <mergeCell ref="AP71:AR71"/>
+    <mergeCell ref="AP70:AR70"/>
+    <mergeCell ref="AP69:AR69"/>
+    <mergeCell ref="AP68:AR68"/>
+    <mergeCell ref="E66:N66"/>
+    <mergeCell ref="E65:N65"/>
+    <mergeCell ref="O65:AO65"/>
+    <mergeCell ref="O66:AO66"/>
+    <mergeCell ref="O67:AO67"/>
+    <mergeCell ref="E71:N71"/>
+    <mergeCell ref="E70:N70"/>
+    <mergeCell ref="E69:N69"/>
+    <mergeCell ref="E68:N68"/>
+    <mergeCell ref="E67:N67"/>
+    <mergeCell ref="AX75:BL75"/>
+    <mergeCell ref="BM75:CI75"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E63:N63"/>
+    <mergeCell ref="E64:N64"/>
+    <mergeCell ref="O63:AO63"/>
+    <mergeCell ref="AP63:AR63"/>
+    <mergeCell ref="AS63:AW63"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="E75:N75"/>
+    <mergeCell ref="O75:AO75"/>
+    <mergeCell ref="AP75:AR75"/>
+    <mergeCell ref="AS75:AW75"/>
+    <mergeCell ref="AX62:BL62"/>
+    <mergeCell ref="BM62:CI62"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E72:N72"/>
+    <mergeCell ref="O72:AO72"/>
+    <mergeCell ref="AP72:AR72"/>
+    <mergeCell ref="AS72:AW72"/>
+    <mergeCell ref="AX72:BL72"/>
+    <mergeCell ref="BM72:CI72"/>
+    <mergeCell ref="AX63:BL63"/>
+    <mergeCell ref="BM63:CI63"/>
+    <mergeCell ref="O64:AO64"/>
+    <mergeCell ref="AP64:AR64"/>
+    <mergeCell ref="AS64:AW64"/>
+    <mergeCell ref="AX64:BL64"/>
+    <mergeCell ref="BM64:CI64"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:N62"/>
+    <mergeCell ref="O62:AO62"/>
+    <mergeCell ref="AP62:AR62"/>
+    <mergeCell ref="AS62:AW62"/>
+    <mergeCell ref="AX60:BL60"/>
+    <mergeCell ref="BM60:CI60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:N61"/>
+    <mergeCell ref="O61:AO61"/>
+    <mergeCell ref="AP61:AR61"/>
+    <mergeCell ref="AS61:AW61"/>
+    <mergeCell ref="AX61:BL61"/>
+    <mergeCell ref="BM61:CI61"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:N60"/>
+    <mergeCell ref="O60:AO60"/>
+    <mergeCell ref="AP60:AR60"/>
+    <mergeCell ref="AS60:AW60"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="H56:CI56"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="I58:CI58"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:CI1"/>
     <mergeCell ref="A2:K2"/>

--- a/document/UI-001_VR内UI_画面仕様書.xlsx
+++ b/document/UI-001_VR内UI_画面仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tryro-dev-camera_sim\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CCF119-7FB1-4574-85AD-9DC3F41ED29C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3162D3CA-A063-4814-8D29-FFFDAC3EF6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2764,13 +2764,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>145675</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>145676</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>220358</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2814,15 +2814,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>141193</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>186018</xdr:rowOff>
+      <xdr:colOff>85163</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>100854</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>17928</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>85165</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>197222</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>29136</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2837,8 +2837,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1082487" y="7324165"/>
-          <a:ext cx="582706" cy="605118"/>
+          <a:off x="1026457" y="7709648"/>
+          <a:ext cx="582706" cy="634253"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2893,13 +2893,13 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>91886</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>159125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>203945</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>58272</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2971,13 +2971,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>136711</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>13447</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>13449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3049,13 +3049,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>42581</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>154642</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>154640</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>53790</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3118,6 +3118,71 @@
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
           </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>174811</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>73958</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>208429</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>107576</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="テキスト ボックス 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A27B1295-1678-48FF-99E3-C521F75D38AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1351429" y="7447429"/>
+          <a:ext cx="3563471" cy="504265"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>UI-003</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3389,7 +3454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CI77"/>
+  <dimension ref="A1:CI80"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="87" width="3.125" customWidth="1"/>
@@ -8229,7 +8294,7 @@
       <c r="CH54" s="84"/>
       <c r="CI54" s="85"/>
     </row>
-    <row r="55" spans="1:87" ht="19.5" thickBot="1">
+    <row r="55" spans="1:87">
       <c r="A55" s="84"/>
       <c r="B55" s="84"/>
       <c r="C55" s="84"/>
@@ -8318,2243 +8383,2510 @@
       <c r="CH55" s="84"/>
       <c r="CI55" s="85"/>
     </row>
-    <row r="56" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A56" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="27">
-        <v>2</v>
-      </c>
-      <c r="D56" s="28"/>
-      <c r="E56" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="30"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="I56" s="33"/>
-      <c r="J56" s="33"/>
-      <c r="K56" s="33"/>
-      <c r="L56" s="33"/>
-      <c r="M56" s="33"/>
-      <c r="N56" s="33"/>
-      <c r="O56" s="33"/>
-      <c r="P56" s="33"/>
-      <c r="Q56" s="33"/>
-      <c r="R56" s="33"/>
-      <c r="S56" s="33"/>
-      <c r="T56" s="33"/>
-      <c r="U56" s="33"/>
-      <c r="V56" s="33"/>
-      <c r="W56" s="33"/>
-      <c r="X56" s="33"/>
-      <c r="Y56" s="33"/>
-      <c r="Z56" s="33"/>
-      <c r="AA56" s="33"/>
-      <c r="AB56" s="33"/>
-      <c r="AC56" s="33"/>
-      <c r="AD56" s="33"/>
-      <c r="AE56" s="33"/>
-      <c r="AF56" s="33"/>
-      <c r="AG56" s="33"/>
-      <c r="AH56" s="33"/>
-      <c r="AI56" s="33"/>
-      <c r="AJ56" s="33"/>
-      <c r="AK56" s="33"/>
-      <c r="AL56" s="33"/>
-      <c r="AM56" s="33"/>
-      <c r="AN56" s="33"/>
-      <c r="AO56" s="33"/>
-      <c r="AP56" s="33"/>
-      <c r="AQ56" s="33"/>
-      <c r="AR56" s="33"/>
-      <c r="AS56" s="33"/>
-      <c r="AT56" s="33"/>
-      <c r="AU56" s="33"/>
-      <c r="AV56" s="33"/>
-      <c r="AW56" s="33"/>
-      <c r="AX56" s="33"/>
-      <c r="AY56" s="33"/>
-      <c r="AZ56" s="33"/>
-      <c r="BA56" s="33"/>
-      <c r="BB56" s="33"/>
-      <c r="BC56" s="33"/>
-      <c r="BD56" s="33"/>
-      <c r="BE56" s="33"/>
-      <c r="BF56" s="33"/>
-      <c r="BG56" s="33"/>
-      <c r="BH56" s="33"/>
-      <c r="BI56" s="33"/>
-      <c r="BJ56" s="33"/>
-      <c r="BK56" s="33"/>
-      <c r="BL56" s="33"/>
-      <c r="BM56" s="33"/>
-      <c r="BN56" s="33"/>
-      <c r="BO56" s="33"/>
-      <c r="BP56" s="33"/>
-      <c r="BQ56" s="33"/>
-      <c r="BR56" s="33"/>
-      <c r="BS56" s="33"/>
-      <c r="BT56" s="33"/>
-      <c r="BU56" s="33"/>
-      <c r="BV56" s="33"/>
-      <c r="BW56" s="33"/>
-      <c r="BX56" s="33"/>
-      <c r="BY56" s="33"/>
-      <c r="BZ56" s="33"/>
-      <c r="CA56" s="33"/>
-      <c r="CB56" s="33"/>
-      <c r="CC56" s="33"/>
-      <c r="CD56" s="33"/>
-      <c r="CE56" s="33"/>
-      <c r="CF56" s="33"/>
-      <c r="CG56" s="33"/>
-      <c r="CH56" s="33"/>
-      <c r="CI56" s="34"/>
+    <row r="56" spans="1:87">
+      <c r="A56" s="84"/>
+      <c r="B56" s="84"/>
+      <c r="C56" s="84"/>
+      <c r="D56" s="84"/>
+      <c r="E56" s="84"/>
+      <c r="F56" s="84"/>
+      <c r="G56" s="84"/>
+      <c r="H56" s="84"/>
+      <c r="I56" s="84"/>
+      <c r="J56" s="84"/>
+      <c r="K56" s="84"/>
+      <c r="L56" s="84"/>
+      <c r="M56" s="84"/>
+      <c r="N56" s="84"/>
+      <c r="O56" s="84"/>
+      <c r="P56" s="84"/>
+      <c r="Q56" s="84"/>
+      <c r="R56" s="84"/>
+      <c r="S56" s="84"/>
+      <c r="T56" s="84"/>
+      <c r="U56" s="84"/>
+      <c r="V56" s="84"/>
+      <c r="W56" s="84"/>
+      <c r="X56" s="84"/>
+      <c r="Y56" s="84"/>
+      <c r="Z56" s="84"/>
+      <c r="AA56" s="84"/>
+      <c r="AB56" s="84"/>
+      <c r="AC56" s="84"/>
+      <c r="AD56" s="84"/>
+      <c r="AE56" s="84"/>
+      <c r="AF56" s="84"/>
+      <c r="AG56" s="84"/>
+      <c r="AH56" s="84"/>
+      <c r="AI56" s="84"/>
+      <c r="AJ56" s="84"/>
+      <c r="AK56" s="84"/>
+      <c r="AL56" s="84"/>
+      <c r="AM56" s="84"/>
+      <c r="AN56" s="84"/>
+      <c r="AO56" s="84"/>
+      <c r="AP56" s="84"/>
+      <c r="AQ56" s="84"/>
+      <c r="AR56" s="84"/>
+      <c r="AS56" s="84"/>
+      <c r="AT56" s="84"/>
+      <c r="AU56" s="84"/>
+      <c r="AV56" s="84"/>
+      <c r="AW56" s="84"/>
+      <c r="AX56" s="84"/>
+      <c r="AY56" s="84"/>
+      <c r="AZ56" s="84"/>
+      <c r="BA56" s="84"/>
+      <c r="BB56" s="84"/>
+      <c r="BC56" s="84"/>
+      <c r="BD56" s="84"/>
+      <c r="BE56" s="84"/>
+      <c r="BF56" s="84"/>
+      <c r="BG56" s="84"/>
+      <c r="BH56" s="84"/>
+      <c r="BI56" s="84"/>
+      <c r="BJ56" s="84"/>
+      <c r="BK56" s="84"/>
+      <c r="BL56" s="84"/>
+      <c r="BM56" s="84"/>
+      <c r="BN56" s="84"/>
+      <c r="BO56" s="84"/>
+      <c r="BP56" s="84"/>
+      <c r="BQ56" s="84"/>
+      <c r="BR56" s="84"/>
+      <c r="BS56" s="84"/>
+      <c r="BT56" s="84"/>
+      <c r="BU56" s="84"/>
+      <c r="BV56" s="84"/>
+      <c r="BW56" s="84"/>
+      <c r="BX56" s="84"/>
+      <c r="BY56" s="84"/>
+      <c r="BZ56" s="84"/>
+      <c r="CA56" s="84"/>
+      <c r="CB56" s="84"/>
+      <c r="CC56" s="84"/>
+      <c r="CD56" s="84"/>
+      <c r="CE56" s="84"/>
+      <c r="CF56" s="84"/>
+      <c r="CG56" s="84"/>
+      <c r="CH56" s="84"/>
+      <c r="CI56" s="85"/>
     </row>
-    <row r="57" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A57" s="75"/>
-      <c r="B57" s="76"/>
-      <c r="C57" s="76"/>
-      <c r="D57" s="76"/>
-      <c r="E57" s="76"/>
-      <c r="F57" s="76"/>
-      <c r="G57" s="76"/>
-      <c r="H57" s="76"/>
-      <c r="I57" s="76"/>
-      <c r="J57" s="76"/>
-      <c r="K57" s="76"/>
-      <c r="L57" s="76"/>
-      <c r="M57" s="76"/>
-      <c r="N57" s="76"/>
-      <c r="O57" s="76"/>
-      <c r="P57" s="76"/>
-      <c r="Q57" s="76"/>
-      <c r="R57" s="76"/>
-      <c r="S57" s="76"/>
-      <c r="T57" s="76"/>
-      <c r="U57" s="76"/>
-      <c r="V57" s="76"/>
-      <c r="W57" s="76"/>
-      <c r="X57" s="76"/>
-      <c r="Y57" s="76"/>
-      <c r="Z57" s="76"/>
-      <c r="AA57" s="76"/>
-      <c r="AB57" s="76"/>
-      <c r="AC57" s="76"/>
-      <c r="AD57" s="76"/>
-      <c r="AE57" s="76"/>
-      <c r="AF57" s="76"/>
-      <c r="AG57" s="76"/>
-      <c r="AH57" s="76"/>
-      <c r="AI57" s="76"/>
-      <c r="AJ57" s="76"/>
-      <c r="AK57" s="76"/>
-      <c r="AL57" s="76"/>
-      <c r="AM57" s="76"/>
-      <c r="AN57" s="76"/>
-      <c r="AO57" s="76"/>
-      <c r="AP57" s="76"/>
-      <c r="AQ57" s="76"/>
-      <c r="AR57" s="76"/>
-      <c r="AS57" s="76"/>
-      <c r="AT57" s="76"/>
-      <c r="AU57" s="76"/>
-      <c r="AV57" s="76"/>
-      <c r="AW57" s="76"/>
-      <c r="AX57" s="76"/>
-      <c r="AY57" s="76"/>
-      <c r="AZ57" s="76"/>
-      <c r="BA57" s="76"/>
-      <c r="BB57" s="76"/>
-      <c r="BC57" s="76"/>
-      <c r="BD57" s="76"/>
-      <c r="BE57" s="76"/>
-      <c r="BF57" s="76"/>
-      <c r="BG57" s="76"/>
-      <c r="BH57" s="76"/>
-      <c r="BI57" s="76"/>
-      <c r="BJ57" s="76"/>
-      <c r="BK57" s="76"/>
-      <c r="BL57" s="76"/>
-      <c r="BM57" s="76"/>
-      <c r="BN57" s="76"/>
-      <c r="BO57" s="76"/>
-      <c r="BP57" s="76"/>
-      <c r="BQ57" s="76"/>
-      <c r="BR57" s="76"/>
-      <c r="BS57" s="76"/>
-      <c r="BT57" s="76"/>
-      <c r="BU57" s="76"/>
-      <c r="BV57" s="76"/>
-      <c r="BW57" s="76"/>
-      <c r="BX57" s="76"/>
-      <c r="BY57" s="76"/>
-      <c r="BZ57" s="76"/>
-      <c r="CA57" s="76"/>
-      <c r="CB57" s="76"/>
-      <c r="CC57" s="76"/>
-      <c r="CD57" s="76"/>
-      <c r="CE57" s="76"/>
-      <c r="CF57" s="76"/>
-      <c r="CG57" s="76"/>
-      <c r="CH57" s="76"/>
-      <c r="CI57" s="77"/>
+    <row r="57" spans="1:87">
+      <c r="A57" s="84"/>
+      <c r="B57" s="84"/>
+      <c r="C57" s="84"/>
+      <c r="D57" s="84"/>
+      <c r="E57" s="84"/>
+      <c r="F57" s="84"/>
+      <c r="G57" s="84"/>
+      <c r="H57" s="84"/>
+      <c r="I57" s="84"/>
+      <c r="J57" s="84"/>
+      <c r="K57" s="84"/>
+      <c r="L57" s="84"/>
+      <c r="M57" s="84"/>
+      <c r="N57" s="84"/>
+      <c r="O57" s="84"/>
+      <c r="P57" s="84"/>
+      <c r="Q57" s="84"/>
+      <c r="R57" s="84"/>
+      <c r="S57" s="84"/>
+      <c r="T57" s="84"/>
+      <c r="U57" s="84"/>
+      <c r="V57" s="84"/>
+      <c r="W57" s="84"/>
+      <c r="X57" s="84"/>
+      <c r="Y57" s="84"/>
+      <c r="Z57" s="84"/>
+      <c r="AA57" s="84"/>
+      <c r="AB57" s="84"/>
+      <c r="AC57" s="84"/>
+      <c r="AD57" s="84"/>
+      <c r="AE57" s="84"/>
+      <c r="AF57" s="84"/>
+      <c r="AG57" s="84"/>
+      <c r="AH57" s="84"/>
+      <c r="AI57" s="84"/>
+      <c r="AJ57" s="84"/>
+      <c r="AK57" s="84"/>
+      <c r="AL57" s="84"/>
+      <c r="AM57" s="84"/>
+      <c r="AN57" s="84"/>
+      <c r="AO57" s="84"/>
+      <c r="AP57" s="84"/>
+      <c r="AQ57" s="84"/>
+      <c r="AR57" s="84"/>
+      <c r="AS57" s="84"/>
+      <c r="AT57" s="84"/>
+      <c r="AU57" s="84"/>
+      <c r="AV57" s="84"/>
+      <c r="AW57" s="84"/>
+      <c r="AX57" s="84"/>
+      <c r="AY57" s="84"/>
+      <c r="AZ57" s="84"/>
+      <c r="BA57" s="84"/>
+      <c r="BB57" s="84"/>
+      <c r="BC57" s="84"/>
+      <c r="BD57" s="84"/>
+      <c r="BE57" s="84"/>
+      <c r="BF57" s="84"/>
+      <c r="BG57" s="84"/>
+      <c r="BH57" s="84"/>
+      <c r="BI57" s="84"/>
+      <c r="BJ57" s="84"/>
+      <c r="BK57" s="84"/>
+      <c r="BL57" s="84"/>
+      <c r="BM57" s="84"/>
+      <c r="BN57" s="84"/>
+      <c r="BO57" s="84"/>
+      <c r="BP57" s="84"/>
+      <c r="BQ57" s="84"/>
+      <c r="BR57" s="84"/>
+      <c r="BS57" s="84"/>
+      <c r="BT57" s="84"/>
+      <c r="BU57" s="84"/>
+      <c r="BV57" s="84"/>
+      <c r="BW57" s="84"/>
+      <c r="BX57" s="84"/>
+      <c r="BY57" s="84"/>
+      <c r="BZ57" s="84"/>
+      <c r="CA57" s="84"/>
+      <c r="CB57" s="84"/>
+      <c r="CC57" s="84"/>
+      <c r="CD57" s="84"/>
+      <c r="CE57" s="84"/>
+      <c r="CF57" s="84"/>
+      <c r="CG57" s="84"/>
+      <c r="CH57" s="84"/>
+      <c r="CI57" s="85"/>
     </row>
-    <row r="58" spans="1:87" ht="27" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A58" s="78"/>
-      <c r="B58" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="36"/>
-      <c r="D58" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="48"/>
-      <c r="F58" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="G58" s="38"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="J58" s="40"/>
-      <c r="K58" s="40"/>
-      <c r="L58" s="40"/>
-      <c r="M58" s="40"/>
-      <c r="N58" s="40"/>
-      <c r="O58" s="40"/>
-      <c r="P58" s="40"/>
-      <c r="Q58" s="40"/>
-      <c r="R58" s="40"/>
-      <c r="S58" s="40"/>
-      <c r="T58" s="40"/>
-      <c r="U58" s="40"/>
-      <c r="V58" s="40"/>
-      <c r="W58" s="40"/>
-      <c r="X58" s="40"/>
-      <c r="Y58" s="40"/>
-      <c r="Z58" s="40"/>
-      <c r="AA58" s="40"/>
-      <c r="AB58" s="40"/>
-      <c r="AC58" s="40"/>
-      <c r="AD58" s="40"/>
-      <c r="AE58" s="40"/>
-      <c r="AF58" s="40"/>
-      <c r="AG58" s="40"/>
-      <c r="AH58" s="40"/>
-      <c r="AI58" s="40"/>
-      <c r="AJ58" s="40"/>
-      <c r="AK58" s="40"/>
-      <c r="AL58" s="40"/>
-      <c r="AM58" s="40"/>
-      <c r="AN58" s="40"/>
-      <c r="AO58" s="40"/>
-      <c r="AP58" s="40"/>
-      <c r="AQ58" s="40"/>
-      <c r="AR58" s="40"/>
-      <c r="AS58" s="40"/>
-      <c r="AT58" s="40"/>
-      <c r="AU58" s="40"/>
-      <c r="AV58" s="40"/>
-      <c r="AW58" s="40"/>
-      <c r="AX58" s="40"/>
-      <c r="AY58" s="40"/>
-      <c r="AZ58" s="40"/>
-      <c r="BA58" s="40"/>
-      <c r="BB58" s="40"/>
-      <c r="BC58" s="40"/>
-      <c r="BD58" s="40"/>
-      <c r="BE58" s="40"/>
-      <c r="BF58" s="40"/>
-      <c r="BG58" s="40"/>
-      <c r="BH58" s="40"/>
-      <c r="BI58" s="40"/>
-      <c r="BJ58" s="40"/>
-      <c r="BK58" s="40"/>
-      <c r="BL58" s="40"/>
-      <c r="BM58" s="40"/>
-      <c r="BN58" s="40"/>
-      <c r="BO58" s="40"/>
-      <c r="BP58" s="40"/>
-      <c r="BQ58" s="40"/>
-      <c r="BR58" s="40"/>
-      <c r="BS58" s="40"/>
-      <c r="BT58" s="40"/>
-      <c r="BU58" s="40"/>
-      <c r="BV58" s="40"/>
-      <c r="BW58" s="40"/>
-      <c r="BX58" s="40"/>
-      <c r="BY58" s="40"/>
-      <c r="BZ58" s="40"/>
-      <c r="CA58" s="40"/>
-      <c r="CB58" s="40"/>
-      <c r="CC58" s="40"/>
-      <c r="CD58" s="40"/>
-      <c r="CE58" s="40"/>
-      <c r="CF58" s="40"/>
-      <c r="CG58" s="40"/>
-      <c r="CH58" s="40"/>
-      <c r="CI58" s="41"/>
+    <row r="58" spans="1:87" ht="19.5" thickBot="1">
+      <c r="A58" s="84"/>
+      <c r="B58" s="84"/>
+      <c r="C58" s="84"/>
+      <c r="D58" s="84"/>
+      <c r="E58" s="84"/>
+      <c r="F58" s="84"/>
+      <c r="G58" s="84"/>
+      <c r="H58" s="84"/>
+      <c r="I58" s="84"/>
+      <c r="J58" s="84"/>
+      <c r="K58" s="84"/>
+      <c r="L58" s="84"/>
+      <c r="M58" s="84"/>
+      <c r="N58" s="84"/>
+      <c r="O58" s="84"/>
+      <c r="P58" s="84"/>
+      <c r="Q58" s="84"/>
+      <c r="R58" s="84"/>
+      <c r="S58" s="84"/>
+      <c r="T58" s="84"/>
+      <c r="U58" s="84"/>
+      <c r="V58" s="84"/>
+      <c r="W58" s="84"/>
+      <c r="X58" s="84"/>
+      <c r="Y58" s="84"/>
+      <c r="Z58" s="84"/>
+      <c r="AA58" s="84"/>
+      <c r="AB58" s="84"/>
+      <c r="AC58" s="84"/>
+      <c r="AD58" s="84"/>
+      <c r="AE58" s="84"/>
+      <c r="AF58" s="84"/>
+      <c r="AG58" s="84"/>
+      <c r="AH58" s="84"/>
+      <c r="AI58" s="84"/>
+      <c r="AJ58" s="84"/>
+      <c r="AK58" s="84"/>
+      <c r="AL58" s="84"/>
+      <c r="AM58" s="84"/>
+      <c r="AN58" s="84"/>
+      <c r="AO58" s="84"/>
+      <c r="AP58" s="84"/>
+      <c r="AQ58" s="84"/>
+      <c r="AR58" s="84"/>
+      <c r="AS58" s="84"/>
+      <c r="AT58" s="84"/>
+      <c r="AU58" s="84"/>
+      <c r="AV58" s="84"/>
+      <c r="AW58" s="84"/>
+      <c r="AX58" s="84"/>
+      <c r="AY58" s="84"/>
+      <c r="AZ58" s="84"/>
+      <c r="BA58" s="84"/>
+      <c r="BB58" s="84"/>
+      <c r="BC58" s="84"/>
+      <c r="BD58" s="84"/>
+      <c r="BE58" s="84"/>
+      <c r="BF58" s="84"/>
+      <c r="BG58" s="84"/>
+      <c r="BH58" s="84"/>
+      <c r="BI58" s="84"/>
+      <c r="BJ58" s="84"/>
+      <c r="BK58" s="84"/>
+      <c r="BL58" s="84"/>
+      <c r="BM58" s="84"/>
+      <c r="BN58" s="84"/>
+      <c r="BO58" s="84"/>
+      <c r="BP58" s="84"/>
+      <c r="BQ58" s="84"/>
+      <c r="BR58" s="84"/>
+      <c r="BS58" s="84"/>
+      <c r="BT58" s="84"/>
+      <c r="BU58" s="84"/>
+      <c r="BV58" s="84"/>
+      <c r="BW58" s="84"/>
+      <c r="BX58" s="84"/>
+      <c r="BY58" s="84"/>
+      <c r="BZ58" s="84"/>
+      <c r="CA58" s="84"/>
+      <c r="CB58" s="84"/>
+      <c r="CC58" s="84"/>
+      <c r="CD58" s="84"/>
+      <c r="CE58" s="84"/>
+      <c r="CF58" s="84"/>
+      <c r="CG58" s="84"/>
+      <c r="CH58" s="84"/>
+      <c r="CI58" s="85"/>
     </row>
     <row r="59" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A59" s="79"/>
-      <c r="B59" s="69"/>
-      <c r="C59" s="70"/>
-      <c r="D59" s="70"/>
-      <c r="E59" s="70"/>
-      <c r="F59" s="70"/>
-      <c r="G59" s="70"/>
-      <c r="H59" s="70"/>
-      <c r="I59" s="70"/>
-      <c r="J59" s="70"/>
-      <c r="K59" s="70"/>
-      <c r="L59" s="70"/>
-      <c r="M59" s="70"/>
-      <c r="N59" s="70"/>
-      <c r="O59" s="70"/>
-      <c r="P59" s="70"/>
-      <c r="Q59" s="70"/>
-      <c r="R59" s="70"/>
-      <c r="S59" s="70"/>
-      <c r="T59" s="70"/>
-      <c r="U59" s="70"/>
-      <c r="V59" s="70"/>
-      <c r="W59" s="70"/>
-      <c r="X59" s="70"/>
-      <c r="Y59" s="70"/>
-      <c r="Z59" s="70"/>
-      <c r="AA59" s="70"/>
-      <c r="AB59" s="70"/>
-      <c r="AC59" s="70"/>
-      <c r="AD59" s="70"/>
-      <c r="AE59" s="70"/>
-      <c r="AF59" s="70"/>
-      <c r="AG59" s="70"/>
-      <c r="AH59" s="70"/>
-      <c r="AI59" s="70"/>
-      <c r="AJ59" s="70"/>
-      <c r="AK59" s="70"/>
-      <c r="AL59" s="70"/>
-      <c r="AM59" s="70"/>
-      <c r="AN59" s="70"/>
-      <c r="AO59" s="70"/>
-      <c r="AP59" s="70"/>
-      <c r="AQ59" s="70"/>
-      <c r="AR59" s="70"/>
-      <c r="AS59" s="70"/>
-      <c r="AT59" s="70"/>
-      <c r="AU59" s="70"/>
-      <c r="AV59" s="70"/>
-      <c r="AW59" s="70"/>
-      <c r="AX59" s="70"/>
-      <c r="AY59" s="70"/>
-      <c r="AZ59" s="70"/>
-      <c r="BA59" s="70"/>
-      <c r="BB59" s="70"/>
-      <c r="BC59" s="70"/>
-      <c r="BD59" s="70"/>
-      <c r="BE59" s="70"/>
-      <c r="BF59" s="70"/>
-      <c r="BG59" s="70"/>
-      <c r="BH59" s="70"/>
-      <c r="BI59" s="70"/>
-      <c r="BJ59" s="70"/>
-      <c r="BK59" s="70"/>
-      <c r="BL59" s="70"/>
-      <c r="BM59" s="70"/>
-      <c r="BN59" s="70"/>
-      <c r="BO59" s="70"/>
-      <c r="BP59" s="70"/>
-      <c r="BQ59" s="70"/>
-      <c r="BR59" s="70"/>
-      <c r="BS59" s="70"/>
-      <c r="BT59" s="70"/>
-      <c r="BU59" s="70"/>
-      <c r="BV59" s="70"/>
-      <c r="BW59" s="70"/>
-      <c r="BX59" s="70"/>
-      <c r="BY59" s="70"/>
-      <c r="BZ59" s="70"/>
-      <c r="CA59" s="70"/>
-      <c r="CB59" s="70"/>
-      <c r="CC59" s="70"/>
-      <c r="CD59" s="70"/>
-      <c r="CE59" s="70"/>
-      <c r="CF59" s="70"/>
-      <c r="CG59" s="70"/>
-      <c r="CH59" s="70"/>
-      <c r="CI59" s="71"/>
+      <c r="A59" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="26"/>
+      <c r="C59" s="27">
+        <v>2</v>
+      </c>
+      <c r="D59" s="28"/>
+      <c r="E59" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="30"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
+      <c r="K59" s="33"/>
+      <c r="L59" s="33"/>
+      <c r="M59" s="33"/>
+      <c r="N59" s="33"/>
+      <c r="O59" s="33"/>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="33"/>
+      <c r="R59" s="33"/>
+      <c r="S59" s="33"/>
+      <c r="T59" s="33"/>
+      <c r="U59" s="33"/>
+      <c r="V59" s="33"/>
+      <c r="W59" s="33"/>
+      <c r="X59" s="33"/>
+      <c r="Y59" s="33"/>
+      <c r="Z59" s="33"/>
+      <c r="AA59" s="33"/>
+      <c r="AB59" s="33"/>
+      <c r="AC59" s="33"/>
+      <c r="AD59" s="33"/>
+      <c r="AE59" s="33"/>
+      <c r="AF59" s="33"/>
+      <c r="AG59" s="33"/>
+      <c r="AH59" s="33"/>
+      <c r="AI59" s="33"/>
+      <c r="AJ59" s="33"/>
+      <c r="AK59" s="33"/>
+      <c r="AL59" s="33"/>
+      <c r="AM59" s="33"/>
+      <c r="AN59" s="33"/>
+      <c r="AO59" s="33"/>
+      <c r="AP59" s="33"/>
+      <c r="AQ59" s="33"/>
+      <c r="AR59" s="33"/>
+      <c r="AS59" s="33"/>
+      <c r="AT59" s="33"/>
+      <c r="AU59" s="33"/>
+      <c r="AV59" s="33"/>
+      <c r="AW59" s="33"/>
+      <c r="AX59" s="33"/>
+      <c r="AY59" s="33"/>
+      <c r="AZ59" s="33"/>
+      <c r="BA59" s="33"/>
+      <c r="BB59" s="33"/>
+      <c r="BC59" s="33"/>
+      <c r="BD59" s="33"/>
+      <c r="BE59" s="33"/>
+      <c r="BF59" s="33"/>
+      <c r="BG59" s="33"/>
+      <c r="BH59" s="33"/>
+      <c r="BI59" s="33"/>
+      <c r="BJ59" s="33"/>
+      <c r="BK59" s="33"/>
+      <c r="BL59" s="33"/>
+      <c r="BM59" s="33"/>
+      <c r="BN59" s="33"/>
+      <c r="BO59" s="33"/>
+      <c r="BP59" s="33"/>
+      <c r="BQ59" s="33"/>
+      <c r="BR59" s="33"/>
+      <c r="BS59" s="33"/>
+      <c r="BT59" s="33"/>
+      <c r="BU59" s="33"/>
+      <c r="BV59" s="33"/>
+      <c r="BW59" s="33"/>
+      <c r="BX59" s="33"/>
+      <c r="BY59" s="33"/>
+      <c r="BZ59" s="33"/>
+      <c r="CA59" s="33"/>
+      <c r="CB59" s="33"/>
+      <c r="CC59" s="33"/>
+      <c r="CD59" s="33"/>
+      <c r="CE59" s="33"/>
+      <c r="CF59" s="33"/>
+      <c r="CG59" s="33"/>
+      <c r="CH59" s="33"/>
+      <c r="CI59" s="34"/>
     </row>
     <row r="60" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A60" s="79"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="35" t="s">
+      <c r="A60" s="75"/>
+      <c r="B60" s="76"/>
+      <c r="C60" s="76"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="76"/>
+      <c r="F60" s="76"/>
+      <c r="G60" s="76"/>
+      <c r="H60" s="76"/>
+      <c r="I60" s="76"/>
+      <c r="J60" s="76"/>
+      <c r="K60" s="76"/>
+      <c r="L60" s="76"/>
+      <c r="M60" s="76"/>
+      <c r="N60" s="76"/>
+      <c r="O60" s="76"/>
+      <c r="P60" s="76"/>
+      <c r="Q60" s="76"/>
+      <c r="R60" s="76"/>
+      <c r="S60" s="76"/>
+      <c r="T60" s="76"/>
+      <c r="U60" s="76"/>
+      <c r="V60" s="76"/>
+      <c r="W60" s="76"/>
+      <c r="X60" s="76"/>
+      <c r="Y60" s="76"/>
+      <c r="Z60" s="76"/>
+      <c r="AA60" s="76"/>
+      <c r="AB60" s="76"/>
+      <c r="AC60" s="76"/>
+      <c r="AD60" s="76"/>
+      <c r="AE60" s="76"/>
+      <c r="AF60" s="76"/>
+      <c r="AG60" s="76"/>
+      <c r="AH60" s="76"/>
+      <c r="AI60" s="76"/>
+      <c r="AJ60" s="76"/>
+      <c r="AK60" s="76"/>
+      <c r="AL60" s="76"/>
+      <c r="AM60" s="76"/>
+      <c r="AN60" s="76"/>
+      <c r="AO60" s="76"/>
+      <c r="AP60" s="76"/>
+      <c r="AQ60" s="76"/>
+      <c r="AR60" s="76"/>
+      <c r="AS60" s="76"/>
+      <c r="AT60" s="76"/>
+      <c r="AU60" s="76"/>
+      <c r="AV60" s="76"/>
+      <c r="AW60" s="76"/>
+      <c r="AX60" s="76"/>
+      <c r="AY60" s="76"/>
+      <c r="AZ60" s="76"/>
+      <c r="BA60" s="76"/>
+      <c r="BB60" s="76"/>
+      <c r="BC60" s="76"/>
+      <c r="BD60" s="76"/>
+      <c r="BE60" s="76"/>
+      <c r="BF60" s="76"/>
+      <c r="BG60" s="76"/>
+      <c r="BH60" s="76"/>
+      <c r="BI60" s="76"/>
+      <c r="BJ60" s="76"/>
+      <c r="BK60" s="76"/>
+      <c r="BL60" s="76"/>
+      <c r="BM60" s="76"/>
+      <c r="BN60" s="76"/>
+      <c r="BO60" s="76"/>
+      <c r="BP60" s="76"/>
+      <c r="BQ60" s="76"/>
+      <c r="BR60" s="76"/>
+      <c r="BS60" s="76"/>
+      <c r="BT60" s="76"/>
+      <c r="BU60" s="76"/>
+      <c r="BV60" s="76"/>
+      <c r="BW60" s="76"/>
+      <c r="BX60" s="76"/>
+      <c r="BY60" s="76"/>
+      <c r="BZ60" s="76"/>
+      <c r="CA60" s="76"/>
+      <c r="CB60" s="76"/>
+      <c r="CC60" s="76"/>
+      <c r="CD60" s="76"/>
+      <c r="CE60" s="76"/>
+      <c r="CF60" s="76"/>
+      <c r="CG60" s="76"/>
+      <c r="CH60" s="76"/>
+      <c r="CI60" s="77"/>
+    </row>
+    <row r="61" spans="1:87" ht="27" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A61" s="78"/>
+      <c r="B61" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="36"/>
-      <c r="E60" s="37" t="s">
+      <c r="C61" s="36"/>
+      <c r="D61" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="48"/>
+      <c r="F61" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="38"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="40"/>
+      <c r="M61" s="40"/>
+      <c r="N61" s="40"/>
+      <c r="O61" s="40"/>
+      <c r="P61" s="40"/>
+      <c r="Q61" s="40"/>
+      <c r="R61" s="40"/>
+      <c r="S61" s="40"/>
+      <c r="T61" s="40"/>
+      <c r="U61" s="40"/>
+      <c r="V61" s="40"/>
+      <c r="W61" s="40"/>
+      <c r="X61" s="40"/>
+      <c r="Y61" s="40"/>
+      <c r="Z61" s="40"/>
+      <c r="AA61" s="40"/>
+      <c r="AB61" s="40"/>
+      <c r="AC61" s="40"/>
+      <c r="AD61" s="40"/>
+      <c r="AE61" s="40"/>
+      <c r="AF61" s="40"/>
+      <c r="AG61" s="40"/>
+      <c r="AH61" s="40"/>
+      <c r="AI61" s="40"/>
+      <c r="AJ61" s="40"/>
+      <c r="AK61" s="40"/>
+      <c r="AL61" s="40"/>
+      <c r="AM61" s="40"/>
+      <c r="AN61" s="40"/>
+      <c r="AO61" s="40"/>
+      <c r="AP61" s="40"/>
+      <c r="AQ61" s="40"/>
+      <c r="AR61" s="40"/>
+      <c r="AS61" s="40"/>
+      <c r="AT61" s="40"/>
+      <c r="AU61" s="40"/>
+      <c r="AV61" s="40"/>
+      <c r="AW61" s="40"/>
+      <c r="AX61" s="40"/>
+      <c r="AY61" s="40"/>
+      <c r="AZ61" s="40"/>
+      <c r="BA61" s="40"/>
+      <c r="BB61" s="40"/>
+      <c r="BC61" s="40"/>
+      <c r="BD61" s="40"/>
+      <c r="BE61" s="40"/>
+      <c r="BF61" s="40"/>
+      <c r="BG61" s="40"/>
+      <c r="BH61" s="40"/>
+      <c r="BI61" s="40"/>
+      <c r="BJ61" s="40"/>
+      <c r="BK61" s="40"/>
+      <c r="BL61" s="40"/>
+      <c r="BM61" s="40"/>
+      <c r="BN61" s="40"/>
+      <c r="BO61" s="40"/>
+      <c r="BP61" s="40"/>
+      <c r="BQ61" s="40"/>
+      <c r="BR61" s="40"/>
+      <c r="BS61" s="40"/>
+      <c r="BT61" s="40"/>
+      <c r="BU61" s="40"/>
+      <c r="BV61" s="40"/>
+      <c r="BW61" s="40"/>
+      <c r="BX61" s="40"/>
+      <c r="BY61" s="40"/>
+      <c r="BZ61" s="40"/>
+      <c r="CA61" s="40"/>
+      <c r="CB61" s="40"/>
+      <c r="CC61" s="40"/>
+      <c r="CD61" s="40"/>
+      <c r="CE61" s="40"/>
+      <c r="CF61" s="40"/>
+      <c r="CG61" s="40"/>
+      <c r="CH61" s="40"/>
+      <c r="CI61" s="41"/>
+    </row>
+    <row r="62" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A62" s="79"/>
+      <c r="B62" s="69"/>
+      <c r="C62" s="70"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="70"/>
+      <c r="F62" s="70"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="70"/>
+      <c r="I62" s="70"/>
+      <c r="J62" s="70"/>
+      <c r="K62" s="70"/>
+      <c r="L62" s="70"/>
+      <c r="M62" s="70"/>
+      <c r="N62" s="70"/>
+      <c r="O62" s="70"/>
+      <c r="P62" s="70"/>
+      <c r="Q62" s="70"/>
+      <c r="R62" s="70"/>
+      <c r="S62" s="70"/>
+      <c r="T62" s="70"/>
+      <c r="U62" s="70"/>
+      <c r="V62" s="70"/>
+      <c r="W62" s="70"/>
+      <c r="X62" s="70"/>
+      <c r="Y62" s="70"/>
+      <c r="Z62" s="70"/>
+      <c r="AA62" s="70"/>
+      <c r="AB62" s="70"/>
+      <c r="AC62" s="70"/>
+      <c r="AD62" s="70"/>
+      <c r="AE62" s="70"/>
+      <c r="AF62" s="70"/>
+      <c r="AG62" s="70"/>
+      <c r="AH62" s="70"/>
+      <c r="AI62" s="70"/>
+      <c r="AJ62" s="70"/>
+      <c r="AK62" s="70"/>
+      <c r="AL62" s="70"/>
+      <c r="AM62" s="70"/>
+      <c r="AN62" s="70"/>
+      <c r="AO62" s="70"/>
+      <c r="AP62" s="70"/>
+      <c r="AQ62" s="70"/>
+      <c r="AR62" s="70"/>
+      <c r="AS62" s="70"/>
+      <c r="AT62" s="70"/>
+      <c r="AU62" s="70"/>
+      <c r="AV62" s="70"/>
+      <c r="AW62" s="70"/>
+      <c r="AX62" s="70"/>
+      <c r="AY62" s="70"/>
+      <c r="AZ62" s="70"/>
+      <c r="BA62" s="70"/>
+      <c r="BB62" s="70"/>
+      <c r="BC62" s="70"/>
+      <c r="BD62" s="70"/>
+      <c r="BE62" s="70"/>
+      <c r="BF62" s="70"/>
+      <c r="BG62" s="70"/>
+      <c r="BH62" s="70"/>
+      <c r="BI62" s="70"/>
+      <c r="BJ62" s="70"/>
+      <c r="BK62" s="70"/>
+      <c r="BL62" s="70"/>
+      <c r="BM62" s="70"/>
+      <c r="BN62" s="70"/>
+      <c r="BO62" s="70"/>
+      <c r="BP62" s="70"/>
+      <c r="BQ62" s="70"/>
+      <c r="BR62" s="70"/>
+      <c r="BS62" s="70"/>
+      <c r="BT62" s="70"/>
+      <c r="BU62" s="70"/>
+      <c r="BV62" s="70"/>
+      <c r="BW62" s="70"/>
+      <c r="BX62" s="70"/>
+      <c r="BY62" s="70"/>
+      <c r="BZ62" s="70"/>
+      <c r="CA62" s="70"/>
+      <c r="CB62" s="70"/>
+      <c r="CC62" s="70"/>
+      <c r="CD62" s="70"/>
+      <c r="CE62" s="70"/>
+      <c r="CF62" s="70"/>
+      <c r="CG62" s="70"/>
+      <c r="CH62" s="70"/>
+      <c r="CI62" s="71"/>
+    </row>
+    <row r="63" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A63" s="79"/>
+      <c r="B63" s="72"/>
+      <c r="C63" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="36"/>
+      <c r="E63" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="38"/>
-      <c r="L60" s="38"/>
-      <c r="M60" s="38"/>
-      <c r="N60" s="36"/>
-      <c r="O60" s="37" t="s">
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="38"/>
+      <c r="L63" s="38"/>
+      <c r="M63" s="38"/>
+      <c r="N63" s="36"/>
+      <c r="O63" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="P60" s="38"/>
-      <c r="Q60" s="38"/>
-      <c r="R60" s="38"/>
-      <c r="S60" s="38"/>
-      <c r="T60" s="38"/>
-      <c r="U60" s="38"/>
-      <c r="V60" s="38"/>
-      <c r="W60" s="38"/>
-      <c r="X60" s="38"/>
-      <c r="Y60" s="38"/>
-      <c r="Z60" s="38"/>
-      <c r="AA60" s="38"/>
-      <c r="AB60" s="38"/>
-      <c r="AC60" s="38"/>
-      <c r="AD60" s="38"/>
-      <c r="AE60" s="38"/>
-      <c r="AF60" s="38"/>
-      <c r="AG60" s="38"/>
-      <c r="AH60" s="38"/>
-      <c r="AI60" s="38"/>
-      <c r="AJ60" s="38"/>
-      <c r="AK60" s="38"/>
-      <c r="AL60" s="38"/>
-      <c r="AM60" s="38"/>
-      <c r="AN60" s="38"/>
-      <c r="AO60" s="36"/>
-      <c r="AP60" s="37" t="s">
+      <c r="P63" s="38"/>
+      <c r="Q63" s="38"/>
+      <c r="R63" s="38"/>
+      <c r="S63" s="38"/>
+      <c r="T63" s="38"/>
+      <c r="U63" s="38"/>
+      <c r="V63" s="38"/>
+      <c r="W63" s="38"/>
+      <c r="X63" s="38"/>
+      <c r="Y63" s="38"/>
+      <c r="Z63" s="38"/>
+      <c r="AA63" s="38"/>
+      <c r="AB63" s="38"/>
+      <c r="AC63" s="38"/>
+      <c r="AD63" s="38"/>
+      <c r="AE63" s="38"/>
+      <c r="AF63" s="38"/>
+      <c r="AG63" s="38"/>
+      <c r="AH63" s="38"/>
+      <c r="AI63" s="38"/>
+      <c r="AJ63" s="38"/>
+      <c r="AK63" s="38"/>
+      <c r="AL63" s="38"/>
+      <c r="AM63" s="38"/>
+      <c r="AN63" s="38"/>
+      <c r="AO63" s="36"/>
+      <c r="AP63" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="AQ60" s="38"/>
-      <c r="AR60" s="36"/>
-      <c r="AS60" s="37" t="s">
+      <c r="AQ63" s="38"/>
+      <c r="AR63" s="36"/>
+      <c r="AS63" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="AT60" s="38"/>
-      <c r="AU60" s="38"/>
-      <c r="AV60" s="38"/>
-      <c r="AW60" s="36"/>
-      <c r="AX60" s="37" t="s">
+      <c r="AT63" s="38"/>
+      <c r="AU63" s="38"/>
+      <c r="AV63" s="38"/>
+      <c r="AW63" s="36"/>
+      <c r="AX63" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="AY60" s="38"/>
-      <c r="AZ60" s="38"/>
-      <c r="BA60" s="38"/>
-      <c r="BB60" s="38"/>
-      <c r="BC60" s="38"/>
-      <c r="BD60" s="38"/>
-      <c r="BE60" s="38"/>
-      <c r="BF60" s="38"/>
-      <c r="BG60" s="38"/>
-      <c r="BH60" s="38"/>
-      <c r="BI60" s="38"/>
-      <c r="BJ60" s="38"/>
-      <c r="BK60" s="38"/>
-      <c r="BL60" s="36"/>
-      <c r="BM60" s="37" t="s">
+      <c r="AY63" s="38"/>
+      <c r="AZ63" s="38"/>
+      <c r="BA63" s="38"/>
+      <c r="BB63" s="38"/>
+      <c r="BC63" s="38"/>
+      <c r="BD63" s="38"/>
+      <c r="BE63" s="38"/>
+      <c r="BF63" s="38"/>
+      <c r="BG63" s="38"/>
+      <c r="BH63" s="38"/>
+      <c r="BI63" s="38"/>
+      <c r="BJ63" s="38"/>
+      <c r="BK63" s="38"/>
+      <c r="BL63" s="36"/>
+      <c r="BM63" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="BN60" s="38"/>
-      <c r="BO60" s="38"/>
-      <c r="BP60" s="38"/>
-      <c r="BQ60" s="38"/>
-      <c r="BR60" s="38"/>
-      <c r="BS60" s="38"/>
-      <c r="BT60" s="38"/>
-      <c r="BU60" s="38"/>
-      <c r="BV60" s="38"/>
-      <c r="BW60" s="38"/>
-      <c r="BX60" s="38"/>
-      <c r="BY60" s="38"/>
-      <c r="BZ60" s="38"/>
-      <c r="CA60" s="38"/>
-      <c r="CB60" s="38"/>
-      <c r="CC60" s="38"/>
-      <c r="CD60" s="38"/>
-      <c r="CE60" s="38"/>
-      <c r="CF60" s="38"/>
-      <c r="CG60" s="38"/>
-      <c r="CH60" s="38"/>
-      <c r="CI60" s="42"/>
+      <c r="BN63" s="38"/>
+      <c r="BO63" s="38"/>
+      <c r="BP63" s="38"/>
+      <c r="BQ63" s="38"/>
+      <c r="BR63" s="38"/>
+      <c r="BS63" s="38"/>
+      <c r="BT63" s="38"/>
+      <c r="BU63" s="38"/>
+      <c r="BV63" s="38"/>
+      <c r="BW63" s="38"/>
+      <c r="BX63" s="38"/>
+      <c r="BY63" s="38"/>
+      <c r="BZ63" s="38"/>
+      <c r="CA63" s="38"/>
+      <c r="CB63" s="38"/>
+      <c r="CC63" s="38"/>
+      <c r="CD63" s="38"/>
+      <c r="CE63" s="38"/>
+      <c r="CF63" s="38"/>
+      <c r="CG63" s="38"/>
+      <c r="CH63" s="38"/>
+      <c r="CI63" s="42"/>
     </row>
-    <row r="61" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A61" s="79"/>
-      <c r="B61" s="73"/>
-      <c r="C61" s="43">
-        <v>1</v>
-      </c>
-      <c r="D61" s="44"/>
-      <c r="E61" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54"/>
-      <c r="H61" s="54"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="54"/>
-      <c r="K61" s="54"/>
-      <c r="L61" s="54"/>
-      <c r="M61" s="54"/>
-      <c r="N61" s="55"/>
-      <c r="O61" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="P61" s="54"/>
-      <c r="Q61" s="54"/>
-      <c r="R61" s="54"/>
-      <c r="S61" s="54"/>
-      <c r="T61" s="54"/>
-      <c r="U61" s="54"/>
-      <c r="V61" s="54"/>
-      <c r="W61" s="54"/>
-      <c r="X61" s="54"/>
-      <c r="Y61" s="54"/>
-      <c r="Z61" s="54"/>
-      <c r="AA61" s="54"/>
-      <c r="AB61" s="54"/>
-      <c r="AC61" s="54"/>
-      <c r="AD61" s="54"/>
-      <c r="AE61" s="54"/>
-      <c r="AF61" s="54"/>
-      <c r="AG61" s="54"/>
-      <c r="AH61" s="54"/>
-      <c r="AI61" s="54"/>
-      <c r="AJ61" s="54"/>
-      <c r="AK61" s="54"/>
-      <c r="AL61" s="54"/>
-      <c r="AM61" s="54"/>
-      <c r="AN61" s="54"/>
-      <c r="AO61" s="55"/>
-      <c r="AP61" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ61" s="54"/>
-      <c r="AR61" s="55"/>
-      <c r="AS61" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="AT61" s="54"/>
-      <c r="AU61" s="54"/>
-      <c r="AV61" s="54"/>
-      <c r="AW61" s="55"/>
-      <c r="AX61" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="AY61" s="54"/>
-      <c r="AZ61" s="54"/>
-      <c r="BA61" s="54"/>
-      <c r="BB61" s="54"/>
-      <c r="BC61" s="54"/>
-      <c r="BD61" s="54"/>
-      <c r="BE61" s="54"/>
-      <c r="BF61" s="54"/>
-      <c r="BG61" s="54"/>
-      <c r="BH61" s="54"/>
-      <c r="BI61" s="54"/>
-      <c r="BJ61" s="54"/>
-      <c r="BK61" s="54"/>
-      <c r="BL61" s="55"/>
-      <c r="BM61" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="BN61" s="54"/>
-      <c r="BO61" s="54"/>
-      <c r="BP61" s="54"/>
-      <c r="BQ61" s="54"/>
-      <c r="BR61" s="54"/>
-      <c r="BS61" s="54"/>
-      <c r="BT61" s="54"/>
-      <c r="BU61" s="54"/>
-      <c r="BV61" s="54"/>
-      <c r="BW61" s="54"/>
-      <c r="BX61" s="54"/>
-      <c r="BY61" s="54"/>
-      <c r="BZ61" s="54"/>
-      <c r="CA61" s="54"/>
-      <c r="CB61" s="54"/>
-      <c r="CC61" s="54"/>
-      <c r="CD61" s="54"/>
-      <c r="CE61" s="54"/>
-      <c r="CF61" s="54"/>
-      <c r="CG61" s="54"/>
-      <c r="CH61" s="54"/>
-      <c r="CI61" s="65"/>
-    </row>
-    <row r="62" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A62" s="79"/>
-      <c r="B62" s="73"/>
-      <c r="C62" s="45">
-        <v>2</v>
-      </c>
-      <c r="D62" s="46"/>
-      <c r="E62" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="F62" s="57"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="57"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="57"/>
-      <c r="K62" s="57"/>
-      <c r="L62" s="57"/>
-      <c r="M62" s="57"/>
-      <c r="N62" s="58"/>
-      <c r="O62" s="56" t="s">
-        <v>43</v>
-      </c>
-      <c r="P62" s="57"/>
-      <c r="Q62" s="57"/>
-      <c r="R62" s="57"/>
-      <c r="S62" s="57"/>
-      <c r="T62" s="57"/>
-      <c r="U62" s="57"/>
-      <c r="V62" s="57"/>
-      <c r="W62" s="57"/>
-      <c r="X62" s="57"/>
-      <c r="Y62" s="57"/>
-      <c r="Z62" s="57"/>
-      <c r="AA62" s="57"/>
-      <c r="AB62" s="57"/>
-      <c r="AC62" s="57"/>
-      <c r="AD62" s="57"/>
-      <c r="AE62" s="57"/>
-      <c r="AF62" s="57"/>
-      <c r="AG62" s="57"/>
-      <c r="AH62" s="57"/>
-      <c r="AI62" s="57"/>
-      <c r="AJ62" s="57"/>
-      <c r="AK62" s="57"/>
-      <c r="AL62" s="57"/>
-      <c r="AM62" s="57"/>
-      <c r="AN62" s="57"/>
-      <c r="AO62" s="58"/>
-      <c r="AP62" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ62" s="57"/>
-      <c r="AR62" s="58"/>
-      <c r="AS62" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="AT62" s="57"/>
-      <c r="AU62" s="57"/>
-      <c r="AV62" s="57"/>
-      <c r="AW62" s="58"/>
-      <c r="AX62" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="AY62" s="57"/>
-      <c r="AZ62" s="57"/>
-      <c r="BA62" s="57"/>
-      <c r="BB62" s="57"/>
-      <c r="BC62" s="57"/>
-      <c r="BD62" s="57"/>
-      <c r="BE62" s="57"/>
-      <c r="BF62" s="57"/>
-      <c r="BG62" s="57"/>
-      <c r="BH62" s="57"/>
-      <c r="BI62" s="57"/>
-      <c r="BJ62" s="57"/>
-      <c r="BK62" s="57"/>
-      <c r="BL62" s="58"/>
-      <c r="BM62" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="BN62" s="57"/>
-      <c r="BO62" s="57"/>
-      <c r="BP62" s="57"/>
-      <c r="BQ62" s="57"/>
-      <c r="BR62" s="57"/>
-      <c r="BS62" s="57"/>
-      <c r="BT62" s="57"/>
-      <c r="BU62" s="57"/>
-      <c r="BV62" s="57"/>
-      <c r="BW62" s="57"/>
-      <c r="BX62" s="57"/>
-      <c r="BY62" s="57"/>
-      <c r="BZ62" s="57"/>
-      <c r="CA62" s="57"/>
-      <c r="CB62" s="57"/>
-      <c r="CC62" s="57"/>
-      <c r="CD62" s="57"/>
-      <c r="CE62" s="57"/>
-      <c r="CF62" s="57"/>
-      <c r="CG62" s="57"/>
-      <c r="CH62" s="57"/>
-      <c r="CI62" s="66"/>
-    </row>
-    <row r="63" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A63" s="79"/>
-      <c r="B63" s="73"/>
-      <c r="C63" s="49">
-        <v>3</v>
-      </c>
-      <c r="D63" s="50"/>
-      <c r="E63" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" s="60"/>
-      <c r="G63" s="60"/>
-      <c r="H63" s="60"/>
-      <c r="I63" s="60"/>
-      <c r="J63" s="60"/>
-      <c r="K63" s="60"/>
-      <c r="L63" s="60"/>
-      <c r="M63" s="60"/>
-      <c r="N63" s="61"/>
-      <c r="O63" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="P63" s="60"/>
-      <c r="Q63" s="60"/>
-      <c r="R63" s="60"/>
-      <c r="S63" s="60"/>
-      <c r="T63" s="60"/>
-      <c r="U63" s="60"/>
-      <c r="V63" s="60"/>
-      <c r="W63" s="60"/>
-      <c r="X63" s="60"/>
-      <c r="Y63" s="60"/>
-      <c r="Z63" s="60"/>
-      <c r="AA63" s="60"/>
-      <c r="AB63" s="60"/>
-      <c r="AC63" s="60"/>
-      <c r="AD63" s="60"/>
-      <c r="AE63" s="60"/>
-      <c r="AF63" s="60"/>
-      <c r="AG63" s="60"/>
-      <c r="AH63" s="60"/>
-      <c r="AI63" s="60"/>
-      <c r="AJ63" s="60"/>
-      <c r="AK63" s="60"/>
-      <c r="AL63" s="60"/>
-      <c r="AM63" s="60"/>
-      <c r="AN63" s="60"/>
-      <c r="AO63" s="61"/>
-      <c r="AP63" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ63" s="60"/>
-      <c r="AR63" s="61"/>
-      <c r="AS63" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="AT63" s="60"/>
-      <c r="AU63" s="60"/>
-      <c r="AV63" s="60"/>
-      <c r="AW63" s="61"/>
-      <c r="AX63" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="AY63" s="60"/>
-      <c r="AZ63" s="60"/>
-      <c r="BA63" s="60"/>
-      <c r="BB63" s="60"/>
-      <c r="BC63" s="60"/>
-      <c r="BD63" s="60"/>
-      <c r="BE63" s="60"/>
-      <c r="BF63" s="60"/>
-      <c r="BG63" s="60"/>
-      <c r="BH63" s="60"/>
-      <c r="BI63" s="60"/>
-      <c r="BJ63" s="60"/>
-      <c r="BK63" s="60"/>
-      <c r="BL63" s="61"/>
-      <c r="BM63" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="BN63" s="60"/>
-      <c r="BO63" s="60"/>
-      <c r="BP63" s="60"/>
-      <c r="BQ63" s="60"/>
-      <c r="BR63" s="60"/>
-      <c r="BS63" s="60"/>
-      <c r="BT63" s="60"/>
-      <c r="BU63" s="60"/>
-      <c r="BV63" s="60"/>
-      <c r="BW63" s="60"/>
-      <c r="BX63" s="60"/>
-      <c r="BY63" s="60"/>
-      <c r="BZ63" s="60"/>
-      <c r="CA63" s="60"/>
-      <c r="CB63" s="60"/>
-      <c r="CC63" s="60"/>
-      <c r="CD63" s="60"/>
-      <c r="CE63" s="60"/>
-      <c r="CF63" s="60"/>
-      <c r="CG63" s="60"/>
-      <c r="CH63" s="60"/>
-      <c r="CI63" s="67"/>
-    </row>
-    <row r="64" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+    <row r="64" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
       <c r="A64" s="79"/>
       <c r="B64" s="73"/>
-      <c r="C64" s="45">
-        <v>4</v>
-      </c>
-      <c r="D64" s="46"/>
-      <c r="E64" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="57"/>
-      <c r="K64" s="57"/>
-      <c r="L64" s="57"/>
-      <c r="M64" s="57"/>
-      <c r="N64" s="58"/>
-      <c r="O64" s="56" t="s">
-        <v>45</v>
-      </c>
-      <c r="P64" s="57"/>
-      <c r="Q64" s="57"/>
-      <c r="R64" s="57"/>
-      <c r="S64" s="57"/>
-      <c r="T64" s="57"/>
-      <c r="U64" s="57"/>
-      <c r="V64" s="57"/>
-      <c r="W64" s="57"/>
-      <c r="X64" s="57"/>
-      <c r="Y64" s="57"/>
-      <c r="Z64" s="57"/>
-      <c r="AA64" s="57"/>
-      <c r="AB64" s="57"/>
-      <c r="AC64" s="57"/>
-      <c r="AD64" s="57"/>
-      <c r="AE64" s="57"/>
-      <c r="AF64" s="57"/>
-      <c r="AG64" s="57"/>
-      <c r="AH64" s="57"/>
-      <c r="AI64" s="57"/>
-      <c r="AJ64" s="57"/>
-      <c r="AK64" s="57"/>
-      <c r="AL64" s="57"/>
-      <c r="AM64" s="57"/>
-      <c r="AN64" s="57"/>
-      <c r="AO64" s="58"/>
-      <c r="AP64" s="56" t="s">
+      <c r="C64" s="43">
+        <v>1</v>
+      </c>
+      <c r="D64" s="44"/>
+      <c r="E64" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="54"/>
+      <c r="I64" s="54"/>
+      <c r="J64" s="54"/>
+      <c r="K64" s="54"/>
+      <c r="L64" s="54"/>
+      <c r="M64" s="54"/>
+      <c r="N64" s="55"/>
+      <c r="O64" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="P64" s="54"/>
+      <c r="Q64" s="54"/>
+      <c r="R64" s="54"/>
+      <c r="S64" s="54"/>
+      <c r="T64" s="54"/>
+      <c r="U64" s="54"/>
+      <c r="V64" s="54"/>
+      <c r="W64" s="54"/>
+      <c r="X64" s="54"/>
+      <c r="Y64" s="54"/>
+      <c r="Z64" s="54"/>
+      <c r="AA64" s="54"/>
+      <c r="AB64" s="54"/>
+      <c r="AC64" s="54"/>
+      <c r="AD64" s="54"/>
+      <c r="AE64" s="54"/>
+      <c r="AF64" s="54"/>
+      <c r="AG64" s="54"/>
+      <c r="AH64" s="54"/>
+      <c r="AI64" s="54"/>
+      <c r="AJ64" s="54"/>
+      <c r="AK64" s="54"/>
+      <c r="AL64" s="54"/>
+      <c r="AM64" s="54"/>
+      <c r="AN64" s="54"/>
+      <c r="AO64" s="55"/>
+      <c r="AP64" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="AQ64" s="57"/>
-      <c r="AR64" s="58"/>
-      <c r="AS64" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="AT64" s="57"/>
-      <c r="AU64" s="57"/>
-      <c r="AV64" s="57"/>
-      <c r="AW64" s="58"/>
-      <c r="AX64" s="56" t="s">
+      <c r="AQ64" s="54"/>
+      <c r="AR64" s="55"/>
+      <c r="AS64" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT64" s="54"/>
+      <c r="AU64" s="54"/>
+      <c r="AV64" s="54"/>
+      <c r="AW64" s="55"/>
+      <c r="AX64" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="AY64" s="57"/>
-      <c r="AZ64" s="57"/>
-      <c r="BA64" s="57"/>
-      <c r="BB64" s="57"/>
-      <c r="BC64" s="57"/>
-      <c r="BD64" s="57"/>
-      <c r="BE64" s="57"/>
-      <c r="BF64" s="57"/>
-      <c r="BG64" s="57"/>
-      <c r="BH64" s="57"/>
-      <c r="BI64" s="57"/>
-      <c r="BJ64" s="57"/>
-      <c r="BK64" s="57"/>
-      <c r="BL64" s="58"/>
-      <c r="BM64" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="BN64" s="57"/>
-      <c r="BO64" s="57"/>
-      <c r="BP64" s="57"/>
-      <c r="BQ64" s="57"/>
-      <c r="BR64" s="57"/>
-      <c r="BS64" s="57"/>
-      <c r="BT64" s="57"/>
-      <c r="BU64" s="57"/>
-      <c r="BV64" s="57"/>
-      <c r="BW64" s="57"/>
-      <c r="BX64" s="57"/>
-      <c r="BY64" s="57"/>
-      <c r="BZ64" s="57"/>
-      <c r="CA64" s="57"/>
-      <c r="CB64" s="57"/>
-      <c r="CC64" s="57"/>
-      <c r="CD64" s="57"/>
-      <c r="CE64" s="57"/>
-      <c r="CF64" s="57"/>
-      <c r="CG64" s="57"/>
-      <c r="CH64" s="57"/>
-      <c r="CI64" s="66"/>
+      <c r="AY64" s="54"/>
+      <c r="AZ64" s="54"/>
+      <c r="BA64" s="54"/>
+      <c r="BB64" s="54"/>
+      <c r="BC64" s="54"/>
+      <c r="BD64" s="54"/>
+      <c r="BE64" s="54"/>
+      <c r="BF64" s="54"/>
+      <c r="BG64" s="54"/>
+      <c r="BH64" s="54"/>
+      <c r="BI64" s="54"/>
+      <c r="BJ64" s="54"/>
+      <c r="BK64" s="54"/>
+      <c r="BL64" s="55"/>
+      <c r="BM64" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="BN64" s="54"/>
+      <c r="BO64" s="54"/>
+      <c r="BP64" s="54"/>
+      <c r="BQ64" s="54"/>
+      <c r="BR64" s="54"/>
+      <c r="BS64" s="54"/>
+      <c r="BT64" s="54"/>
+      <c r="BU64" s="54"/>
+      <c r="BV64" s="54"/>
+      <c r="BW64" s="54"/>
+      <c r="BX64" s="54"/>
+      <c r="BY64" s="54"/>
+      <c r="BZ64" s="54"/>
+      <c r="CA64" s="54"/>
+      <c r="CB64" s="54"/>
+      <c r="CC64" s="54"/>
+      <c r="CD64" s="54"/>
+      <c r="CE64" s="54"/>
+      <c r="CF64" s="54"/>
+      <c r="CG64" s="54"/>
+      <c r="CH64" s="54"/>
+      <c r="CI64" s="65"/>
     </row>
     <row r="65" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A65" s="79"/>
       <c r="B65" s="73"/>
-      <c r="C65" s="49">
-        <v>5</v>
-      </c>
-      <c r="D65" s="50"/>
-      <c r="E65" s="59" t="s">
-        <v>29</v>
-      </c>
-      <c r="F65" s="60"/>
-      <c r="G65" s="60"/>
-      <c r="H65" s="60"/>
-      <c r="I65" s="60"/>
-      <c r="J65" s="60"/>
-      <c r="K65" s="60"/>
-      <c r="L65" s="60"/>
-      <c r="M65" s="60"/>
-      <c r="N65" s="61"/>
-      <c r="O65" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="P65" s="60"/>
-      <c r="Q65" s="60"/>
-      <c r="R65" s="60"/>
-      <c r="S65" s="60"/>
-      <c r="T65" s="60"/>
-      <c r="U65" s="60"/>
-      <c r="V65" s="60"/>
-      <c r="W65" s="60"/>
-      <c r="X65" s="60"/>
-      <c r="Y65" s="60"/>
-      <c r="Z65" s="60"/>
-      <c r="AA65" s="60"/>
-      <c r="AB65" s="60"/>
-      <c r="AC65" s="60"/>
-      <c r="AD65" s="60"/>
-      <c r="AE65" s="60"/>
-      <c r="AF65" s="60"/>
-      <c r="AG65" s="60"/>
-      <c r="AH65" s="60"/>
-      <c r="AI65" s="60"/>
-      <c r="AJ65" s="60"/>
-      <c r="AK65" s="60"/>
-      <c r="AL65" s="60"/>
-      <c r="AM65" s="60"/>
-      <c r="AN65" s="60"/>
-      <c r="AO65" s="61"/>
-      <c r="AP65" s="59" t="s">
+      <c r="C65" s="45">
+        <v>2</v>
+      </c>
+      <c r="D65" s="46"/>
+      <c r="E65" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="57"/>
+      <c r="K65" s="57"/>
+      <c r="L65" s="57"/>
+      <c r="M65" s="57"/>
+      <c r="N65" s="58"/>
+      <c r="O65" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="P65" s="57"/>
+      <c r="Q65" s="57"/>
+      <c r="R65" s="57"/>
+      <c r="S65" s="57"/>
+      <c r="T65" s="57"/>
+      <c r="U65" s="57"/>
+      <c r="V65" s="57"/>
+      <c r="W65" s="57"/>
+      <c r="X65" s="57"/>
+      <c r="Y65" s="57"/>
+      <c r="Z65" s="57"/>
+      <c r="AA65" s="57"/>
+      <c r="AB65" s="57"/>
+      <c r="AC65" s="57"/>
+      <c r="AD65" s="57"/>
+      <c r="AE65" s="57"/>
+      <c r="AF65" s="57"/>
+      <c r="AG65" s="57"/>
+      <c r="AH65" s="57"/>
+      <c r="AI65" s="57"/>
+      <c r="AJ65" s="57"/>
+      <c r="AK65" s="57"/>
+      <c r="AL65" s="57"/>
+      <c r="AM65" s="57"/>
+      <c r="AN65" s="57"/>
+      <c r="AO65" s="58"/>
+      <c r="AP65" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AQ65" s="60"/>
-      <c r="AR65" s="61"/>
-      <c r="AS65" s="59" t="s">
+      <c r="AQ65" s="57"/>
+      <c r="AR65" s="58"/>
+      <c r="AS65" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="AT65" s="60"/>
-      <c r="AU65" s="60"/>
-      <c r="AV65" s="60"/>
-      <c r="AW65" s="61"/>
-      <c r="AX65" s="59" t="s">
+      <c r="AT65" s="57"/>
+      <c r="AU65" s="57"/>
+      <c r="AV65" s="57"/>
+      <c r="AW65" s="58"/>
+      <c r="AX65" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY65" s="60"/>
-      <c r="AZ65" s="60"/>
-      <c r="BA65" s="60"/>
-      <c r="BB65" s="60"/>
-      <c r="BC65" s="60"/>
-      <c r="BD65" s="60"/>
-      <c r="BE65" s="60"/>
-      <c r="BF65" s="60"/>
-      <c r="BG65" s="60"/>
-      <c r="BH65" s="60"/>
-      <c r="BI65" s="60"/>
-      <c r="BJ65" s="60"/>
-      <c r="BK65" s="60"/>
-      <c r="BL65" s="61"/>
-      <c r="BM65" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="BN65" s="60"/>
-      <c r="BO65" s="60"/>
-      <c r="BP65" s="60"/>
-      <c r="BQ65" s="60"/>
-      <c r="BR65" s="60"/>
-      <c r="BS65" s="60"/>
-      <c r="BT65" s="60"/>
-      <c r="BU65" s="60"/>
-      <c r="BV65" s="60"/>
-      <c r="BW65" s="60"/>
-      <c r="BX65" s="60"/>
-      <c r="BY65" s="60"/>
-      <c r="BZ65" s="60"/>
-      <c r="CA65" s="60"/>
-      <c r="CB65" s="60"/>
-      <c r="CC65" s="60"/>
-      <c r="CD65" s="60"/>
-      <c r="CE65" s="60"/>
-      <c r="CF65" s="60"/>
-      <c r="CG65" s="60"/>
-      <c r="CH65" s="60"/>
-      <c r="CI65" s="67"/>
+      <c r="AY65" s="57"/>
+      <c r="AZ65" s="57"/>
+      <c r="BA65" s="57"/>
+      <c r="BB65" s="57"/>
+      <c r="BC65" s="57"/>
+      <c r="BD65" s="57"/>
+      <c r="BE65" s="57"/>
+      <c r="BF65" s="57"/>
+      <c r="BG65" s="57"/>
+      <c r="BH65" s="57"/>
+      <c r="BI65" s="57"/>
+      <c r="BJ65" s="57"/>
+      <c r="BK65" s="57"/>
+      <c r="BL65" s="58"/>
+      <c r="BM65" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="BN65" s="57"/>
+      <c r="BO65" s="57"/>
+      <c r="BP65" s="57"/>
+      <c r="BQ65" s="57"/>
+      <c r="BR65" s="57"/>
+      <c r="BS65" s="57"/>
+      <c r="BT65" s="57"/>
+      <c r="BU65" s="57"/>
+      <c r="BV65" s="57"/>
+      <c r="BW65" s="57"/>
+      <c r="BX65" s="57"/>
+      <c r="BY65" s="57"/>
+      <c r="BZ65" s="57"/>
+      <c r="CA65" s="57"/>
+      <c r="CB65" s="57"/>
+      <c r="CC65" s="57"/>
+      <c r="CD65" s="57"/>
+      <c r="CE65" s="57"/>
+      <c r="CF65" s="57"/>
+      <c r="CG65" s="57"/>
+      <c r="CH65" s="57"/>
+      <c r="CI65" s="66"/>
     </row>
     <row r="66" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A66" s="79"/>
       <c r="B66" s="73"/>
-      <c r="C66" s="45">
-        <v>6</v>
-      </c>
-      <c r="D66" s="46"/>
-      <c r="E66" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="57"/>
-      <c r="J66" s="57"/>
-      <c r="K66" s="57"/>
-      <c r="L66" s="57"/>
-      <c r="M66" s="57"/>
-      <c r="N66" s="58"/>
-      <c r="O66" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="P66" s="57"/>
-      <c r="Q66" s="57"/>
-      <c r="R66" s="57"/>
-      <c r="S66" s="57"/>
-      <c r="T66" s="57"/>
-      <c r="U66" s="57"/>
-      <c r="V66" s="57"/>
-      <c r="W66" s="57"/>
-      <c r="X66" s="57"/>
-      <c r="Y66" s="57"/>
-      <c r="Z66" s="57"/>
-      <c r="AA66" s="57"/>
-      <c r="AB66" s="57"/>
-      <c r="AC66" s="57"/>
-      <c r="AD66" s="57"/>
-      <c r="AE66" s="57"/>
-      <c r="AF66" s="57"/>
-      <c r="AG66" s="57"/>
-      <c r="AH66" s="57"/>
-      <c r="AI66" s="57"/>
-      <c r="AJ66" s="57"/>
-      <c r="AK66" s="57"/>
-      <c r="AL66" s="57"/>
-      <c r="AM66" s="57"/>
-      <c r="AN66" s="57"/>
-      <c r="AO66" s="58"/>
-      <c r="AP66" s="56" t="s">
+      <c r="C66" s="49">
+        <v>3</v>
+      </c>
+      <c r="D66" s="50"/>
+      <c r="E66" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" s="60"/>
+      <c r="G66" s="60"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="60"/>
+      <c r="K66" s="60"/>
+      <c r="L66" s="60"/>
+      <c r="M66" s="60"/>
+      <c r="N66" s="61"/>
+      <c r="O66" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="P66" s="60"/>
+      <c r="Q66" s="60"/>
+      <c r="R66" s="60"/>
+      <c r="S66" s="60"/>
+      <c r="T66" s="60"/>
+      <c r="U66" s="60"/>
+      <c r="V66" s="60"/>
+      <c r="W66" s="60"/>
+      <c r="X66" s="60"/>
+      <c r="Y66" s="60"/>
+      <c r="Z66" s="60"/>
+      <c r="AA66" s="60"/>
+      <c r="AB66" s="60"/>
+      <c r="AC66" s="60"/>
+      <c r="AD66" s="60"/>
+      <c r="AE66" s="60"/>
+      <c r="AF66" s="60"/>
+      <c r="AG66" s="60"/>
+      <c r="AH66" s="60"/>
+      <c r="AI66" s="60"/>
+      <c r="AJ66" s="60"/>
+      <c r="AK66" s="60"/>
+      <c r="AL66" s="60"/>
+      <c r="AM66" s="60"/>
+      <c r="AN66" s="60"/>
+      <c r="AO66" s="61"/>
+      <c r="AP66" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AQ66" s="57"/>
-      <c r="AR66" s="58"/>
-      <c r="AS66" s="56" t="s">
+      <c r="AQ66" s="60"/>
+      <c r="AR66" s="61"/>
+      <c r="AS66" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="AT66" s="57"/>
-      <c r="AU66" s="57"/>
-      <c r="AV66" s="57"/>
-      <c r="AW66" s="58"/>
-      <c r="AX66" s="56" t="s">
+      <c r="AT66" s="60"/>
+      <c r="AU66" s="60"/>
+      <c r="AV66" s="60"/>
+      <c r="AW66" s="61"/>
+      <c r="AX66" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY66" s="57"/>
-      <c r="AZ66" s="57"/>
-      <c r="BA66" s="57"/>
-      <c r="BB66" s="57"/>
-      <c r="BC66" s="57"/>
-      <c r="BD66" s="57"/>
-      <c r="BE66" s="57"/>
-      <c r="BF66" s="57"/>
-      <c r="BG66" s="57"/>
-      <c r="BH66" s="57"/>
-      <c r="BI66" s="57"/>
-      <c r="BJ66" s="57"/>
-      <c r="BK66" s="57"/>
-      <c r="BL66" s="58"/>
-      <c r="BM66" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="BN66" s="57"/>
-      <c r="BO66" s="57"/>
-      <c r="BP66" s="57"/>
-      <c r="BQ66" s="57"/>
-      <c r="BR66" s="57"/>
-      <c r="BS66" s="57"/>
-      <c r="BT66" s="57"/>
-      <c r="BU66" s="57"/>
-      <c r="BV66" s="57"/>
-      <c r="BW66" s="57"/>
-      <c r="BX66" s="57"/>
-      <c r="BY66" s="57"/>
-      <c r="BZ66" s="57"/>
-      <c r="CA66" s="57"/>
-      <c r="CB66" s="57"/>
-      <c r="CC66" s="57"/>
-      <c r="CD66" s="57"/>
-      <c r="CE66" s="57"/>
-      <c r="CF66" s="57"/>
-      <c r="CG66" s="57"/>
-      <c r="CH66" s="57"/>
-      <c r="CI66" s="66"/>
+      <c r="AY66" s="60"/>
+      <c r="AZ66" s="60"/>
+      <c r="BA66" s="60"/>
+      <c r="BB66" s="60"/>
+      <c r="BC66" s="60"/>
+      <c r="BD66" s="60"/>
+      <c r="BE66" s="60"/>
+      <c r="BF66" s="60"/>
+      <c r="BG66" s="60"/>
+      <c r="BH66" s="60"/>
+      <c r="BI66" s="60"/>
+      <c r="BJ66" s="60"/>
+      <c r="BK66" s="60"/>
+      <c r="BL66" s="61"/>
+      <c r="BM66" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="BN66" s="60"/>
+      <c r="BO66" s="60"/>
+      <c r="BP66" s="60"/>
+      <c r="BQ66" s="60"/>
+      <c r="BR66" s="60"/>
+      <c r="BS66" s="60"/>
+      <c r="BT66" s="60"/>
+      <c r="BU66" s="60"/>
+      <c r="BV66" s="60"/>
+      <c r="BW66" s="60"/>
+      <c r="BX66" s="60"/>
+      <c r="BY66" s="60"/>
+      <c r="BZ66" s="60"/>
+      <c r="CA66" s="60"/>
+      <c r="CB66" s="60"/>
+      <c r="CC66" s="60"/>
+      <c r="CD66" s="60"/>
+      <c r="CE66" s="60"/>
+      <c r="CF66" s="60"/>
+      <c r="CG66" s="60"/>
+      <c r="CH66" s="60"/>
+      <c r="CI66" s="67"/>
     </row>
     <row r="67" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A67" s="79"/>
       <c r="B67" s="73"/>
-      <c r="C67" s="49">
-        <v>7</v>
-      </c>
-      <c r="D67" s="50"/>
-      <c r="E67" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="F67" s="60"/>
-      <c r="G67" s="60"/>
-      <c r="H67" s="60"/>
-      <c r="I67" s="60"/>
-      <c r="J67" s="60"/>
-      <c r="K67" s="60"/>
-      <c r="L67" s="60"/>
-      <c r="M67" s="60"/>
-      <c r="N67" s="61"/>
-      <c r="O67" s="59" t="s">
-        <v>48</v>
-      </c>
-      <c r="P67" s="60"/>
-      <c r="Q67" s="60"/>
-      <c r="R67" s="60"/>
-      <c r="S67" s="60"/>
-      <c r="T67" s="60"/>
-      <c r="U67" s="60"/>
-      <c r="V67" s="60"/>
-      <c r="W67" s="60"/>
-      <c r="X67" s="60"/>
-      <c r="Y67" s="60"/>
-      <c r="Z67" s="60"/>
-      <c r="AA67" s="60"/>
-      <c r="AB67" s="60"/>
-      <c r="AC67" s="60"/>
-      <c r="AD67" s="60"/>
-      <c r="AE67" s="60"/>
-      <c r="AF67" s="60"/>
-      <c r="AG67" s="60"/>
-      <c r="AH67" s="60"/>
-      <c r="AI67" s="60"/>
-      <c r="AJ67" s="60"/>
-      <c r="AK67" s="60"/>
-      <c r="AL67" s="60"/>
-      <c r="AM67" s="60"/>
-      <c r="AN67" s="60"/>
-      <c r="AO67" s="61"/>
-      <c r="AP67" s="59" t="s">
+      <c r="C67" s="45">
+        <v>4</v>
+      </c>
+      <c r="D67" s="46"/>
+      <c r="E67" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="57"/>
+      <c r="K67" s="57"/>
+      <c r="L67" s="57"/>
+      <c r="M67" s="57"/>
+      <c r="N67" s="58"/>
+      <c r="O67" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="P67" s="57"/>
+      <c r="Q67" s="57"/>
+      <c r="R67" s="57"/>
+      <c r="S67" s="57"/>
+      <c r="T67" s="57"/>
+      <c r="U67" s="57"/>
+      <c r="V67" s="57"/>
+      <c r="W67" s="57"/>
+      <c r="X67" s="57"/>
+      <c r="Y67" s="57"/>
+      <c r="Z67" s="57"/>
+      <c r="AA67" s="57"/>
+      <c r="AB67" s="57"/>
+      <c r="AC67" s="57"/>
+      <c r="AD67" s="57"/>
+      <c r="AE67" s="57"/>
+      <c r="AF67" s="57"/>
+      <c r="AG67" s="57"/>
+      <c r="AH67" s="57"/>
+      <c r="AI67" s="57"/>
+      <c r="AJ67" s="57"/>
+      <c r="AK67" s="57"/>
+      <c r="AL67" s="57"/>
+      <c r="AM67" s="57"/>
+      <c r="AN67" s="57"/>
+      <c r="AO67" s="58"/>
+      <c r="AP67" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AQ67" s="60"/>
-      <c r="AR67" s="61"/>
-      <c r="AS67" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="AT67" s="60"/>
-      <c r="AU67" s="60"/>
-      <c r="AV67" s="60"/>
-      <c r="AW67" s="61"/>
-      <c r="AX67" s="59" t="s">
+      <c r="AQ67" s="57"/>
+      <c r="AR67" s="58"/>
+      <c r="AS67" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT67" s="57"/>
+      <c r="AU67" s="57"/>
+      <c r="AV67" s="57"/>
+      <c r="AW67" s="58"/>
+      <c r="AX67" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY67" s="60"/>
-      <c r="AZ67" s="60"/>
-      <c r="BA67" s="60"/>
-      <c r="BB67" s="60"/>
-      <c r="BC67" s="60"/>
-      <c r="BD67" s="60"/>
-      <c r="BE67" s="60"/>
-      <c r="BF67" s="60"/>
-      <c r="BG67" s="60"/>
-      <c r="BH67" s="60"/>
-      <c r="BI67" s="60"/>
-      <c r="BJ67" s="60"/>
-      <c r="BK67" s="60"/>
-      <c r="BL67" s="61"/>
-      <c r="BM67" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="BN67" s="60"/>
-      <c r="BO67" s="60"/>
-      <c r="BP67" s="60"/>
-      <c r="BQ67" s="60"/>
-      <c r="BR67" s="60"/>
-      <c r="BS67" s="60"/>
-      <c r="BT67" s="60"/>
-      <c r="BU67" s="60"/>
-      <c r="BV67" s="60"/>
-      <c r="BW67" s="60"/>
-      <c r="BX67" s="60"/>
-      <c r="BY67" s="60"/>
-      <c r="BZ67" s="60"/>
-      <c r="CA67" s="60"/>
-      <c r="CB67" s="60"/>
-      <c r="CC67" s="60"/>
-      <c r="CD67" s="60"/>
-      <c r="CE67" s="60"/>
-      <c r="CF67" s="60"/>
-      <c r="CG67" s="60"/>
-      <c r="CH67" s="60"/>
-      <c r="CI67" s="67"/>
+      <c r="AY67" s="57"/>
+      <c r="AZ67" s="57"/>
+      <c r="BA67" s="57"/>
+      <c r="BB67" s="57"/>
+      <c r="BC67" s="57"/>
+      <c r="BD67" s="57"/>
+      <c r="BE67" s="57"/>
+      <c r="BF67" s="57"/>
+      <c r="BG67" s="57"/>
+      <c r="BH67" s="57"/>
+      <c r="BI67" s="57"/>
+      <c r="BJ67" s="57"/>
+      <c r="BK67" s="57"/>
+      <c r="BL67" s="58"/>
+      <c r="BM67" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="BN67" s="57"/>
+      <c r="BO67" s="57"/>
+      <c r="BP67" s="57"/>
+      <c r="BQ67" s="57"/>
+      <c r="BR67" s="57"/>
+      <c r="BS67" s="57"/>
+      <c r="BT67" s="57"/>
+      <c r="BU67" s="57"/>
+      <c r="BV67" s="57"/>
+      <c r="BW67" s="57"/>
+      <c r="BX67" s="57"/>
+      <c r="BY67" s="57"/>
+      <c r="BZ67" s="57"/>
+      <c r="CA67" s="57"/>
+      <c r="CB67" s="57"/>
+      <c r="CC67" s="57"/>
+      <c r="CD67" s="57"/>
+      <c r="CE67" s="57"/>
+      <c r="CF67" s="57"/>
+      <c r="CG67" s="57"/>
+      <c r="CH67" s="57"/>
+      <c r="CI67" s="66"/>
     </row>
     <row r="68" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A68" s="79"/>
       <c r="B68" s="73"/>
-      <c r="C68" s="45">
-        <v>8</v>
-      </c>
-      <c r="D68" s="46"/>
-      <c r="E68" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="57"/>
-      <c r="J68" s="57"/>
-      <c r="K68" s="57"/>
-      <c r="L68" s="57"/>
-      <c r="M68" s="57"/>
-      <c r="N68" s="58"/>
-      <c r="O68" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="P68" s="57"/>
-      <c r="Q68" s="57"/>
-      <c r="R68" s="57"/>
-      <c r="S68" s="57"/>
-      <c r="T68" s="57"/>
-      <c r="U68" s="57"/>
-      <c r="V68" s="57"/>
-      <c r="W68" s="57"/>
-      <c r="X68" s="57"/>
-      <c r="Y68" s="57"/>
-      <c r="Z68" s="57"/>
-      <c r="AA68" s="57"/>
-      <c r="AB68" s="57"/>
-      <c r="AC68" s="57"/>
-      <c r="AD68" s="57"/>
-      <c r="AE68" s="57"/>
-      <c r="AF68" s="57"/>
-      <c r="AG68" s="57"/>
-      <c r="AH68" s="57"/>
-      <c r="AI68" s="57"/>
-      <c r="AJ68" s="57"/>
-      <c r="AK68" s="57"/>
-      <c r="AL68" s="57"/>
-      <c r="AM68" s="57"/>
-      <c r="AN68" s="57"/>
-      <c r="AO68" s="58"/>
-      <c r="AP68" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ68" s="57"/>
-      <c r="AR68" s="58"/>
-      <c r="AS68" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="AT68" s="57"/>
-      <c r="AU68" s="57"/>
-      <c r="AV68" s="57"/>
-      <c r="AW68" s="58"/>
-      <c r="AX68" s="56" t="s">
+      <c r="C68" s="49">
+        <v>5</v>
+      </c>
+      <c r="D68" s="50"/>
+      <c r="E68" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68" s="60"/>
+      <c r="G68" s="60"/>
+      <c r="H68" s="60"/>
+      <c r="I68" s="60"/>
+      <c r="J68" s="60"/>
+      <c r="K68" s="60"/>
+      <c r="L68" s="60"/>
+      <c r="M68" s="60"/>
+      <c r="N68" s="61"/>
+      <c r="O68" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="P68" s="60"/>
+      <c r="Q68" s="60"/>
+      <c r="R68" s="60"/>
+      <c r="S68" s="60"/>
+      <c r="T68" s="60"/>
+      <c r="U68" s="60"/>
+      <c r="V68" s="60"/>
+      <c r="W68" s="60"/>
+      <c r="X68" s="60"/>
+      <c r="Y68" s="60"/>
+      <c r="Z68" s="60"/>
+      <c r="AA68" s="60"/>
+      <c r="AB68" s="60"/>
+      <c r="AC68" s="60"/>
+      <c r="AD68" s="60"/>
+      <c r="AE68" s="60"/>
+      <c r="AF68" s="60"/>
+      <c r="AG68" s="60"/>
+      <c r="AH68" s="60"/>
+      <c r="AI68" s="60"/>
+      <c r="AJ68" s="60"/>
+      <c r="AK68" s="60"/>
+      <c r="AL68" s="60"/>
+      <c r="AM68" s="60"/>
+      <c r="AN68" s="60"/>
+      <c r="AO68" s="61"/>
+      <c r="AP68" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY68" s="57"/>
-      <c r="AZ68" s="57"/>
-      <c r="BA68" s="57"/>
-      <c r="BB68" s="57"/>
-      <c r="BC68" s="57"/>
-      <c r="BD68" s="57"/>
-      <c r="BE68" s="57"/>
-      <c r="BF68" s="57"/>
-      <c r="BG68" s="57"/>
-      <c r="BH68" s="57"/>
-      <c r="BI68" s="57"/>
-      <c r="BJ68" s="57"/>
-      <c r="BK68" s="57"/>
-      <c r="BL68" s="58"/>
-      <c r="BM68" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="BN68" s="57"/>
-      <c r="BO68" s="57"/>
-      <c r="BP68" s="57"/>
-      <c r="BQ68" s="57"/>
-      <c r="BR68" s="57"/>
-      <c r="BS68" s="57"/>
-      <c r="BT68" s="57"/>
-      <c r="BU68" s="57"/>
-      <c r="BV68" s="57"/>
-      <c r="BW68" s="57"/>
-      <c r="BX68" s="57"/>
-      <c r="BY68" s="57"/>
-      <c r="BZ68" s="57"/>
-      <c r="CA68" s="57"/>
-      <c r="CB68" s="57"/>
-      <c r="CC68" s="57"/>
-      <c r="CD68" s="57"/>
-      <c r="CE68" s="57"/>
-      <c r="CF68" s="57"/>
-      <c r="CG68" s="57"/>
-      <c r="CH68" s="57"/>
-      <c r="CI68" s="66"/>
+      <c r="AQ68" s="60"/>
+      <c r="AR68" s="61"/>
+      <c r="AS68" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT68" s="60"/>
+      <c r="AU68" s="60"/>
+      <c r="AV68" s="60"/>
+      <c r="AW68" s="61"/>
+      <c r="AX68" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY68" s="60"/>
+      <c r="AZ68" s="60"/>
+      <c r="BA68" s="60"/>
+      <c r="BB68" s="60"/>
+      <c r="BC68" s="60"/>
+      <c r="BD68" s="60"/>
+      <c r="BE68" s="60"/>
+      <c r="BF68" s="60"/>
+      <c r="BG68" s="60"/>
+      <c r="BH68" s="60"/>
+      <c r="BI68" s="60"/>
+      <c r="BJ68" s="60"/>
+      <c r="BK68" s="60"/>
+      <c r="BL68" s="61"/>
+      <c r="BM68" s="59" t="s">
+        <v>57</v>
+      </c>
+      <c r="BN68" s="60"/>
+      <c r="BO68" s="60"/>
+      <c r="BP68" s="60"/>
+      <c r="BQ68" s="60"/>
+      <c r="BR68" s="60"/>
+      <c r="BS68" s="60"/>
+      <c r="BT68" s="60"/>
+      <c r="BU68" s="60"/>
+      <c r="BV68" s="60"/>
+      <c r="BW68" s="60"/>
+      <c r="BX68" s="60"/>
+      <c r="BY68" s="60"/>
+      <c r="BZ68" s="60"/>
+      <c r="CA68" s="60"/>
+      <c r="CB68" s="60"/>
+      <c r="CC68" s="60"/>
+      <c r="CD68" s="60"/>
+      <c r="CE68" s="60"/>
+      <c r="CF68" s="60"/>
+      <c r="CG68" s="60"/>
+      <c r="CH68" s="60"/>
+      <c r="CI68" s="67"/>
     </row>
     <row r="69" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A69" s="79"/>
       <c r="B69" s="73"/>
-      <c r="C69" s="49">
-        <v>9</v>
-      </c>
-      <c r="D69" s="50"/>
-      <c r="E69" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="F69" s="60"/>
-      <c r="G69" s="60"/>
-      <c r="H69" s="60"/>
-      <c r="I69" s="60"/>
-      <c r="J69" s="60"/>
-      <c r="K69" s="60"/>
-      <c r="L69" s="60"/>
-      <c r="M69" s="60"/>
-      <c r="N69" s="61"/>
-      <c r="O69" s="59" t="s">
-        <v>50</v>
-      </c>
-      <c r="P69" s="60"/>
-      <c r="Q69" s="60"/>
-      <c r="R69" s="60"/>
-      <c r="S69" s="60"/>
-      <c r="T69" s="60"/>
-      <c r="U69" s="60"/>
-      <c r="V69" s="60"/>
-      <c r="W69" s="60"/>
-      <c r="X69" s="60"/>
-      <c r="Y69" s="60"/>
-      <c r="Z69" s="60"/>
-      <c r="AA69" s="60"/>
-      <c r="AB69" s="60"/>
-      <c r="AC69" s="60"/>
-      <c r="AD69" s="60"/>
-      <c r="AE69" s="60"/>
-      <c r="AF69" s="60"/>
-      <c r="AG69" s="60"/>
-      <c r="AH69" s="60"/>
-      <c r="AI69" s="60"/>
-      <c r="AJ69" s="60"/>
-      <c r="AK69" s="60"/>
-      <c r="AL69" s="60"/>
-      <c r="AM69" s="60"/>
-      <c r="AN69" s="60"/>
-      <c r="AO69" s="61"/>
-      <c r="AP69" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ69" s="60"/>
-      <c r="AR69" s="61"/>
-      <c r="AS69" s="59" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT69" s="60"/>
-      <c r="AU69" s="60"/>
-      <c r="AV69" s="60"/>
-      <c r="AW69" s="61"/>
-      <c r="AX69" s="59" t="s">
+      <c r="C69" s="45">
+        <v>6</v>
+      </c>
+      <c r="D69" s="46"/>
+      <c r="E69" s="56" t="s">
+        <v>30</v>
+      </c>
+      <c r="F69" s="57"/>
+      <c r="G69" s="57"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="57"/>
+      <c r="J69" s="57"/>
+      <c r="K69" s="57"/>
+      <c r="L69" s="57"/>
+      <c r="M69" s="57"/>
+      <c r="N69" s="58"/>
+      <c r="O69" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="P69" s="57"/>
+      <c r="Q69" s="57"/>
+      <c r="R69" s="57"/>
+      <c r="S69" s="57"/>
+      <c r="T69" s="57"/>
+      <c r="U69" s="57"/>
+      <c r="V69" s="57"/>
+      <c r="W69" s="57"/>
+      <c r="X69" s="57"/>
+      <c r="Y69" s="57"/>
+      <c r="Z69" s="57"/>
+      <c r="AA69" s="57"/>
+      <c r="AB69" s="57"/>
+      <c r="AC69" s="57"/>
+      <c r="AD69" s="57"/>
+      <c r="AE69" s="57"/>
+      <c r="AF69" s="57"/>
+      <c r="AG69" s="57"/>
+      <c r="AH69" s="57"/>
+      <c r="AI69" s="57"/>
+      <c r="AJ69" s="57"/>
+      <c r="AK69" s="57"/>
+      <c r="AL69" s="57"/>
+      <c r="AM69" s="57"/>
+      <c r="AN69" s="57"/>
+      <c r="AO69" s="58"/>
+      <c r="AP69" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY69" s="60"/>
-      <c r="AZ69" s="60"/>
-      <c r="BA69" s="60"/>
-      <c r="BB69" s="60"/>
-      <c r="BC69" s="60"/>
-      <c r="BD69" s="60"/>
-      <c r="BE69" s="60"/>
-      <c r="BF69" s="60"/>
-      <c r="BG69" s="60"/>
-      <c r="BH69" s="60"/>
-      <c r="BI69" s="60"/>
-      <c r="BJ69" s="60"/>
-      <c r="BK69" s="60"/>
-      <c r="BL69" s="61"/>
-      <c r="BM69" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="BN69" s="60"/>
-      <c r="BO69" s="60"/>
-      <c r="BP69" s="60"/>
-      <c r="BQ69" s="60"/>
-      <c r="BR69" s="60"/>
-      <c r="BS69" s="60"/>
-      <c r="BT69" s="60"/>
-      <c r="BU69" s="60"/>
-      <c r="BV69" s="60"/>
-      <c r="BW69" s="60"/>
-      <c r="BX69" s="60"/>
-      <c r="BY69" s="60"/>
-      <c r="BZ69" s="60"/>
-      <c r="CA69" s="60"/>
-      <c r="CB69" s="60"/>
-      <c r="CC69" s="60"/>
-      <c r="CD69" s="60"/>
-      <c r="CE69" s="60"/>
-      <c r="CF69" s="60"/>
-      <c r="CG69" s="60"/>
-      <c r="CH69" s="60"/>
-      <c r="CI69" s="67"/>
+      <c r="AQ69" s="57"/>
+      <c r="AR69" s="58"/>
+      <c r="AS69" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT69" s="57"/>
+      <c r="AU69" s="57"/>
+      <c r="AV69" s="57"/>
+      <c r="AW69" s="58"/>
+      <c r="AX69" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY69" s="57"/>
+      <c r="AZ69" s="57"/>
+      <c r="BA69" s="57"/>
+      <c r="BB69" s="57"/>
+      <c r="BC69" s="57"/>
+      <c r="BD69" s="57"/>
+      <c r="BE69" s="57"/>
+      <c r="BF69" s="57"/>
+      <c r="BG69" s="57"/>
+      <c r="BH69" s="57"/>
+      <c r="BI69" s="57"/>
+      <c r="BJ69" s="57"/>
+      <c r="BK69" s="57"/>
+      <c r="BL69" s="58"/>
+      <c r="BM69" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="BN69" s="57"/>
+      <c r="BO69" s="57"/>
+      <c r="BP69" s="57"/>
+      <c r="BQ69" s="57"/>
+      <c r="BR69" s="57"/>
+      <c r="BS69" s="57"/>
+      <c r="BT69" s="57"/>
+      <c r="BU69" s="57"/>
+      <c r="BV69" s="57"/>
+      <c r="BW69" s="57"/>
+      <c r="BX69" s="57"/>
+      <c r="BY69" s="57"/>
+      <c r="BZ69" s="57"/>
+      <c r="CA69" s="57"/>
+      <c r="CB69" s="57"/>
+      <c r="CC69" s="57"/>
+      <c r="CD69" s="57"/>
+      <c r="CE69" s="57"/>
+      <c r="CF69" s="57"/>
+      <c r="CG69" s="57"/>
+      <c r="CH69" s="57"/>
+      <c r="CI69" s="66"/>
     </row>
     <row r="70" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A70" s="79"/>
       <c r="B70" s="73"/>
-      <c r="C70" s="45">
-        <v>10</v>
-      </c>
-      <c r="D70" s="46"/>
-      <c r="E70" s="56" t="s">
-        <v>35</v>
-      </c>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="57"/>
-      <c r="K70" s="57"/>
-      <c r="L70" s="57"/>
-      <c r="M70" s="57"/>
-      <c r="N70" s="58"/>
-      <c r="O70" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="P70" s="57"/>
-      <c r="Q70" s="57"/>
-      <c r="R70" s="57"/>
-      <c r="S70" s="57"/>
-      <c r="T70" s="57"/>
-      <c r="U70" s="57"/>
-      <c r="V70" s="57"/>
-      <c r="W70" s="57"/>
-      <c r="X70" s="57"/>
-      <c r="Y70" s="57"/>
-      <c r="Z70" s="57"/>
-      <c r="AA70" s="57"/>
-      <c r="AB70" s="57"/>
-      <c r="AC70" s="57"/>
-      <c r="AD70" s="57"/>
-      <c r="AE70" s="57"/>
-      <c r="AF70" s="57"/>
-      <c r="AG70" s="57"/>
-      <c r="AH70" s="57"/>
-      <c r="AI70" s="57"/>
-      <c r="AJ70" s="57"/>
-      <c r="AK70" s="57"/>
-      <c r="AL70" s="57"/>
-      <c r="AM70" s="57"/>
-      <c r="AN70" s="57"/>
-      <c r="AO70" s="58"/>
-      <c r="AP70" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="AQ70" s="57"/>
-      <c r="AR70" s="58"/>
-      <c r="AS70" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT70" s="57"/>
-      <c r="AU70" s="57"/>
-      <c r="AV70" s="57"/>
-      <c r="AW70" s="58"/>
-      <c r="AX70" s="56" t="s">
+      <c r="C70" s="49">
+        <v>7</v>
+      </c>
+      <c r="D70" s="50"/>
+      <c r="E70" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F70" s="60"/>
+      <c r="G70" s="60"/>
+      <c r="H70" s="60"/>
+      <c r="I70" s="60"/>
+      <c r="J70" s="60"/>
+      <c r="K70" s="60"/>
+      <c r="L70" s="60"/>
+      <c r="M70" s="60"/>
+      <c r="N70" s="61"/>
+      <c r="O70" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="P70" s="60"/>
+      <c r="Q70" s="60"/>
+      <c r="R70" s="60"/>
+      <c r="S70" s="60"/>
+      <c r="T70" s="60"/>
+      <c r="U70" s="60"/>
+      <c r="V70" s="60"/>
+      <c r="W70" s="60"/>
+      <c r="X70" s="60"/>
+      <c r="Y70" s="60"/>
+      <c r="Z70" s="60"/>
+      <c r="AA70" s="60"/>
+      <c r="AB70" s="60"/>
+      <c r="AC70" s="60"/>
+      <c r="AD70" s="60"/>
+      <c r="AE70" s="60"/>
+      <c r="AF70" s="60"/>
+      <c r="AG70" s="60"/>
+      <c r="AH70" s="60"/>
+      <c r="AI70" s="60"/>
+      <c r="AJ70" s="60"/>
+      <c r="AK70" s="60"/>
+      <c r="AL70" s="60"/>
+      <c r="AM70" s="60"/>
+      <c r="AN70" s="60"/>
+      <c r="AO70" s="61"/>
+      <c r="AP70" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AY70" s="57"/>
-      <c r="AZ70" s="57"/>
-      <c r="BA70" s="57"/>
-      <c r="BB70" s="57"/>
-      <c r="BC70" s="57"/>
-      <c r="BD70" s="57"/>
-      <c r="BE70" s="57"/>
-      <c r="BF70" s="57"/>
-      <c r="BG70" s="57"/>
-      <c r="BH70" s="57"/>
-      <c r="BI70" s="57"/>
-      <c r="BJ70" s="57"/>
-      <c r="BK70" s="57"/>
-      <c r="BL70" s="58"/>
-      <c r="BM70" s="56" t="s">
-        <v>63</v>
-      </c>
-      <c r="BN70" s="57"/>
-      <c r="BO70" s="57"/>
-      <c r="BP70" s="57"/>
-      <c r="BQ70" s="57"/>
-      <c r="BR70" s="57"/>
-      <c r="BS70" s="57"/>
-      <c r="BT70" s="57"/>
-      <c r="BU70" s="57"/>
-      <c r="BV70" s="57"/>
-      <c r="BW70" s="57"/>
-      <c r="BX70" s="57"/>
-      <c r="BY70" s="57"/>
-      <c r="BZ70" s="57"/>
-      <c r="CA70" s="57"/>
-      <c r="CB70" s="57"/>
-      <c r="CC70" s="57"/>
-      <c r="CD70" s="57"/>
-      <c r="CE70" s="57"/>
-      <c r="CF70" s="57"/>
-      <c r="CG70" s="57"/>
-      <c r="CH70" s="57"/>
-      <c r="CI70" s="66"/>
+      <c r="AQ70" s="60"/>
+      <c r="AR70" s="61"/>
+      <c r="AS70" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT70" s="60"/>
+      <c r="AU70" s="60"/>
+      <c r="AV70" s="60"/>
+      <c r="AW70" s="61"/>
+      <c r="AX70" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY70" s="60"/>
+      <c r="AZ70" s="60"/>
+      <c r="BA70" s="60"/>
+      <c r="BB70" s="60"/>
+      <c r="BC70" s="60"/>
+      <c r="BD70" s="60"/>
+      <c r="BE70" s="60"/>
+      <c r="BF70" s="60"/>
+      <c r="BG70" s="60"/>
+      <c r="BH70" s="60"/>
+      <c r="BI70" s="60"/>
+      <c r="BJ70" s="60"/>
+      <c r="BK70" s="60"/>
+      <c r="BL70" s="61"/>
+      <c r="BM70" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="BN70" s="60"/>
+      <c r="BO70" s="60"/>
+      <c r="BP70" s="60"/>
+      <c r="BQ70" s="60"/>
+      <c r="BR70" s="60"/>
+      <c r="BS70" s="60"/>
+      <c r="BT70" s="60"/>
+      <c r="BU70" s="60"/>
+      <c r="BV70" s="60"/>
+      <c r="BW70" s="60"/>
+      <c r="BX70" s="60"/>
+      <c r="BY70" s="60"/>
+      <c r="BZ70" s="60"/>
+      <c r="CA70" s="60"/>
+      <c r="CB70" s="60"/>
+      <c r="CC70" s="60"/>
+      <c r="CD70" s="60"/>
+      <c r="CE70" s="60"/>
+      <c r="CF70" s="60"/>
+      <c r="CG70" s="60"/>
+      <c r="CH70" s="60"/>
+      <c r="CI70" s="67"/>
     </row>
     <row r="71" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A71" s="79"/>
       <c r="B71" s="73"/>
-      <c r="C71" s="49">
-        <v>11</v>
-      </c>
-      <c r="D71" s="50"/>
-      <c r="E71" s="59" t="s">
-        <v>36</v>
-      </c>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="60"/>
-      <c r="J71" s="60"/>
-      <c r="K71" s="60"/>
-      <c r="L71" s="60"/>
-      <c r="M71" s="60"/>
-      <c r="N71" s="61"/>
-      <c r="O71" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="P71" s="60"/>
-      <c r="Q71" s="60"/>
-      <c r="R71" s="60"/>
-      <c r="S71" s="60"/>
-      <c r="T71" s="60"/>
-      <c r="U71" s="60"/>
-      <c r="V71" s="60"/>
-      <c r="W71" s="60"/>
-      <c r="X71" s="60"/>
-      <c r="Y71" s="60"/>
-      <c r="Z71" s="60"/>
-      <c r="AA71" s="60"/>
-      <c r="AB71" s="60"/>
-      <c r="AC71" s="60"/>
-      <c r="AD71" s="60"/>
-      <c r="AE71" s="60"/>
-      <c r="AF71" s="60"/>
-      <c r="AG71" s="60"/>
-      <c r="AH71" s="60"/>
-      <c r="AI71" s="60"/>
-      <c r="AJ71" s="60"/>
-      <c r="AK71" s="60"/>
-      <c r="AL71" s="60"/>
-      <c r="AM71" s="60"/>
-      <c r="AN71" s="60"/>
-      <c r="AO71" s="61"/>
-      <c r="AP71" s="59" t="s">
+      <c r="C71" s="45">
+        <v>8</v>
+      </c>
+      <c r="D71" s="46"/>
+      <c r="E71" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="57"/>
+      <c r="J71" s="57"/>
+      <c r="K71" s="57"/>
+      <c r="L71" s="57"/>
+      <c r="M71" s="57"/>
+      <c r="N71" s="58"/>
+      <c r="O71" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="P71" s="57"/>
+      <c r="Q71" s="57"/>
+      <c r="R71" s="57"/>
+      <c r="S71" s="57"/>
+      <c r="T71" s="57"/>
+      <c r="U71" s="57"/>
+      <c r="V71" s="57"/>
+      <c r="W71" s="57"/>
+      <c r="X71" s="57"/>
+      <c r="Y71" s="57"/>
+      <c r="Z71" s="57"/>
+      <c r="AA71" s="57"/>
+      <c r="AB71" s="57"/>
+      <c r="AC71" s="57"/>
+      <c r="AD71" s="57"/>
+      <c r="AE71" s="57"/>
+      <c r="AF71" s="57"/>
+      <c r="AG71" s="57"/>
+      <c r="AH71" s="57"/>
+      <c r="AI71" s="57"/>
+      <c r="AJ71" s="57"/>
+      <c r="AK71" s="57"/>
+      <c r="AL71" s="57"/>
+      <c r="AM71" s="57"/>
+      <c r="AN71" s="57"/>
+      <c r="AO71" s="58"/>
+      <c r="AP71" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="AQ71" s="60"/>
-      <c r="AR71" s="61"/>
-      <c r="AS71" s="59" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT71" s="60"/>
-      <c r="AU71" s="60"/>
-      <c r="AV71" s="60"/>
-      <c r="AW71" s="61"/>
-      <c r="AX71" s="59" t="s">
+      <c r="AQ71" s="57"/>
+      <c r="AR71" s="58"/>
+      <c r="AS71" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT71" s="57"/>
+      <c r="AU71" s="57"/>
+      <c r="AV71" s="57"/>
+      <c r="AW71" s="58"/>
+      <c r="AX71" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AY71" s="60"/>
-      <c r="AZ71" s="60"/>
-      <c r="BA71" s="60"/>
-      <c r="BB71" s="60"/>
-      <c r="BC71" s="60"/>
-      <c r="BD71" s="60"/>
-      <c r="BE71" s="60"/>
-      <c r="BF71" s="60"/>
-      <c r="BG71" s="60"/>
-      <c r="BH71" s="60"/>
-      <c r="BI71" s="60"/>
-      <c r="BJ71" s="60"/>
-      <c r="BK71" s="60"/>
-      <c r="BL71" s="61"/>
-      <c r="BM71" s="59" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN71" s="60"/>
-      <c r="BO71" s="60"/>
-      <c r="BP71" s="60"/>
-      <c r="BQ71" s="60"/>
-      <c r="BR71" s="60"/>
-      <c r="BS71" s="60"/>
-      <c r="BT71" s="60"/>
-      <c r="BU71" s="60"/>
-      <c r="BV71" s="60"/>
-      <c r="BW71" s="60"/>
-      <c r="BX71" s="60"/>
-      <c r="BY71" s="60"/>
-      <c r="BZ71" s="60"/>
-      <c r="CA71" s="60"/>
-      <c r="CB71" s="60"/>
-      <c r="CC71" s="60"/>
-      <c r="CD71" s="60"/>
-      <c r="CE71" s="60"/>
-      <c r="CF71" s="60"/>
-      <c r="CG71" s="60"/>
-      <c r="CH71" s="60"/>
-      <c r="CI71" s="67"/>
+      <c r="AY71" s="57"/>
+      <c r="AZ71" s="57"/>
+      <c r="BA71" s="57"/>
+      <c r="BB71" s="57"/>
+      <c r="BC71" s="57"/>
+      <c r="BD71" s="57"/>
+      <c r="BE71" s="57"/>
+      <c r="BF71" s="57"/>
+      <c r="BG71" s="57"/>
+      <c r="BH71" s="57"/>
+      <c r="BI71" s="57"/>
+      <c r="BJ71" s="57"/>
+      <c r="BK71" s="57"/>
+      <c r="BL71" s="58"/>
+      <c r="BM71" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="BN71" s="57"/>
+      <c r="BO71" s="57"/>
+      <c r="BP71" s="57"/>
+      <c r="BQ71" s="57"/>
+      <c r="BR71" s="57"/>
+      <c r="BS71" s="57"/>
+      <c r="BT71" s="57"/>
+      <c r="BU71" s="57"/>
+      <c r="BV71" s="57"/>
+      <c r="BW71" s="57"/>
+      <c r="BX71" s="57"/>
+      <c r="BY71" s="57"/>
+      <c r="BZ71" s="57"/>
+      <c r="CA71" s="57"/>
+      <c r="CB71" s="57"/>
+      <c r="CC71" s="57"/>
+      <c r="CD71" s="57"/>
+      <c r="CE71" s="57"/>
+      <c r="CF71" s="57"/>
+      <c r="CG71" s="57"/>
+      <c r="CH71" s="57"/>
+      <c r="CI71" s="66"/>
     </row>
     <row r="72" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A72" s="79"/>
       <c r="B72" s="73"/>
-      <c r="C72" s="45">
-        <v>12</v>
-      </c>
-      <c r="D72" s="46"/>
-      <c r="E72" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
-      <c r="K72" s="57"/>
-      <c r="L72" s="57"/>
-      <c r="M72" s="57"/>
-      <c r="N72" s="58"/>
-      <c r="O72" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="P72" s="57"/>
-      <c r="Q72" s="57"/>
-      <c r="R72" s="57"/>
-      <c r="S72" s="57"/>
-      <c r="T72" s="57"/>
-      <c r="U72" s="57"/>
-      <c r="V72" s="57"/>
-      <c r="W72" s="57"/>
-      <c r="X72" s="57"/>
-      <c r="Y72" s="57"/>
-      <c r="Z72" s="57"/>
-      <c r="AA72" s="57"/>
-      <c r="AB72" s="57"/>
-      <c r="AC72" s="57"/>
-      <c r="AD72" s="57"/>
-      <c r="AE72" s="57"/>
-      <c r="AF72" s="57"/>
-      <c r="AG72" s="57"/>
-      <c r="AH72" s="57"/>
-      <c r="AI72" s="57"/>
-      <c r="AJ72" s="57"/>
-      <c r="AK72" s="57"/>
-      <c r="AL72" s="57"/>
-      <c r="AM72" s="57"/>
-      <c r="AN72" s="57"/>
-      <c r="AO72" s="58"/>
-      <c r="AP72" s="56" t="s">
+      <c r="C72" s="49">
+        <v>9</v>
+      </c>
+      <c r="D72" s="50"/>
+      <c r="E72" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72" s="60"/>
+      <c r="G72" s="60"/>
+      <c r="H72" s="60"/>
+      <c r="I72" s="60"/>
+      <c r="J72" s="60"/>
+      <c r="K72" s="60"/>
+      <c r="L72" s="60"/>
+      <c r="M72" s="60"/>
+      <c r="N72" s="61"/>
+      <c r="O72" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="P72" s="60"/>
+      <c r="Q72" s="60"/>
+      <c r="R72" s="60"/>
+      <c r="S72" s="60"/>
+      <c r="T72" s="60"/>
+      <c r="U72" s="60"/>
+      <c r="V72" s="60"/>
+      <c r="W72" s="60"/>
+      <c r="X72" s="60"/>
+      <c r="Y72" s="60"/>
+      <c r="Z72" s="60"/>
+      <c r="AA72" s="60"/>
+      <c r="AB72" s="60"/>
+      <c r="AC72" s="60"/>
+      <c r="AD72" s="60"/>
+      <c r="AE72" s="60"/>
+      <c r="AF72" s="60"/>
+      <c r="AG72" s="60"/>
+      <c r="AH72" s="60"/>
+      <c r="AI72" s="60"/>
+      <c r="AJ72" s="60"/>
+      <c r="AK72" s="60"/>
+      <c r="AL72" s="60"/>
+      <c r="AM72" s="60"/>
+      <c r="AN72" s="60"/>
+      <c r="AO72" s="61"/>
+      <c r="AP72" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ72" s="60"/>
+      <c r="AR72" s="61"/>
+      <c r="AS72" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT72" s="60"/>
+      <c r="AU72" s="60"/>
+      <c r="AV72" s="60"/>
+      <c r="AW72" s="61"/>
+      <c r="AX72" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AQ72" s="57"/>
-      <c r="AR72" s="58"/>
-      <c r="AS72" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="AT72" s="57"/>
-      <c r="AU72" s="57"/>
-      <c r="AV72" s="57"/>
-      <c r="AW72" s="58"/>
-      <c r="AX72" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="AY72" s="57"/>
-      <c r="AZ72" s="57"/>
-      <c r="BA72" s="57"/>
-      <c r="BB72" s="57"/>
-      <c r="BC72" s="57"/>
-      <c r="BD72" s="57"/>
-      <c r="BE72" s="57"/>
-      <c r="BF72" s="57"/>
-      <c r="BG72" s="57"/>
-      <c r="BH72" s="57"/>
-      <c r="BI72" s="57"/>
-      <c r="BJ72" s="57"/>
-      <c r="BK72" s="57"/>
-      <c r="BL72" s="58"/>
-      <c r="BM72" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="BN72" s="57"/>
-      <c r="BO72" s="57"/>
-      <c r="BP72" s="57"/>
-      <c r="BQ72" s="57"/>
-      <c r="BR72" s="57"/>
-      <c r="BS72" s="57"/>
-      <c r="BT72" s="57"/>
-      <c r="BU72" s="57"/>
-      <c r="BV72" s="57"/>
-      <c r="BW72" s="57"/>
-      <c r="BX72" s="57"/>
-      <c r="BY72" s="57"/>
-      <c r="BZ72" s="57"/>
-      <c r="CA72" s="57"/>
-      <c r="CB72" s="57"/>
-      <c r="CC72" s="57"/>
-      <c r="CD72" s="57"/>
-      <c r="CE72" s="57"/>
-      <c r="CF72" s="57"/>
-      <c r="CG72" s="57"/>
-      <c r="CH72" s="57"/>
-      <c r="CI72" s="66"/>
+      <c r="AY72" s="60"/>
+      <c r="AZ72" s="60"/>
+      <c r="BA72" s="60"/>
+      <c r="BB72" s="60"/>
+      <c r="BC72" s="60"/>
+      <c r="BD72" s="60"/>
+      <c r="BE72" s="60"/>
+      <c r="BF72" s="60"/>
+      <c r="BG72" s="60"/>
+      <c r="BH72" s="60"/>
+      <c r="BI72" s="60"/>
+      <c r="BJ72" s="60"/>
+      <c r="BK72" s="60"/>
+      <c r="BL72" s="61"/>
+      <c r="BM72" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="BN72" s="60"/>
+      <c r="BO72" s="60"/>
+      <c r="BP72" s="60"/>
+      <c r="BQ72" s="60"/>
+      <c r="BR72" s="60"/>
+      <c r="BS72" s="60"/>
+      <c r="BT72" s="60"/>
+      <c r="BU72" s="60"/>
+      <c r="BV72" s="60"/>
+      <c r="BW72" s="60"/>
+      <c r="BX72" s="60"/>
+      <c r="BY72" s="60"/>
+      <c r="BZ72" s="60"/>
+      <c r="CA72" s="60"/>
+      <c r="CB72" s="60"/>
+      <c r="CC72" s="60"/>
+      <c r="CD72" s="60"/>
+      <c r="CE72" s="60"/>
+      <c r="CF72" s="60"/>
+      <c r="CG72" s="60"/>
+      <c r="CH72" s="60"/>
+      <c r="CI72" s="67"/>
     </row>
     <row r="73" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A73" s="79"/>
       <c r="B73" s="73"/>
-      <c r="C73" s="49">
-        <v>13</v>
-      </c>
-      <c r="D73" s="50"/>
-      <c r="E73" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="F73" s="60"/>
-      <c r="G73" s="60"/>
-      <c r="H73" s="60"/>
-      <c r="I73" s="60"/>
-      <c r="J73" s="60"/>
-      <c r="K73" s="60"/>
-      <c r="L73" s="60"/>
-      <c r="M73" s="60"/>
-      <c r="N73" s="61"/>
-      <c r="O73" s="59" t="s">
-        <v>54</v>
-      </c>
-      <c r="P73" s="60"/>
-      <c r="Q73" s="60"/>
-      <c r="R73" s="60"/>
-      <c r="S73" s="60"/>
-      <c r="T73" s="60"/>
-      <c r="U73" s="60"/>
-      <c r="V73" s="60"/>
-      <c r="W73" s="60"/>
-      <c r="X73" s="60"/>
-      <c r="Y73" s="60"/>
-      <c r="Z73" s="60"/>
-      <c r="AA73" s="60"/>
-      <c r="AB73" s="60"/>
-      <c r="AC73" s="60"/>
-      <c r="AD73" s="60"/>
-      <c r="AE73" s="60"/>
-      <c r="AF73" s="60"/>
-      <c r="AG73" s="60"/>
-      <c r="AH73" s="60"/>
-      <c r="AI73" s="60"/>
-      <c r="AJ73" s="60"/>
-      <c r="AK73" s="60"/>
-      <c r="AL73" s="60"/>
-      <c r="AM73" s="60"/>
-      <c r="AN73" s="60"/>
-      <c r="AO73" s="61"/>
-      <c r="AP73" s="59" t="s">
+      <c r="C73" s="45">
+        <v>10</v>
+      </c>
+      <c r="D73" s="46"/>
+      <c r="E73" s="56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F73" s="57"/>
+      <c r="G73" s="57"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
+      <c r="J73" s="57"/>
+      <c r="K73" s="57"/>
+      <c r="L73" s="57"/>
+      <c r="M73" s="57"/>
+      <c r="N73" s="58"/>
+      <c r="O73" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="P73" s="57"/>
+      <c r="Q73" s="57"/>
+      <c r="R73" s="57"/>
+      <c r="S73" s="57"/>
+      <c r="T73" s="57"/>
+      <c r="U73" s="57"/>
+      <c r="V73" s="57"/>
+      <c r="W73" s="57"/>
+      <c r="X73" s="57"/>
+      <c r="Y73" s="57"/>
+      <c r="Z73" s="57"/>
+      <c r="AA73" s="57"/>
+      <c r="AB73" s="57"/>
+      <c r="AC73" s="57"/>
+      <c r="AD73" s="57"/>
+      <c r="AE73" s="57"/>
+      <c r="AF73" s="57"/>
+      <c r="AG73" s="57"/>
+      <c r="AH73" s="57"/>
+      <c r="AI73" s="57"/>
+      <c r="AJ73" s="57"/>
+      <c r="AK73" s="57"/>
+      <c r="AL73" s="57"/>
+      <c r="AM73" s="57"/>
+      <c r="AN73" s="57"/>
+      <c r="AO73" s="58"/>
+      <c r="AP73" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ73" s="57"/>
+      <c r="AR73" s="58"/>
+      <c r="AS73" s="56" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT73" s="57"/>
+      <c r="AU73" s="57"/>
+      <c r="AV73" s="57"/>
+      <c r="AW73" s="58"/>
+      <c r="AX73" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="AQ73" s="60"/>
-      <c r="AR73" s="61"/>
-      <c r="AS73" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="AT73" s="60"/>
-      <c r="AU73" s="60"/>
-      <c r="AV73" s="60"/>
-      <c r="AW73" s="61"/>
-      <c r="AX73" s="59" t="s">
-        <v>40</v>
-      </c>
-      <c r="AY73" s="60"/>
-      <c r="AZ73" s="60"/>
-      <c r="BA73" s="60"/>
-      <c r="BB73" s="60"/>
-      <c r="BC73" s="60"/>
-      <c r="BD73" s="60"/>
-      <c r="BE73" s="60"/>
-      <c r="BF73" s="60"/>
-      <c r="BG73" s="60"/>
-      <c r="BH73" s="60"/>
-      <c r="BI73" s="60"/>
-      <c r="BJ73" s="60"/>
-      <c r="BK73" s="60"/>
-      <c r="BL73" s="61"/>
-      <c r="BM73" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="BN73" s="60"/>
-      <c r="BO73" s="60"/>
-      <c r="BP73" s="60"/>
-      <c r="BQ73" s="60"/>
-      <c r="BR73" s="60"/>
-      <c r="BS73" s="60"/>
-      <c r="BT73" s="60"/>
-      <c r="BU73" s="60"/>
-      <c r="BV73" s="60"/>
-      <c r="BW73" s="60"/>
-      <c r="BX73" s="60"/>
-      <c r="BY73" s="60"/>
-      <c r="BZ73" s="60"/>
-      <c r="CA73" s="60"/>
-      <c r="CB73" s="60"/>
-      <c r="CC73" s="60"/>
-      <c r="CD73" s="60"/>
-      <c r="CE73" s="60"/>
-      <c r="CF73" s="60"/>
-      <c r="CG73" s="60"/>
-      <c r="CH73" s="60"/>
-      <c r="CI73" s="67"/>
+      <c r="AY73" s="57"/>
+      <c r="AZ73" s="57"/>
+      <c r="BA73" s="57"/>
+      <c r="BB73" s="57"/>
+      <c r="BC73" s="57"/>
+      <c r="BD73" s="57"/>
+      <c r="BE73" s="57"/>
+      <c r="BF73" s="57"/>
+      <c r="BG73" s="57"/>
+      <c r="BH73" s="57"/>
+      <c r="BI73" s="57"/>
+      <c r="BJ73" s="57"/>
+      <c r="BK73" s="57"/>
+      <c r="BL73" s="58"/>
+      <c r="BM73" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="BN73" s="57"/>
+      <c r="BO73" s="57"/>
+      <c r="BP73" s="57"/>
+      <c r="BQ73" s="57"/>
+      <c r="BR73" s="57"/>
+      <c r="BS73" s="57"/>
+      <c r="BT73" s="57"/>
+      <c r="BU73" s="57"/>
+      <c r="BV73" s="57"/>
+      <c r="BW73" s="57"/>
+      <c r="BX73" s="57"/>
+      <c r="BY73" s="57"/>
+      <c r="BZ73" s="57"/>
+      <c r="CA73" s="57"/>
+      <c r="CB73" s="57"/>
+      <c r="CC73" s="57"/>
+      <c r="CD73" s="57"/>
+      <c r="CE73" s="57"/>
+      <c r="CF73" s="57"/>
+      <c r="CG73" s="57"/>
+      <c r="CH73" s="57"/>
+      <c r="CI73" s="66"/>
     </row>
     <row r="74" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
       <c r="A74" s="79"/>
       <c r="B74" s="73"/>
-      <c r="C74" s="45">
-        <v>14</v>
-      </c>
-      <c r="D74" s="46"/>
-      <c r="E74" s="56" t="s">
-        <v>69</v>
-      </c>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="57"/>
-      <c r="K74" s="57"/>
-      <c r="L74" s="57"/>
-      <c r="M74" s="57"/>
-      <c r="N74" s="58"/>
-      <c r="O74" s="56" t="s">
-        <v>70</v>
-      </c>
-      <c r="P74" s="57"/>
-      <c r="Q74" s="57"/>
-      <c r="R74" s="57"/>
-      <c r="S74" s="57"/>
-      <c r="T74" s="57"/>
-      <c r="U74" s="57"/>
-      <c r="V74" s="57"/>
-      <c r="W74" s="57"/>
-      <c r="X74" s="57"/>
-      <c r="Y74" s="57"/>
-      <c r="Z74" s="57"/>
-      <c r="AA74" s="57"/>
-      <c r="AB74" s="57"/>
-      <c r="AC74" s="57"/>
-      <c r="AD74" s="57"/>
-      <c r="AE74" s="57"/>
-      <c r="AF74" s="57"/>
-      <c r="AG74" s="57"/>
-      <c r="AH74" s="57"/>
-      <c r="AI74" s="57"/>
-      <c r="AJ74" s="57"/>
-      <c r="AK74" s="57"/>
-      <c r="AL74" s="57"/>
-      <c r="AM74" s="57"/>
-      <c r="AN74" s="57"/>
-      <c r="AO74" s="58"/>
-      <c r="AP74" s="56" t="s">
+      <c r="C74" s="49">
+        <v>11</v>
+      </c>
+      <c r="D74" s="50"/>
+      <c r="E74" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="60"/>
+      <c r="J74" s="60"/>
+      <c r="K74" s="60"/>
+      <c r="L74" s="60"/>
+      <c r="M74" s="60"/>
+      <c r="N74" s="61"/>
+      <c r="O74" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="P74" s="60"/>
+      <c r="Q74" s="60"/>
+      <c r="R74" s="60"/>
+      <c r="S74" s="60"/>
+      <c r="T74" s="60"/>
+      <c r="U74" s="60"/>
+      <c r="V74" s="60"/>
+      <c r="W74" s="60"/>
+      <c r="X74" s="60"/>
+      <c r="Y74" s="60"/>
+      <c r="Z74" s="60"/>
+      <c r="AA74" s="60"/>
+      <c r="AB74" s="60"/>
+      <c r="AC74" s="60"/>
+      <c r="AD74" s="60"/>
+      <c r="AE74" s="60"/>
+      <c r="AF74" s="60"/>
+      <c r="AG74" s="60"/>
+      <c r="AH74" s="60"/>
+      <c r="AI74" s="60"/>
+      <c r="AJ74" s="60"/>
+      <c r="AK74" s="60"/>
+      <c r="AL74" s="60"/>
+      <c r="AM74" s="60"/>
+      <c r="AN74" s="60"/>
+      <c r="AO74" s="61"/>
+      <c r="AP74" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ74" s="60"/>
+      <c r="AR74" s="61"/>
+      <c r="AS74" s="59" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT74" s="60"/>
+      <c r="AU74" s="60"/>
+      <c r="AV74" s="60"/>
+      <c r="AW74" s="61"/>
+      <c r="AX74" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="AQ74" s="57"/>
-      <c r="AR74" s="58"/>
-      <c r="AS74" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="AT74" s="57"/>
-      <c r="AU74" s="57"/>
-      <c r="AV74" s="57"/>
-      <c r="AW74" s="58"/>
-      <c r="AX74" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="AY74" s="57"/>
-      <c r="AZ74" s="57"/>
-      <c r="BA74" s="57"/>
-      <c r="BB74" s="57"/>
-      <c r="BC74" s="57"/>
-      <c r="BD74" s="57"/>
-      <c r="BE74" s="57"/>
-      <c r="BF74" s="57"/>
-      <c r="BG74" s="57"/>
-      <c r="BH74" s="57"/>
-      <c r="BI74" s="57"/>
-      <c r="BJ74" s="57"/>
-      <c r="BK74" s="57"/>
-      <c r="BL74" s="58"/>
-      <c r="BM74" s="56" t="s">
-        <v>71</v>
-      </c>
-      <c r="BN74" s="57"/>
-      <c r="BO74" s="57"/>
-      <c r="BP74" s="57"/>
-      <c r="BQ74" s="57"/>
-      <c r="BR74" s="57"/>
-      <c r="BS74" s="57"/>
-      <c r="BT74" s="57"/>
-      <c r="BU74" s="57"/>
-      <c r="BV74" s="57"/>
-      <c r="BW74" s="57"/>
-      <c r="BX74" s="57"/>
-      <c r="BY74" s="57"/>
-      <c r="BZ74" s="57"/>
-      <c r="CA74" s="57"/>
-      <c r="CB74" s="57"/>
-      <c r="CC74" s="57"/>
-      <c r="CD74" s="57"/>
-      <c r="CE74" s="57"/>
-      <c r="CF74" s="57"/>
-      <c r="CG74" s="57"/>
-      <c r="CH74" s="57"/>
-      <c r="CI74" s="66"/>
+      <c r="AY74" s="60"/>
+      <c r="AZ74" s="60"/>
+      <c r="BA74" s="60"/>
+      <c r="BB74" s="60"/>
+      <c r="BC74" s="60"/>
+      <c r="BD74" s="60"/>
+      <c r="BE74" s="60"/>
+      <c r="BF74" s="60"/>
+      <c r="BG74" s="60"/>
+      <c r="BH74" s="60"/>
+      <c r="BI74" s="60"/>
+      <c r="BJ74" s="60"/>
+      <c r="BK74" s="60"/>
+      <c r="BL74" s="61"/>
+      <c r="BM74" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN74" s="60"/>
+      <c r="BO74" s="60"/>
+      <c r="BP74" s="60"/>
+      <c r="BQ74" s="60"/>
+      <c r="BR74" s="60"/>
+      <c r="BS74" s="60"/>
+      <c r="BT74" s="60"/>
+      <c r="BU74" s="60"/>
+      <c r="BV74" s="60"/>
+      <c r="BW74" s="60"/>
+      <c r="BX74" s="60"/>
+      <c r="BY74" s="60"/>
+      <c r="BZ74" s="60"/>
+      <c r="CA74" s="60"/>
+      <c r="CB74" s="60"/>
+      <c r="CC74" s="60"/>
+      <c r="CD74" s="60"/>
+      <c r="CE74" s="60"/>
+      <c r="CF74" s="60"/>
+      <c r="CG74" s="60"/>
+      <c r="CH74" s="60"/>
+      <c r="CI74" s="67"/>
     </row>
     <row r="75" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A75" s="80"/>
-      <c r="B75" s="74"/>
-      <c r="C75" s="51">
+      <c r="A75" s="79"/>
+      <c r="B75" s="73"/>
+      <c r="C75" s="45">
+        <v>12</v>
+      </c>
+      <c r="D75" s="46"/>
+      <c r="E75" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="F75" s="57"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="57"/>
+      <c r="J75" s="57"/>
+      <c r="K75" s="57"/>
+      <c r="L75" s="57"/>
+      <c r="M75" s="57"/>
+      <c r="N75" s="58"/>
+      <c r="O75" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="P75" s="57"/>
+      <c r="Q75" s="57"/>
+      <c r="R75" s="57"/>
+      <c r="S75" s="57"/>
+      <c r="T75" s="57"/>
+      <c r="U75" s="57"/>
+      <c r="V75" s="57"/>
+      <c r="W75" s="57"/>
+      <c r="X75" s="57"/>
+      <c r="Y75" s="57"/>
+      <c r="Z75" s="57"/>
+      <c r="AA75" s="57"/>
+      <c r="AB75" s="57"/>
+      <c r="AC75" s="57"/>
+      <c r="AD75" s="57"/>
+      <c r="AE75" s="57"/>
+      <c r="AF75" s="57"/>
+      <c r="AG75" s="57"/>
+      <c r="AH75" s="57"/>
+      <c r="AI75" s="57"/>
+      <c r="AJ75" s="57"/>
+      <c r="AK75" s="57"/>
+      <c r="AL75" s="57"/>
+      <c r="AM75" s="57"/>
+      <c r="AN75" s="57"/>
+      <c r="AO75" s="58"/>
+      <c r="AP75" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ75" s="57"/>
+      <c r="AR75" s="58"/>
+      <c r="AS75" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT75" s="57"/>
+      <c r="AU75" s="57"/>
+      <c r="AV75" s="57"/>
+      <c r="AW75" s="58"/>
+      <c r="AX75" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY75" s="57"/>
+      <c r="AZ75" s="57"/>
+      <c r="BA75" s="57"/>
+      <c r="BB75" s="57"/>
+      <c r="BC75" s="57"/>
+      <c r="BD75" s="57"/>
+      <c r="BE75" s="57"/>
+      <c r="BF75" s="57"/>
+      <c r="BG75" s="57"/>
+      <c r="BH75" s="57"/>
+      <c r="BI75" s="57"/>
+      <c r="BJ75" s="57"/>
+      <c r="BK75" s="57"/>
+      <c r="BL75" s="58"/>
+      <c r="BM75" s="56" t="s">
+        <v>65</v>
+      </c>
+      <c r="BN75" s="57"/>
+      <c r="BO75" s="57"/>
+      <c r="BP75" s="57"/>
+      <c r="BQ75" s="57"/>
+      <c r="BR75" s="57"/>
+      <c r="BS75" s="57"/>
+      <c r="BT75" s="57"/>
+      <c r="BU75" s="57"/>
+      <c r="BV75" s="57"/>
+      <c r="BW75" s="57"/>
+      <c r="BX75" s="57"/>
+      <c r="BY75" s="57"/>
+      <c r="BZ75" s="57"/>
+      <c r="CA75" s="57"/>
+      <c r="CB75" s="57"/>
+      <c r="CC75" s="57"/>
+      <c r="CD75" s="57"/>
+      <c r="CE75" s="57"/>
+      <c r="CF75" s="57"/>
+      <c r="CG75" s="57"/>
+      <c r="CH75" s="57"/>
+      <c r="CI75" s="66"/>
+    </row>
+    <row r="76" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A76" s="79"/>
+      <c r="B76" s="73"/>
+      <c r="C76" s="49">
+        <v>13</v>
+      </c>
+      <c r="D76" s="50"/>
+      <c r="E76" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="60"/>
+      <c r="J76" s="60"/>
+      <c r="K76" s="60"/>
+      <c r="L76" s="60"/>
+      <c r="M76" s="60"/>
+      <c r="N76" s="61"/>
+      <c r="O76" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="P76" s="60"/>
+      <c r="Q76" s="60"/>
+      <c r="R76" s="60"/>
+      <c r="S76" s="60"/>
+      <c r="T76" s="60"/>
+      <c r="U76" s="60"/>
+      <c r="V76" s="60"/>
+      <c r="W76" s="60"/>
+      <c r="X76" s="60"/>
+      <c r="Y76" s="60"/>
+      <c r="Z76" s="60"/>
+      <c r="AA76" s="60"/>
+      <c r="AB76" s="60"/>
+      <c r="AC76" s="60"/>
+      <c r="AD76" s="60"/>
+      <c r="AE76" s="60"/>
+      <c r="AF76" s="60"/>
+      <c r="AG76" s="60"/>
+      <c r="AH76" s="60"/>
+      <c r="AI76" s="60"/>
+      <c r="AJ76" s="60"/>
+      <c r="AK76" s="60"/>
+      <c r="AL76" s="60"/>
+      <c r="AM76" s="60"/>
+      <c r="AN76" s="60"/>
+      <c r="AO76" s="61"/>
+      <c r="AP76" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ76" s="60"/>
+      <c r="AR76" s="61"/>
+      <c r="AS76" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT76" s="60"/>
+      <c r="AU76" s="60"/>
+      <c r="AV76" s="60"/>
+      <c r="AW76" s="61"/>
+      <c r="AX76" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY76" s="60"/>
+      <c r="AZ76" s="60"/>
+      <c r="BA76" s="60"/>
+      <c r="BB76" s="60"/>
+      <c r="BC76" s="60"/>
+      <c r="BD76" s="60"/>
+      <c r="BE76" s="60"/>
+      <c r="BF76" s="60"/>
+      <c r="BG76" s="60"/>
+      <c r="BH76" s="60"/>
+      <c r="BI76" s="60"/>
+      <c r="BJ76" s="60"/>
+      <c r="BK76" s="60"/>
+      <c r="BL76" s="61"/>
+      <c r="BM76" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="BN76" s="60"/>
+      <c r="BO76" s="60"/>
+      <c r="BP76" s="60"/>
+      <c r="BQ76" s="60"/>
+      <c r="BR76" s="60"/>
+      <c r="BS76" s="60"/>
+      <c r="BT76" s="60"/>
+      <c r="BU76" s="60"/>
+      <c r="BV76" s="60"/>
+      <c r="BW76" s="60"/>
+      <c r="BX76" s="60"/>
+      <c r="BY76" s="60"/>
+      <c r="BZ76" s="60"/>
+      <c r="CA76" s="60"/>
+      <c r="CB76" s="60"/>
+      <c r="CC76" s="60"/>
+      <c r="CD76" s="60"/>
+      <c r="CE76" s="60"/>
+      <c r="CF76" s="60"/>
+      <c r="CG76" s="60"/>
+      <c r="CH76" s="60"/>
+      <c r="CI76" s="67"/>
+    </row>
+    <row r="77" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A77" s="79"/>
+      <c r="B77" s="73"/>
+      <c r="C77" s="45">
+        <v>14</v>
+      </c>
+      <c r="D77" s="46"/>
+      <c r="E77" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="F77" s="57"/>
+      <c r="G77" s="57"/>
+      <c r="H77" s="57"/>
+      <c r="I77" s="57"/>
+      <c r="J77" s="57"/>
+      <c r="K77" s="57"/>
+      <c r="L77" s="57"/>
+      <c r="M77" s="57"/>
+      <c r="N77" s="58"/>
+      <c r="O77" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="P77" s="57"/>
+      <c r="Q77" s="57"/>
+      <c r="R77" s="57"/>
+      <c r="S77" s="57"/>
+      <c r="T77" s="57"/>
+      <c r="U77" s="57"/>
+      <c r="V77" s="57"/>
+      <c r="W77" s="57"/>
+      <c r="X77" s="57"/>
+      <c r="Y77" s="57"/>
+      <c r="Z77" s="57"/>
+      <c r="AA77" s="57"/>
+      <c r="AB77" s="57"/>
+      <c r="AC77" s="57"/>
+      <c r="AD77" s="57"/>
+      <c r="AE77" s="57"/>
+      <c r="AF77" s="57"/>
+      <c r="AG77" s="57"/>
+      <c r="AH77" s="57"/>
+      <c r="AI77" s="57"/>
+      <c r="AJ77" s="57"/>
+      <c r="AK77" s="57"/>
+      <c r="AL77" s="57"/>
+      <c r="AM77" s="57"/>
+      <c r="AN77" s="57"/>
+      <c r="AO77" s="58"/>
+      <c r="AP77" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ77" s="57"/>
+      <c r="AR77" s="58"/>
+      <c r="AS77" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT77" s="57"/>
+      <c r="AU77" s="57"/>
+      <c r="AV77" s="57"/>
+      <c r="AW77" s="58"/>
+      <c r="AX77" s="56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AY77" s="57"/>
+      <c r="AZ77" s="57"/>
+      <c r="BA77" s="57"/>
+      <c r="BB77" s="57"/>
+      <c r="BC77" s="57"/>
+      <c r="BD77" s="57"/>
+      <c r="BE77" s="57"/>
+      <c r="BF77" s="57"/>
+      <c r="BG77" s="57"/>
+      <c r="BH77" s="57"/>
+      <c r="BI77" s="57"/>
+      <c r="BJ77" s="57"/>
+      <c r="BK77" s="57"/>
+      <c r="BL77" s="58"/>
+      <c r="BM77" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="BN77" s="57"/>
+      <c r="BO77" s="57"/>
+      <c r="BP77" s="57"/>
+      <c r="BQ77" s="57"/>
+      <c r="BR77" s="57"/>
+      <c r="BS77" s="57"/>
+      <c r="BT77" s="57"/>
+      <c r="BU77" s="57"/>
+      <c r="BV77" s="57"/>
+      <c r="BW77" s="57"/>
+      <c r="BX77" s="57"/>
+      <c r="BY77" s="57"/>
+      <c r="BZ77" s="57"/>
+      <c r="CA77" s="57"/>
+      <c r="CB77" s="57"/>
+      <c r="CC77" s="57"/>
+      <c r="CD77" s="57"/>
+      <c r="CE77" s="57"/>
+      <c r="CF77" s="57"/>
+      <c r="CG77" s="57"/>
+      <c r="CH77" s="57"/>
+      <c r="CI77" s="66"/>
+    </row>
+    <row r="78" spans="1:87" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A78" s="80"/>
+      <c r="B78" s="74"/>
+      <c r="C78" s="51">
         <v>15</v>
       </c>
-      <c r="D75" s="52"/>
-      <c r="E75" s="62" t="s">
+      <c r="D78" s="52"/>
+      <c r="E78" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="F75" s="63"/>
-      <c r="G75" s="63"/>
-      <c r="H75" s="63"/>
-      <c r="I75" s="63"/>
-      <c r="J75" s="63"/>
-      <c r="K75" s="63"/>
-      <c r="L75" s="63"/>
-      <c r="M75" s="63"/>
-      <c r="N75" s="64"/>
-      <c r="O75" s="62" t="s">
+      <c r="F78" s="63"/>
+      <c r="G78" s="63"/>
+      <c r="H78" s="63"/>
+      <c r="I78" s="63"/>
+      <c r="J78" s="63"/>
+      <c r="K78" s="63"/>
+      <c r="L78" s="63"/>
+      <c r="M78" s="63"/>
+      <c r="N78" s="64"/>
+      <c r="O78" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="P75" s="63"/>
-      <c r="Q75" s="63"/>
-      <c r="R75" s="63"/>
-      <c r="S75" s="63"/>
-      <c r="T75" s="63"/>
-      <c r="U75" s="63"/>
-      <c r="V75" s="63"/>
-      <c r="W75" s="63"/>
-      <c r="X75" s="63"/>
-      <c r="Y75" s="63"/>
-      <c r="Z75" s="63"/>
-      <c r="AA75" s="63"/>
-      <c r="AB75" s="63"/>
-      <c r="AC75" s="63"/>
-      <c r="AD75" s="63"/>
-      <c r="AE75" s="63"/>
-      <c r="AF75" s="63"/>
-      <c r="AG75" s="63"/>
-      <c r="AH75" s="63"/>
-      <c r="AI75" s="63"/>
-      <c r="AJ75" s="63"/>
-      <c r="AK75" s="63"/>
-      <c r="AL75" s="63"/>
-      <c r="AM75" s="63"/>
-      <c r="AN75" s="63"/>
-      <c r="AO75" s="64"/>
-      <c r="AP75" s="62" t="s">
+      <c r="P78" s="63"/>
+      <c r="Q78" s="63"/>
+      <c r="R78" s="63"/>
+      <c r="S78" s="63"/>
+      <c r="T78" s="63"/>
+      <c r="U78" s="63"/>
+      <c r="V78" s="63"/>
+      <c r="W78" s="63"/>
+      <c r="X78" s="63"/>
+      <c r="Y78" s="63"/>
+      <c r="Z78" s="63"/>
+      <c r="AA78" s="63"/>
+      <c r="AB78" s="63"/>
+      <c r="AC78" s="63"/>
+      <c r="AD78" s="63"/>
+      <c r="AE78" s="63"/>
+      <c r="AF78" s="63"/>
+      <c r="AG78" s="63"/>
+      <c r="AH78" s="63"/>
+      <c r="AI78" s="63"/>
+      <c r="AJ78" s="63"/>
+      <c r="AK78" s="63"/>
+      <c r="AL78" s="63"/>
+      <c r="AM78" s="63"/>
+      <c r="AN78" s="63"/>
+      <c r="AO78" s="64"/>
+      <c r="AP78" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="AQ75" s="63"/>
-      <c r="AR75" s="64"/>
-      <c r="AS75" s="62" t="s">
+      <c r="AQ78" s="63"/>
+      <c r="AR78" s="64"/>
+      <c r="AS78" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="AT75" s="63"/>
-      <c r="AU75" s="63"/>
-      <c r="AV75" s="63"/>
-      <c r="AW75" s="64"/>
-      <c r="AX75" s="62" t="s">
+      <c r="AT78" s="63"/>
+      <c r="AU78" s="63"/>
+      <c r="AV78" s="63"/>
+      <c r="AW78" s="64"/>
+      <c r="AX78" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="AY75" s="63"/>
-      <c r="AZ75" s="63"/>
-      <c r="BA75" s="63"/>
-      <c r="BB75" s="63"/>
-      <c r="BC75" s="63"/>
-      <c r="BD75" s="63"/>
-      <c r="BE75" s="63"/>
-      <c r="BF75" s="63"/>
-      <c r="BG75" s="63"/>
-      <c r="BH75" s="63"/>
-      <c r="BI75" s="63"/>
-      <c r="BJ75" s="63"/>
-      <c r="BK75" s="63"/>
-      <c r="BL75" s="64"/>
-      <c r="BM75" s="62" t="s">
+      <c r="AY78" s="63"/>
+      <c r="AZ78" s="63"/>
+      <c r="BA78" s="63"/>
+      <c r="BB78" s="63"/>
+      <c r="BC78" s="63"/>
+      <c r="BD78" s="63"/>
+      <c r="BE78" s="63"/>
+      <c r="BF78" s="63"/>
+      <c r="BG78" s="63"/>
+      <c r="BH78" s="63"/>
+      <c r="BI78" s="63"/>
+      <c r="BJ78" s="63"/>
+      <c r="BK78" s="63"/>
+      <c r="BL78" s="64"/>
+      <c r="BM78" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="BN75" s="63"/>
-      <c r="BO75" s="63"/>
-      <c r="BP75" s="63"/>
-      <c r="BQ75" s="63"/>
-      <c r="BR75" s="63"/>
-      <c r="BS75" s="63"/>
-      <c r="BT75" s="63"/>
-      <c r="BU75" s="63"/>
-      <c r="BV75" s="63"/>
-      <c r="BW75" s="63"/>
-      <c r="BX75" s="63"/>
-      <c r="BY75" s="63"/>
-      <c r="BZ75" s="63"/>
-      <c r="CA75" s="63"/>
-      <c r="CB75" s="63"/>
-      <c r="CC75" s="63"/>
-      <c r="CD75" s="63"/>
-      <c r="CE75" s="63"/>
-      <c r="CF75" s="63"/>
-      <c r="CG75" s="63"/>
-      <c r="CH75" s="63"/>
-      <c r="CI75" s="68"/>
+      <c r="BN78" s="63"/>
+      <c r="BO78" s="63"/>
+      <c r="BP78" s="63"/>
+      <c r="BQ78" s="63"/>
+      <c r="BR78" s="63"/>
+      <c r="BS78" s="63"/>
+      <c r="BT78" s="63"/>
+      <c r="BU78" s="63"/>
+      <c r="BV78" s="63"/>
+      <c r="BW78" s="63"/>
+      <c r="BX78" s="63"/>
+      <c r="BY78" s="63"/>
+      <c r="BZ78" s="63"/>
+      <c r="CA78" s="63"/>
+      <c r="CB78" s="63"/>
+      <c r="CC78" s="63"/>
+      <c r="CD78" s="63"/>
+      <c r="CE78" s="63"/>
+      <c r="CF78" s="63"/>
+      <c r="CG78" s="63"/>
+      <c r="CH78" s="63"/>
+      <c r="CI78" s="68"/>
     </row>
-    <row r="76" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
-      <c r="A76" s="81"/>
-      <c r="B76" s="82"/>
-      <c r="C76" s="82"/>
-      <c r="D76" s="82"/>
-      <c r="E76" s="82"/>
-      <c r="F76" s="82"/>
-      <c r="G76" s="82"/>
-      <c r="H76" s="82"/>
-      <c r="I76" s="82"/>
-      <c r="J76" s="82"/>
-      <c r="K76" s="82"/>
-      <c r="L76" s="82"/>
-      <c r="M76" s="82"/>
-      <c r="N76" s="82"/>
-      <c r="O76" s="82"/>
-      <c r="P76" s="82"/>
-      <c r="Q76" s="82"/>
-      <c r="R76" s="82"/>
-      <c r="S76" s="82"/>
-      <c r="T76" s="82"/>
-      <c r="U76" s="82"/>
-      <c r="V76" s="82"/>
-      <c r="W76" s="82"/>
-      <c r="X76" s="82"/>
-      <c r="Y76" s="82"/>
-      <c r="Z76" s="82"/>
-      <c r="AA76" s="82"/>
-      <c r="AB76" s="82"/>
-      <c r="AC76" s="82"/>
-      <c r="AD76" s="82"/>
-      <c r="AE76" s="82"/>
-      <c r="AF76" s="82"/>
-      <c r="AG76" s="82"/>
-      <c r="AH76" s="82"/>
-      <c r="AI76" s="82"/>
-      <c r="AJ76" s="82"/>
-      <c r="AK76" s="82"/>
-      <c r="AL76" s="82"/>
-      <c r="AM76" s="82"/>
-      <c r="AN76" s="82"/>
-      <c r="AO76" s="82"/>
-      <c r="AP76" s="82"/>
-      <c r="AQ76" s="82"/>
-      <c r="AR76" s="82"/>
-      <c r="AS76" s="82"/>
-      <c r="AT76" s="82"/>
-      <c r="AU76" s="82"/>
-      <c r="AV76" s="82"/>
-      <c r="AW76" s="82"/>
-      <c r="AX76" s="82"/>
-      <c r="AY76" s="82"/>
-      <c r="AZ76" s="82"/>
-      <c r="BA76" s="82"/>
-      <c r="BB76" s="82"/>
-      <c r="BC76" s="82"/>
-      <c r="BD76" s="82"/>
-      <c r="BE76" s="82"/>
-      <c r="BF76" s="82"/>
-      <c r="BG76" s="82"/>
-      <c r="BH76" s="82"/>
-      <c r="BI76" s="82"/>
-      <c r="BJ76" s="82"/>
-      <c r="BK76" s="82"/>
-      <c r="BL76" s="82"/>
-      <c r="BM76" s="82"/>
-      <c r="BN76" s="82"/>
-      <c r="BO76" s="82"/>
-      <c r="BP76" s="82"/>
-      <c r="BQ76" s="82"/>
-      <c r="BR76" s="82"/>
-      <c r="BS76" s="82"/>
-      <c r="BT76" s="82"/>
-      <c r="BU76" s="82"/>
-      <c r="BV76" s="82"/>
-      <c r="BW76" s="82"/>
-      <c r="BX76" s="82"/>
-      <c r="BY76" s="82"/>
-      <c r="BZ76" s="82"/>
-      <c r="CA76" s="82"/>
-      <c r="CB76" s="82"/>
-      <c r="CC76" s="82"/>
-      <c r="CD76" s="82"/>
-      <c r="CE76" s="82"/>
-      <c r="CF76" s="82"/>
-      <c r="CG76" s="82"/>
-      <c r="CH76" s="82"/>
-      <c r="CI76" s="83"/>
+    <row r="79" spans="1:87" ht="20.25" thickTop="1" thickBot="1">
+      <c r="A79" s="81"/>
+      <c r="B79" s="82"/>
+      <c r="C79" s="82"/>
+      <c r="D79" s="82"/>
+      <c r="E79" s="82"/>
+      <c r="F79" s="82"/>
+      <c r="G79" s="82"/>
+      <c r="H79" s="82"/>
+      <c r="I79" s="82"/>
+      <c r="J79" s="82"/>
+      <c r="K79" s="82"/>
+      <c r="L79" s="82"/>
+      <c r="M79" s="82"/>
+      <c r="N79" s="82"/>
+      <c r="O79" s="82"/>
+      <c r="P79" s="82"/>
+      <c r="Q79" s="82"/>
+      <c r="R79" s="82"/>
+      <c r="S79" s="82"/>
+      <c r="T79" s="82"/>
+      <c r="U79" s="82"/>
+      <c r="V79" s="82"/>
+      <c r="W79" s="82"/>
+      <c r="X79" s="82"/>
+      <c r="Y79" s="82"/>
+      <c r="Z79" s="82"/>
+      <c r="AA79" s="82"/>
+      <c r="AB79" s="82"/>
+      <c r="AC79" s="82"/>
+      <c r="AD79" s="82"/>
+      <c r="AE79" s="82"/>
+      <c r="AF79" s="82"/>
+      <c r="AG79" s="82"/>
+      <c r="AH79" s="82"/>
+      <c r="AI79" s="82"/>
+      <c r="AJ79" s="82"/>
+      <c r="AK79" s="82"/>
+      <c r="AL79" s="82"/>
+      <c r="AM79" s="82"/>
+      <c r="AN79" s="82"/>
+      <c r="AO79" s="82"/>
+      <c r="AP79" s="82"/>
+      <c r="AQ79" s="82"/>
+      <c r="AR79" s="82"/>
+      <c r="AS79" s="82"/>
+      <c r="AT79" s="82"/>
+      <c r="AU79" s="82"/>
+      <c r="AV79" s="82"/>
+      <c r="AW79" s="82"/>
+      <c r="AX79" s="82"/>
+      <c r="AY79" s="82"/>
+      <c r="AZ79" s="82"/>
+      <c r="BA79" s="82"/>
+      <c r="BB79" s="82"/>
+      <c r="BC79" s="82"/>
+      <c r="BD79" s="82"/>
+      <c r="BE79" s="82"/>
+      <c r="BF79" s="82"/>
+      <c r="BG79" s="82"/>
+      <c r="BH79" s="82"/>
+      <c r="BI79" s="82"/>
+      <c r="BJ79" s="82"/>
+      <c r="BK79" s="82"/>
+      <c r="BL79" s="82"/>
+      <c r="BM79" s="82"/>
+      <c r="BN79" s="82"/>
+      <c r="BO79" s="82"/>
+      <c r="BP79" s="82"/>
+      <c r="BQ79" s="82"/>
+      <c r="BR79" s="82"/>
+      <c r="BS79" s="82"/>
+      <c r="BT79" s="82"/>
+      <c r="BU79" s="82"/>
+      <c r="BV79" s="82"/>
+      <c r="BW79" s="82"/>
+      <c r="BX79" s="82"/>
+      <c r="BY79" s="82"/>
+      <c r="BZ79" s="82"/>
+      <c r="CA79" s="82"/>
+      <c r="CB79" s="82"/>
+      <c r="CC79" s="82"/>
+      <c r="CD79" s="82"/>
+      <c r="CE79" s="82"/>
+      <c r="CF79" s="82"/>
+      <c r="CG79" s="82"/>
+      <c r="CH79" s="82"/>
+      <c r="CI79" s="83"/>
     </row>
-    <row r="77" spans="1:87" ht="19.5" thickTop="1"/>
+    <row r="80" spans="1:87" ht="19.5" thickTop="1"/>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="AX73:BL73"/>
-    <mergeCell ref="AX74:BL74"/>
+    <mergeCell ref="AX76:BL76"/>
+    <mergeCell ref="AX77:BL77"/>
+    <mergeCell ref="BM76:CI76"/>
+    <mergeCell ref="BM77:CI77"/>
+    <mergeCell ref="B62:CI62"/>
+    <mergeCell ref="B63:B78"/>
+    <mergeCell ref="A60:CI60"/>
+    <mergeCell ref="A61:A78"/>
+    <mergeCell ref="A79:CI79"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E76:N76"/>
+    <mergeCell ref="E77:N77"/>
+    <mergeCell ref="O76:AO76"/>
+    <mergeCell ref="O77:AO77"/>
+    <mergeCell ref="AP76:AR76"/>
+    <mergeCell ref="AP77:AR77"/>
+    <mergeCell ref="AS76:AW76"/>
+    <mergeCell ref="AS77:AW77"/>
+    <mergeCell ref="AX69:BL69"/>
+    <mergeCell ref="AX68:BL68"/>
+    <mergeCell ref="BM74:CI74"/>
     <mergeCell ref="BM73:CI73"/>
-    <mergeCell ref="BM74:CI74"/>
-    <mergeCell ref="B59:CI59"/>
-    <mergeCell ref="B60:B75"/>
-    <mergeCell ref="A57:CI57"/>
-    <mergeCell ref="A58:A75"/>
-    <mergeCell ref="A76:CI76"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="E73:N73"/>
-    <mergeCell ref="E74:N74"/>
-    <mergeCell ref="O73:AO73"/>
-    <mergeCell ref="O74:AO74"/>
-    <mergeCell ref="AP73:AR73"/>
-    <mergeCell ref="AP74:AR74"/>
-    <mergeCell ref="AS73:AW73"/>
-    <mergeCell ref="AS74:AW74"/>
-    <mergeCell ref="AX66:BL66"/>
-    <mergeCell ref="AX65:BL65"/>
+    <mergeCell ref="BM72:CI72"/>
     <mergeCell ref="BM71:CI71"/>
     <mergeCell ref="BM70:CI70"/>
     <mergeCell ref="BM69:CI69"/>
     <mergeCell ref="BM68:CI68"/>
-    <mergeCell ref="BM67:CI67"/>
-    <mergeCell ref="BM66:CI66"/>
-    <mergeCell ref="BM65:CI65"/>
+    <mergeCell ref="AX74:BL74"/>
+    <mergeCell ref="AX73:BL73"/>
+    <mergeCell ref="AX72:BL72"/>
     <mergeCell ref="AX71:BL71"/>
     <mergeCell ref="AX70:BL70"/>
-    <mergeCell ref="AX69:BL69"/>
-    <mergeCell ref="AX68:BL68"/>
-    <mergeCell ref="AX67:BL67"/>
-    <mergeCell ref="AP67:AR67"/>
-    <mergeCell ref="AP66:AR66"/>
-    <mergeCell ref="AP65:AR65"/>
+    <mergeCell ref="AP70:AR70"/>
+    <mergeCell ref="AP69:AR69"/>
+    <mergeCell ref="AP68:AR68"/>
+    <mergeCell ref="AS74:AW74"/>
+    <mergeCell ref="AS73:AW73"/>
+    <mergeCell ref="AS72:AW72"/>
     <mergeCell ref="AS71:AW71"/>
     <mergeCell ref="AS70:AW70"/>
     <mergeCell ref="AS69:AW69"/>
     <mergeCell ref="AS68:AW68"/>
-    <mergeCell ref="AS67:AW67"/>
-    <mergeCell ref="AS66:AW66"/>
-    <mergeCell ref="AS65:AW65"/>
+    <mergeCell ref="O71:AO71"/>
+    <mergeCell ref="O72:AO72"/>
+    <mergeCell ref="O73:AO73"/>
+    <mergeCell ref="O74:AO74"/>
+    <mergeCell ref="AP74:AR74"/>
+    <mergeCell ref="AP73:AR73"/>
+    <mergeCell ref="AP72:AR72"/>
+    <mergeCell ref="AP71:AR71"/>
+    <mergeCell ref="E69:N69"/>
+    <mergeCell ref="E68:N68"/>
     <mergeCell ref="O68:AO68"/>
     <mergeCell ref="O69:AO69"/>
     <mergeCell ref="O70:AO70"/>
-    <mergeCell ref="O71:AO71"/>
-    <mergeCell ref="AP71:AR71"/>
-    <mergeCell ref="AP70:AR70"/>
-    <mergeCell ref="AP69:AR69"/>
-    <mergeCell ref="AP68:AR68"/>
-    <mergeCell ref="E66:N66"/>
-    <mergeCell ref="E65:N65"/>
-    <mergeCell ref="O65:AO65"/>
-    <mergeCell ref="O66:AO66"/>
-    <mergeCell ref="O67:AO67"/>
+    <mergeCell ref="E74:N74"/>
+    <mergeCell ref="E73:N73"/>
+    <mergeCell ref="E72:N72"/>
     <mergeCell ref="E71:N71"/>
     <mergeCell ref="E70:N70"/>
-    <mergeCell ref="E69:N69"/>
-    <mergeCell ref="E68:N68"/>
-    <mergeCell ref="E67:N67"/>
-    <mergeCell ref="AX75:BL75"/>
-    <mergeCell ref="BM75:CI75"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="AX78:BL78"/>
+    <mergeCell ref="BM78:CI78"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="C67:D67"/>
     <mergeCell ref="C68:D68"/>
     <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E63:N63"/>
-    <mergeCell ref="E64:N64"/>
-    <mergeCell ref="O63:AO63"/>
-    <mergeCell ref="AP63:AR63"/>
-    <mergeCell ref="AS63:AW63"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E66:N66"/>
+    <mergeCell ref="E67:N67"/>
+    <mergeCell ref="O66:AO66"/>
+    <mergeCell ref="AP66:AR66"/>
+    <mergeCell ref="AS66:AW66"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="E78:N78"/>
+    <mergeCell ref="O78:AO78"/>
+    <mergeCell ref="AP78:AR78"/>
+    <mergeCell ref="AS78:AW78"/>
+    <mergeCell ref="AX65:BL65"/>
+    <mergeCell ref="BM65:CI65"/>
     <mergeCell ref="C75:D75"/>
     <mergeCell ref="E75:N75"/>
     <mergeCell ref="O75:AO75"/>
     <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="AS75:AW75"/>
-    <mergeCell ref="AX62:BL62"/>
-    <mergeCell ref="BM62:CI62"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="E72:N72"/>
-    <mergeCell ref="O72:AO72"/>
-    <mergeCell ref="AP72:AR72"/>
-    <mergeCell ref="AS72:AW72"/>
-    <mergeCell ref="AX72:BL72"/>
-    <mergeCell ref="BM72:CI72"/>
+    <mergeCell ref="AX75:BL75"/>
+    <mergeCell ref="BM75:CI75"/>
+    <mergeCell ref="AX66:BL66"/>
+    <mergeCell ref="BM66:CI66"/>
+    <mergeCell ref="O67:AO67"/>
+    <mergeCell ref="AP67:AR67"/>
+    <mergeCell ref="AS67:AW67"/>
+    <mergeCell ref="AX67:BL67"/>
+    <mergeCell ref="BM67:CI67"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:N65"/>
+    <mergeCell ref="O65:AO65"/>
+    <mergeCell ref="AP65:AR65"/>
+    <mergeCell ref="AS65:AW65"/>
     <mergeCell ref="AX63:BL63"/>
     <mergeCell ref="BM63:CI63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:N64"/>
     <mergeCell ref="O64:AO64"/>
     <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="AS64:AW64"/>
     <mergeCell ref="AX64:BL64"/>
     <mergeCell ref="BM64:CI64"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:N62"/>
-    <mergeCell ref="O62:AO62"/>
-    <mergeCell ref="AP62:AR62"/>
-    <mergeCell ref="AS62:AW62"/>
-    <mergeCell ref="AX60:BL60"/>
-    <mergeCell ref="BM60:CI60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:N61"/>
-    <mergeCell ref="O61:AO61"/>
-    <mergeCell ref="AP61:AR61"/>
-    <mergeCell ref="AS61:AW61"/>
-    <mergeCell ref="AX61:BL61"/>
-    <mergeCell ref="BM61:CI61"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:N60"/>
-    <mergeCell ref="O60:AO60"/>
-    <mergeCell ref="AP60:AR60"/>
-    <mergeCell ref="AS60:AW60"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="H56:CI56"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:H58"/>
-    <mergeCell ref="I58:CI58"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:N63"/>
+    <mergeCell ref="O63:AO63"/>
+    <mergeCell ref="AP63:AR63"/>
+    <mergeCell ref="AS63:AW63"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:G59"/>
+    <mergeCell ref="H59:CI59"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="I61:CI61"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="L1:CI1"/>
     <mergeCell ref="A2:K2"/>

--- a/document/UI-001_VR内UI_画面仕様書.xlsx
+++ b/document/UI-001_VR内UI_画面仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tryro-dev-camera_sim\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3162D3CA-A063-4814-8D29-FFFDAC3EF6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E606E7-43AA-4245-B3FA-AAC653B222A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
